--- a/output/Data and Chart Outputs/guatemala_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/guatemala_power_generation_daily.xlsx
@@ -872,7 +872,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Bioenergy_MWh = BIOMASA + BIOGAS (sugar-mill bagasse cogeneration, landfill biogas).</t>
+          <t>Bioenergy_MWh = BIOMASA + BIOGAS + BIOMASA/CARBON (sugar-mill bagasse cogeneration, incl. mill boilers co-firing bagasse with coal, which AMM reports as one fuel; landfill biogas).</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2312,7 @@
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>413.5251</v>
+        <v>413.5252</v>
       </c>
     </row>
     <row r="54">
@@ -2338,7 +2338,7 @@
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>275.0964</v>
+        <v>275.0967</v>
       </c>
     </row>
     <row r="55">
@@ -2494,7 +2494,7 @@
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>228.3754</v>
+        <v>228.3753</v>
       </c>
     </row>
     <row r="61">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>369.7825</v>
+        <v>369.7824</v>
       </c>
     </row>
     <row r="62">
@@ -2546,7 +2546,7 @@
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>346.3065</v>
+        <v>346.3062</v>
       </c>
     </row>
     <row r="63">
@@ -2572,7 +2572,7 @@
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>318.0387</v>
+        <v>318.0388</v>
       </c>
     </row>
     <row r="64">
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>398.525</v>
+        <v>398.5251</v>
       </c>
     </row>
     <row r="65">
@@ -2624,7 +2624,7 @@
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>420.3828</v>
+        <v>420.3832</v>
       </c>
     </row>
     <row r="66">
@@ -57140,10 +57140,10 @@
         <v>5358.4</v>
       </c>
       <c r="I1553" t="n">
-        <v>5497.4</v>
+        <v>9269.200000000001</v>
       </c>
       <c r="J1553" t="n">
-        <v>4511</v>
+        <v>739.2</v>
       </c>
       <c r="K1553" t="n">
         <v>41047</v>
@@ -57175,10 +57175,10 @@
         <v>5211</v>
       </c>
       <c r="I1554" t="n">
-        <v>6290</v>
+        <v>10311.6</v>
       </c>
       <c r="J1554" t="n">
-        <v>4771.7</v>
+        <v>750</v>
       </c>
       <c r="K1554" t="n">
         <v>41154</v>
@@ -57210,10 +57210,10 @@
         <v>4446.8</v>
       </c>
       <c r="I1555" t="n">
-        <v>6671.3</v>
+        <v>10695.9</v>
       </c>
       <c r="J1555" t="n">
-        <v>4757.9</v>
+        <v>733.4</v>
       </c>
       <c r="K1555" t="n">
         <v>41424.4</v>
@@ -57245,10 +57245,10 @@
         <v>5327.5</v>
       </c>
       <c r="I1556" t="n">
-        <v>6675.4</v>
+        <v>10641.8</v>
       </c>
       <c r="J1556" t="n">
-        <v>4718.5</v>
+        <v>752.1</v>
       </c>
       <c r="K1556" t="n">
         <v>41807.9</v>
@@ -57280,10 +57280,10 @@
         <v>5115.6</v>
       </c>
       <c r="I1557" t="n">
-        <v>6711.7</v>
+        <v>10529.8</v>
       </c>
       <c r="J1557" t="n">
-        <v>4577.4</v>
+        <v>759.2</v>
       </c>
       <c r="K1557" t="n">
         <v>39648.6</v>
@@ -57315,10 +57315,10 @@
         <v>3303.9</v>
       </c>
       <c r="I1558" t="n">
-        <v>6819.2</v>
+        <v>10629.8</v>
       </c>
       <c r="J1558" t="n">
-        <v>4546.7</v>
+        <v>736.1</v>
       </c>
       <c r="K1558" t="n">
         <v>37274.5</v>
@@ -57350,10 +57350,10 @@
         <v>2548.8</v>
       </c>
       <c r="I1559" t="n">
-        <v>6067.4</v>
+        <v>9822.700000000001</v>
       </c>
       <c r="J1559" t="n">
-        <v>4512.2</v>
+        <v>757</v>
       </c>
       <c r="K1559" t="n">
         <v>38244</v>
@@ -57385,10 +57385,10 @@
         <v>344</v>
       </c>
       <c r="I1560" t="n">
-        <v>6078</v>
+        <v>9930.799999999999</v>
       </c>
       <c r="J1560" t="n">
-        <v>4591</v>
+        <v>738.2</v>
       </c>
       <c r="K1560" t="n">
         <v>36728.1</v>
@@ -57420,10 +57420,10 @@
         <v>744.7</v>
       </c>
       <c r="I1561" t="n">
-        <v>5613.1</v>
+        <v>9351</v>
       </c>
       <c r="J1561" t="n">
-        <v>4459.8</v>
+        <v>721.9</v>
       </c>
       <c r="K1561" t="n">
         <v>38228.7</v>
@@ -57455,10 +57455,10 @@
         <v>1246.4</v>
       </c>
       <c r="I1562" t="n">
-        <v>5973.9</v>
+        <v>9942</v>
       </c>
       <c r="J1562" t="n">
-        <v>4708.9</v>
+        <v>740.7</v>
       </c>
       <c r="K1562" t="n">
         <v>39380.3</v>
@@ -57490,10 +57490,10 @@
         <v>1712</v>
       </c>
       <c r="I1563" t="n">
-        <v>6229.7</v>
+        <v>10220</v>
       </c>
       <c r="J1563" t="n">
-        <v>4751.3</v>
+        <v>761</v>
       </c>
       <c r="K1563" t="n">
         <v>38694.1</v>
@@ -57525,10 +57525,10 @@
         <v>634.9</v>
       </c>
       <c r="I1564" t="n">
-        <v>6084.6</v>
+        <v>10072.8</v>
       </c>
       <c r="J1564" t="n">
-        <v>4756.9</v>
+        <v>768.7</v>
       </c>
       <c r="K1564" t="n">
         <v>36985.4</v>
@@ -57560,10 +57560,10 @@
         <v>1202</v>
       </c>
       <c r="I1565" t="n">
-        <v>6283.6</v>
+        <v>10252</v>
       </c>
       <c r="J1565" t="n">
-        <v>4739.4</v>
+        <v>771</v>
       </c>
       <c r="K1565" t="n">
         <v>33495.8</v>
@@ -57595,13 +57595,13 @@
         <v>1618.3</v>
       </c>
       <c r="I1566" t="n">
-        <v>6498.9</v>
+        <v>10501.1</v>
       </c>
       <c r="J1566" t="n">
-        <v>4760.4</v>
+        <v>758.3</v>
       </c>
       <c r="K1566" t="n">
-        <v>35543.7</v>
+        <v>35543.8</v>
       </c>
     </row>
     <row r="1567">
@@ -57630,10 +57630,10 @@
         <v>1413.3</v>
       </c>
       <c r="I1567" t="n">
-        <v>6385.4</v>
+        <v>10392.4</v>
       </c>
       <c r="J1567" t="n">
-        <v>4746.8</v>
+        <v>739.8</v>
       </c>
       <c r="K1567" t="n">
         <v>35536.2</v>
@@ -57665,10 +57665,10 @@
         <v>1120.4</v>
       </c>
       <c r="I1568" t="n">
-        <v>6429.1</v>
+        <v>10437.6</v>
       </c>
       <c r="J1568" t="n">
-        <v>4751.2</v>
+        <v>742.8</v>
       </c>
       <c r="K1568" t="n">
         <v>34114.9</v>
@@ -57700,10 +57700,10 @@
         <v>715</v>
       </c>
       <c r="I1569" t="n">
-        <v>6489.6</v>
+        <v>10446.9</v>
       </c>
       <c r="J1569" t="n">
-        <v>4693.8</v>
+        <v>736.6</v>
       </c>
       <c r="K1569" t="n">
         <v>31118.2</v>
@@ -57735,10 +57735,10 @@
         <v>604.8</v>
       </c>
       <c r="I1570" t="n">
-        <v>6563.8</v>
+        <v>10556.1</v>
       </c>
       <c r="J1570" t="n">
-        <v>4718.3</v>
+        <v>726</v>
       </c>
       <c r="K1570" t="n">
         <v>29326.2</v>
@@ -57770,10 +57770,10 @@
         <v>1002.6</v>
       </c>
       <c r="I1571" t="n">
-        <v>6276.6</v>
+        <v>10201.3</v>
       </c>
       <c r="J1571" t="n">
-        <v>4669.8</v>
+        <v>745.1</v>
       </c>
       <c r="K1571" t="n">
         <v>30197</v>
@@ -57805,10 +57805,10 @@
         <v>2375.5</v>
       </c>
       <c r="I1572" t="n">
-        <v>6234</v>
+        <v>10235.2</v>
       </c>
       <c r="J1572" t="n">
-        <v>4748.2</v>
+        <v>747</v>
       </c>
       <c r="K1572" t="n">
         <v>31319.2</v>
@@ -57840,10 +57840,10 @@
         <v>3162.8</v>
       </c>
       <c r="I1573" t="n">
-        <v>6331.1</v>
+        <v>10283.2</v>
       </c>
       <c r="J1573" t="n">
-        <v>4637.7</v>
+        <v>685.6</v>
       </c>
       <c r="K1573" t="n">
         <v>37995.7</v>
@@ -57875,10 +57875,10 @@
         <v>4775.7</v>
       </c>
       <c r="I1574" t="n">
-        <v>6237.6</v>
+        <v>10272.4</v>
       </c>
       <c r="J1574" t="n">
-        <v>4767.8</v>
+        <v>732.9</v>
       </c>
       <c r="K1574" t="n">
         <v>40675.9</v>
@@ -57910,10 +57910,10 @@
         <v>1862.4</v>
       </c>
       <c r="I1575" t="n">
-        <v>6537.2</v>
+        <v>10528.6</v>
       </c>
       <c r="J1575" t="n">
-        <v>4738.6</v>
+        <v>747.2</v>
       </c>
       <c r="K1575" t="n">
         <v>38676.4</v>
@@ -57945,10 +57945,10 @@
         <v>4799.2</v>
       </c>
       <c r="I1576" t="n">
-        <v>6463.2</v>
+        <v>10477</v>
       </c>
       <c r="J1576" t="n">
-        <v>4762.9</v>
+        <v>749.1</v>
       </c>
       <c r="K1576" t="n">
         <v>40895.4</v>
@@ -57980,10 +57980,10 @@
         <v>4920.2</v>
       </c>
       <c r="I1577" t="n">
-        <v>6205.2</v>
+        <v>10206.3</v>
       </c>
       <c r="J1577" t="n">
-        <v>4748.9</v>
+        <v>747.8</v>
       </c>
       <c r="K1577" t="n">
         <v>40214</v>
@@ -58015,10 +58015,10 @@
         <v>3266.6</v>
       </c>
       <c r="I1578" t="n">
-        <v>6284.8</v>
+        <v>10114.6</v>
       </c>
       <c r="J1578" t="n">
-        <v>4564</v>
+        <v>734.1</v>
       </c>
       <c r="K1578" t="n">
         <v>36287.1</v>
@@ -58050,10 +58050,10 @@
         <v>2188.8</v>
       </c>
       <c r="I1579" t="n">
-        <v>6194.3</v>
+        <v>10122.6</v>
       </c>
       <c r="J1579" t="n">
-        <v>4669.4</v>
+        <v>741.2</v>
       </c>
       <c r="K1579" t="n">
         <v>32208.6</v>
@@ -58085,10 +58085,10 @@
         <v>4824.9</v>
       </c>
       <c r="I1580" t="n">
-        <v>6609.7</v>
+        <v>9542.200000000001</v>
       </c>
       <c r="J1580" t="n">
-        <v>3662</v>
+        <v>729.4</v>
       </c>
       <c r="K1580" t="n">
         <v>36288.8</v>
@@ -58120,10 +58120,10 @@
         <v>4841.7</v>
       </c>
       <c r="I1581" t="n">
-        <v>6788.9</v>
+        <v>9740.1</v>
       </c>
       <c r="J1581" t="n">
-        <v>3707.6</v>
+        <v>756.4</v>
       </c>
       <c r="K1581" t="n">
         <v>36714.2</v>
@@ -58155,10 +58155,10 @@
         <v>5248</v>
       </c>
       <c r="I1582" t="n">
-        <v>6636.4</v>
+        <v>9586.799999999999</v>
       </c>
       <c r="J1582" t="n">
-        <v>3677.7</v>
+        <v>727.4</v>
       </c>
       <c r="K1582" t="n">
         <v>36926.8</v>
@@ -58190,10 +58190,10 @@
         <v>6210.9</v>
       </c>
       <c r="I1583" t="n">
-        <v>1435</v>
+        <v>2495.1</v>
       </c>
       <c r="J1583" t="n">
-        <v>1813.8</v>
+        <v>753.6</v>
       </c>
       <c r="K1583" t="n">
         <v>33208</v>
@@ -58225,10 +58225,10 @@
         <v>7815.3</v>
       </c>
       <c r="I1584" t="n">
-        <v>1340.3</v>
+        <v>2317</v>
       </c>
       <c r="J1584" t="n">
-        <v>1723.8</v>
+        <v>747.2</v>
       </c>
       <c r="K1584" t="n">
         <v>36802.7</v>
@@ -58260,10 +58260,10 @@
         <v>5436.2</v>
       </c>
       <c r="I1585" t="n">
-        <v>1053.8</v>
+        <v>2048.5</v>
       </c>
       <c r="J1585" t="n">
-        <v>1700.7</v>
+        <v>706</v>
       </c>
       <c r="K1585" t="n">
         <v>34897.8</v>
@@ -58295,10 +58295,10 @@
         <v>4722.4</v>
       </c>
       <c r="I1586" t="n">
-        <v>908.1</v>
+        <v>1892.2</v>
       </c>
       <c r="J1586" t="n">
-        <v>1709.9</v>
+        <v>725.9</v>
       </c>
       <c r="K1586" t="n">
         <v>30981.1</v>
@@ -58330,10 +58330,10 @@
         <v>7165</v>
       </c>
       <c r="I1587" t="n">
-        <v>1238.7</v>
+        <v>2255.9</v>
       </c>
       <c r="J1587" t="n">
-        <v>1746.7</v>
+        <v>729.5</v>
       </c>
       <c r="K1587" t="n">
         <v>37716.8</v>
@@ -58365,10 +58365,10 @@
         <v>5845.6</v>
       </c>
       <c r="I1588" t="n">
-        <v>1271.1</v>
+        <v>2292.2</v>
       </c>
       <c r="J1588" t="n">
-        <v>1753.5</v>
+        <v>732.4</v>
       </c>
       <c r="K1588" t="n">
         <v>36905.5</v>
@@ -58400,10 +58400,10 @@
         <v>7319.3</v>
       </c>
       <c r="I1589" t="n">
-        <v>1418.7</v>
+        <v>2435.6</v>
       </c>
       <c r="J1589" t="n">
-        <v>1751.1</v>
+        <v>734.2</v>
       </c>
       <c r="K1589" t="n">
         <v>37728.2</v>
@@ -58435,10 +58435,10 @@
         <v>10060.6</v>
       </c>
       <c r="I1590" t="n">
-        <v>1420.1</v>
+        <v>2420.5</v>
       </c>
       <c r="J1590" t="n">
-        <v>1665.7</v>
+        <v>665.3</v>
       </c>
       <c r="K1590" t="n">
         <v>40138.3</v>
@@ -58470,10 +58470,10 @@
         <v>7036.7</v>
       </c>
       <c r="I1591" t="n">
-        <v>1309.3</v>
+        <v>2366.6</v>
       </c>
       <c r="J1591" t="n">
-        <v>1819</v>
+        <v>761.7</v>
       </c>
       <c r="K1591" t="n">
         <v>37920.9</v>
@@ -58505,10 +58505,10 @@
         <v>3849.5</v>
       </c>
       <c r="I1592" t="n">
-        <v>727.9</v>
+        <v>1738.6</v>
       </c>
       <c r="J1592" t="n">
-        <v>1756.4</v>
+        <v>745.8</v>
       </c>
       <c r="K1592" t="n">
         <v>31058.5</v>
@@ -58540,10 +58540,10 @@
         <v>3250</v>
       </c>
       <c r="I1593" t="n">
-        <v>729.4</v>
+        <v>1704.2</v>
       </c>
       <c r="J1593" t="n">
-        <v>1701.2</v>
+        <v>726.4</v>
       </c>
       <c r="K1593" t="n">
         <v>29127.7</v>
@@ -58575,10 +58575,10 @@
         <v>4132.1</v>
       </c>
       <c r="I1594" t="n">
-        <v>730.1</v>
+        <v>1793.3</v>
       </c>
       <c r="J1594" t="n">
-        <v>1784.8</v>
+        <v>721.6</v>
       </c>
       <c r="K1594" t="n">
         <v>33988.5</v>
@@ -58610,10 +58610,10 @@
         <v>4927.2</v>
       </c>
       <c r="I1595" t="n">
-        <v>1155.6</v>
+        <v>2173</v>
       </c>
       <c r="J1595" t="n">
-        <v>1734.4</v>
+        <v>717</v>
       </c>
       <c r="K1595" t="n">
         <v>37464.9</v>
@@ -58645,10 +58645,10 @@
         <v>5345.2</v>
       </c>
       <c r="I1596" t="n">
-        <v>1176.9</v>
+        <v>2219</v>
       </c>
       <c r="J1596" t="n">
-        <v>1789.7</v>
+        <v>747.6</v>
       </c>
       <c r="K1596" t="n">
         <v>36830.7</v>
@@ -58680,10 +58680,10 @@
         <v>6385.1</v>
       </c>
       <c r="I1597" t="n">
-        <v>1344.2</v>
+        <v>2298</v>
       </c>
       <c r="J1597" t="n">
-        <v>1699.7</v>
+        <v>745.9</v>
       </c>
       <c r="K1597" t="n">
         <v>39071.3</v>
@@ -58715,10 +58715,10 @@
         <v>6061.1</v>
       </c>
       <c r="I1598" t="n">
-        <v>1275.4</v>
+        <v>2214.7</v>
       </c>
       <c r="J1598" t="n">
-        <v>1671</v>
+        <v>731.7</v>
       </c>
       <c r="K1598" t="n">
         <v>39037.2</v>
@@ -58750,10 +58750,10 @@
         <v>4499.6</v>
       </c>
       <c r="I1599" t="n">
-        <v>1158.8</v>
+        <v>2168.2</v>
       </c>
       <c r="J1599" t="n">
-        <v>1745.8</v>
+        <v>736.5</v>
       </c>
       <c r="K1599" t="n">
         <v>36959.2</v>
@@ -58785,10 +58785,10 @@
         <v>2909.2</v>
       </c>
       <c r="I1600" t="n">
-        <v>1192.3</v>
+        <v>2184.8</v>
       </c>
       <c r="J1600" t="n">
-        <v>1729.4</v>
+        <v>736.9</v>
       </c>
       <c r="K1600" t="n">
         <v>32496</v>
@@ -58820,10 +58820,10 @@
         <v>5668.6</v>
       </c>
       <c r="I1601" t="n">
-        <v>1242.3</v>
+        <v>2315.6</v>
       </c>
       <c r="J1601" t="n">
-        <v>1815</v>
+        <v>741.6</v>
       </c>
       <c r="K1601" t="n">
         <v>37278.4</v>
@@ -58855,10 +58855,10 @@
         <v>6113</v>
       </c>
       <c r="I1602" t="n">
-        <v>1345.2</v>
+        <v>2430.4</v>
       </c>
       <c r="J1602" t="n">
-        <v>1811.4</v>
+        <v>726.2</v>
       </c>
       <c r="K1602" t="n">
         <v>38563.1</v>
@@ -58890,10 +58890,10 @@
         <v>7047.3</v>
       </c>
       <c r="I1603" t="n">
-        <v>1344.7</v>
+        <v>2425.3</v>
       </c>
       <c r="J1603" t="n">
-        <v>1816.7</v>
+        <v>736.1</v>
       </c>
       <c r="K1603" t="n">
         <v>39023.9</v>
@@ -58925,10 +58925,10 @@
         <v>6932</v>
       </c>
       <c r="I1604" t="n">
-        <v>1343.2</v>
+        <v>2468.2</v>
       </c>
       <c r="J1604" t="n">
-        <v>1859</v>
+        <v>734.1</v>
       </c>
       <c r="K1604" t="n">
         <v>38981.7</v>
@@ -58960,10 +58960,10 @@
         <v>5739.5</v>
       </c>
       <c r="I1605" t="n">
-        <v>1347</v>
+        <v>2407.4</v>
       </c>
       <c r="J1605" t="n">
-        <v>1789.8</v>
+        <v>729.5</v>
       </c>
       <c r="K1605" t="n">
         <v>37909.9</v>
@@ -58995,10 +58995,10 @@
         <v>3942.4</v>
       </c>
       <c r="I1606" t="n">
-        <v>1108.9</v>
+        <v>2214.2</v>
       </c>
       <c r="J1606" t="n">
-        <v>1822.2</v>
+        <v>717</v>
       </c>
       <c r="K1606" t="n">
         <v>35908.2</v>
@@ -59030,13 +59030,13 @@
         <v>3101.2</v>
       </c>
       <c r="I1607" t="n">
-        <v>968.7</v>
+        <v>1990.6</v>
       </c>
       <c r="J1607" t="n">
-        <v>1732.7</v>
+        <v>710.8</v>
       </c>
       <c r="K1607" t="n">
-        <v>30987.3</v>
+        <v>30987.2</v>
       </c>
     </row>
     <row r="1608">
@@ -59065,10 +59065,10 @@
         <v>6050.9</v>
       </c>
       <c r="I1608" t="n">
-        <v>1213.4</v>
+        <v>2457.3</v>
       </c>
       <c r="J1608" t="n">
-        <v>1984.5</v>
+        <v>740.6</v>
       </c>
       <c r="K1608" t="n">
         <v>35158</v>
@@ -59100,10 +59100,10 @@
         <v>6603.2</v>
       </c>
       <c r="I1609" t="n">
-        <v>1342.1</v>
+        <v>3652.1</v>
       </c>
       <c r="J1609" t="n">
-        <v>3053.3</v>
+        <v>743.3</v>
       </c>
       <c r="K1609" t="n">
         <v>37171.3</v>
@@ -59135,10 +59135,10 @@
         <v>6994.5</v>
       </c>
       <c r="I1610" t="n">
-        <v>1329</v>
+        <v>3590.8</v>
       </c>
       <c r="J1610" t="n">
-        <v>2977</v>
+        <v>715.2</v>
       </c>
       <c r="K1610" t="n">
         <v>37327.8</v>
@@ -59170,10 +59170,10 @@
         <v>6387.9</v>
       </c>
       <c r="I1611" t="n">
-        <v>1217.7</v>
+        <v>3189.7</v>
       </c>
       <c r="J1611" t="n">
-        <v>2696.1</v>
+        <v>724</v>
       </c>
       <c r="K1611" t="n">
         <v>36519.9</v>
@@ -59205,10 +59205,10 @@
         <v>6092.4</v>
       </c>
       <c r="I1612" t="n">
-        <v>1263.9</v>
+        <v>3263.9</v>
       </c>
       <c r="J1612" t="n">
-        <v>2722.5</v>
+        <v>722.4</v>
       </c>
       <c r="K1612" t="n">
         <v>35985.4</v>
@@ -59240,10 +59240,10 @@
         <v>4420</v>
       </c>
       <c r="I1613" t="n">
-        <v>1154.6</v>
+        <v>2993.9</v>
       </c>
       <c r="J1613" t="n">
-        <v>2549.3</v>
+        <v>710</v>
       </c>
       <c r="K1613" t="n">
         <v>34242.6</v>
@@ -64630,10 +64630,10 @@
         <v>1</v>
       </c>
       <c r="I1767" t="n">
-        <v>519.7</v>
+        <v>1247.2</v>
       </c>
       <c r="J1767" t="n">
-        <v>1488.4</v>
+        <v>760.9</v>
       </c>
       <c r="K1767" t="n">
         <v>31152</v>
@@ -64665,10 +64665,10 @@
         <v>85.3</v>
       </c>
       <c r="I1768" t="n">
-        <v>522.5</v>
+        <v>1250.2</v>
       </c>
       <c r="J1768" t="n">
-        <v>1480.8</v>
+        <v>753.1</v>
       </c>
       <c r="K1768" t="n">
         <v>27510.9</v>
@@ -64700,10 +64700,10 @@
         <v>195.2</v>
       </c>
       <c r="I1769" t="n">
-        <v>608.8</v>
+        <v>2142.4</v>
       </c>
       <c r="J1769" t="n">
-        <v>2272.2</v>
+        <v>738.6</v>
       </c>
       <c r="K1769" t="n">
         <v>33828.1</v>
@@ -64735,10 +64735,10 @@
         <v>655.8</v>
       </c>
       <c r="I1770" t="n">
-        <v>895.4</v>
+        <v>2856.3</v>
       </c>
       <c r="J1770" t="n">
-        <v>2714.9</v>
+        <v>754</v>
       </c>
       <c r="K1770" t="n">
         <v>34609.7</v>
@@ -64770,10 +64770,10 @@
         <v>1218.8</v>
       </c>
       <c r="I1771" t="n">
-        <v>921.1</v>
+        <v>3192.2</v>
       </c>
       <c r="J1771" t="n">
-        <v>3013.9</v>
+        <v>742.8</v>
       </c>
       <c r="K1771" t="n">
         <v>35438.6</v>
@@ -64805,10 +64805,10 @@
         <v>868.5</v>
       </c>
       <c r="I1772" t="n">
-        <v>694.5</v>
+        <v>2839.6</v>
       </c>
       <c r="J1772" t="n">
-        <v>2880.5</v>
+        <v>735.5</v>
       </c>
       <c r="K1772" t="n">
         <v>35897.6</v>
@@ -64840,10 +64840,10 @@
         <v>3134.7</v>
       </c>
       <c r="I1773" t="n">
-        <v>952.3</v>
+        <v>3414.8</v>
       </c>
       <c r="J1773" t="n">
-        <v>3210.4</v>
+        <v>747.9</v>
       </c>
       <c r="K1773" t="n">
         <v>37673.1</v>
@@ -64875,10 +64875,10 @@
         <v>3458.1</v>
       </c>
       <c r="I1774" t="n">
-        <v>1293.4</v>
+        <v>3563.9</v>
       </c>
       <c r="J1774" t="n">
-        <v>3018.5</v>
+        <v>748</v>
       </c>
       <c r="K1774" t="n">
         <v>36074.7</v>
@@ -64910,10 +64910,10 @@
         <v>1130.9</v>
       </c>
       <c r="I1775" t="n">
-        <v>1408.3</v>
+        <v>3447.4</v>
       </c>
       <c r="J1775" t="n">
-        <v>2773</v>
+        <v>734</v>
       </c>
       <c r="K1775" t="n">
         <v>30283.6</v>
@@ -64945,10 +64945,10 @@
         <v>842.7</v>
       </c>
       <c r="I1776" t="n">
-        <v>1410.7</v>
+        <v>3635.8</v>
       </c>
       <c r="J1776" t="n">
-        <v>2950.6</v>
+        <v>725.5</v>
       </c>
       <c r="K1776" t="n">
         <v>34826.7</v>
@@ -64980,10 +64980,10 @@
         <v>138.7</v>
       </c>
       <c r="I1777" t="n">
-        <v>1176.4</v>
+        <v>2534.6</v>
       </c>
       <c r="J1777" t="n">
-        <v>1974.2</v>
+        <v>615.9</v>
       </c>
       <c r="K1777" t="n">
         <v>34019.8</v>
@@ -65015,10 +65015,10 @@
         <v>156.9</v>
       </c>
       <c r="I1778" t="n">
-        <v>1012.1</v>
+        <v>2815.8</v>
       </c>
       <c r="J1778" t="n">
-        <v>2442.3</v>
+        <v>638.6</v>
       </c>
       <c r="K1778" t="n">
         <v>34854.6</v>
@@ -65050,10 +65050,10 @@
         <v>674.2</v>
       </c>
       <c r="I1779" t="n">
-        <v>1324.2</v>
+        <v>3264.9</v>
       </c>
       <c r="J1779" t="n">
-        <v>2685.7</v>
+        <v>745</v>
       </c>
       <c r="K1779" t="n">
         <v>35973.4</v>
@@ -65085,10 +65085,10 @@
         <v>672.1</v>
       </c>
       <c r="I1780" t="n">
-        <v>1822.9</v>
+        <v>4327.5</v>
       </c>
       <c r="J1780" t="n">
-        <v>3243.8</v>
+        <v>739.2</v>
       </c>
       <c r="K1780" t="n">
         <v>36125</v>
@@ -65120,10 +65120,10 @@
         <v>1093.5</v>
       </c>
       <c r="I1781" t="n">
-        <v>2479.6</v>
+        <v>5563.2</v>
       </c>
       <c r="J1781" t="n">
-        <v>3825.7</v>
+        <v>742.1</v>
       </c>
       <c r="K1781" t="n">
         <v>36980.2</v>
@@ -65155,10 +65155,10 @@
         <v>1627.7</v>
       </c>
       <c r="I1782" t="n">
-        <v>2631.9</v>
+        <v>5741.2</v>
       </c>
       <c r="J1782" t="n">
-        <v>3867.8</v>
+        <v>758.4</v>
       </c>
       <c r="K1782" t="n">
         <v>33202.4</v>
@@ -65190,10 +65190,10 @@
         <v>2601.3</v>
       </c>
       <c r="I1783" t="n">
-        <v>2867.4</v>
+        <v>5974.7</v>
       </c>
       <c r="J1783" t="n">
-        <v>3862.3</v>
+        <v>755</v>
       </c>
       <c r="K1783" t="n">
         <v>36920.9</v>
@@ -65225,10 +65225,10 @@
         <v>4196</v>
       </c>
       <c r="I1784" t="n">
-        <v>3246.6</v>
+        <v>6331.6</v>
       </c>
       <c r="J1784" t="n">
-        <v>3842.5</v>
+        <v>757.5</v>
       </c>
       <c r="K1784" t="n">
         <v>38708</v>
@@ -65260,10 +65260,10 @@
         <v>2493</v>
       </c>
       <c r="I1785" t="n">
-        <v>3675.2</v>
+        <v>6737.6</v>
       </c>
       <c r="J1785" t="n">
-        <v>3806.2</v>
+        <v>743.8</v>
       </c>
       <c r="K1785" t="n">
         <v>38473.3</v>
@@ -65295,10 +65295,10 @@
         <v>3211.3</v>
       </c>
       <c r="I1786" t="n">
-        <v>3832.6</v>
+        <v>6903.6</v>
       </c>
       <c r="J1786" t="n">
-        <v>3816.9</v>
+        <v>746</v>
       </c>
       <c r="K1786" t="n">
         <v>38116.1</v>
@@ -65330,10 +65330,10 @@
         <v>3895.8</v>
       </c>
       <c r="I1787" t="n">
-        <v>4171.6</v>
+        <v>7247.1</v>
       </c>
       <c r="J1787" t="n">
-        <v>3816.3</v>
+        <v>740.8</v>
       </c>
       <c r="K1787" t="n">
         <v>39137.6</v>
@@ -65365,10 +65365,10 @@
         <v>1289.3</v>
       </c>
       <c r="I1788" t="n">
-        <v>4200</v>
+        <v>7545.9</v>
       </c>
       <c r="J1788" t="n">
-        <v>4071.1</v>
+        <v>725.2</v>
       </c>
       <c r="K1788" t="n">
         <v>33662.9</v>
@@ -65400,10 +65400,10 @@
         <v>69.09999999999999</v>
       </c>
       <c r="I1789" t="n">
-        <v>4157.2</v>
+        <v>8590</v>
       </c>
       <c r="J1789" t="n">
-        <v>5146</v>
+        <v>713.2</v>
       </c>
       <c r="K1789" t="n">
         <v>30230.8</v>
@@ -65435,10 +65435,10 @@
         <v>1009.8</v>
       </c>
       <c r="I1790" t="n">
-        <v>4595.8</v>
+        <v>9576.700000000001</v>
       </c>
       <c r="J1790" t="n">
-        <v>5716</v>
+        <v>735</v>
       </c>
       <c r="K1790" t="n">
         <v>35953.4</v>
@@ -65470,10 +65470,10 @@
         <v>1833.1</v>
       </c>
       <c r="I1791" t="n">
-        <v>4970</v>
+        <v>9892.799999999999</v>
       </c>
       <c r="J1791" t="n">
-        <v>5673.5</v>
+        <v>750.7</v>
       </c>
       <c r="K1791" t="n">
         <v>38968</v>
@@ -65505,10 +65505,10 @@
         <v>1390.3</v>
       </c>
       <c r="I1792" t="n">
-        <v>4764.8</v>
+        <v>9187.299999999999</v>
       </c>
       <c r="J1792" t="n">
-        <v>5160.5</v>
+        <v>738</v>
       </c>
       <c r="K1792" t="n">
         <v>35936</v>
@@ -65540,10 +65540,10 @@
         <v>1382.5</v>
       </c>
       <c r="I1793" t="n">
-        <v>5052.7</v>
+        <v>9392.9</v>
       </c>
       <c r="J1793" t="n">
-        <v>5057.9</v>
+        <v>717.7</v>
       </c>
       <c r="K1793" t="n">
         <v>37817.1</v>
@@ -65575,10 +65575,10 @@
         <v>423.3</v>
       </c>
       <c r="I1794" t="n">
-        <v>4540</v>
+        <v>8878.700000000001</v>
       </c>
       <c r="J1794" t="n">
-        <v>5068.7</v>
+        <v>730</v>
       </c>
       <c r="K1794" t="n">
         <v>37047.9</v>
@@ -65610,10 +65610,10 @@
         <v>1</v>
       </c>
       <c r="I1795" t="n">
-        <v>4584.3</v>
+        <v>8895.200000000001</v>
       </c>
       <c r="J1795" t="n">
-        <v>5056.1</v>
+        <v>745.2</v>
       </c>
       <c r="K1795" t="n">
         <v>32915.9</v>
@@ -65645,10 +65645,10 @@
         <v>212.4</v>
       </c>
       <c r="I1796" t="n">
-        <v>4636.8</v>
+        <v>9400.9</v>
       </c>
       <c r="J1796" t="n">
-        <v>5507.6</v>
+        <v>743.4</v>
       </c>
       <c r="K1796" t="n">
         <v>32277.4</v>
@@ -65680,10 +65680,10 @@
         <v>962.4</v>
       </c>
       <c r="I1797" t="n">
-        <v>8057.8</v>
+        <v>9761.6</v>
       </c>
       <c r="J1797" t="n">
-        <v>2448.8</v>
+        <v>745</v>
       </c>
       <c r="K1797" t="n">
         <v>34094.7</v>
@@ -65715,10 +65715,10 @@
         <v>3153.7</v>
       </c>
       <c r="I1798" t="n">
-        <v>8410.799999999999</v>
+        <v>10182.3</v>
       </c>
       <c r="J1798" t="n">
-        <v>2512</v>
+        <v>740.5</v>
       </c>
       <c r="K1798" t="n">
         <v>37258.7</v>
@@ -65750,10 +65750,10 @@
         <v>1621</v>
       </c>
       <c r="I1799" t="n">
-        <v>8859.799999999999</v>
+        <v>10613.6</v>
       </c>
       <c r="J1799" t="n">
-        <v>2489.9</v>
+        <v>736.1</v>
       </c>
       <c r="K1799" t="n">
         <v>35808.4</v>
@@ -65785,10 +65785,10 @@
         <v>2557.1</v>
       </c>
       <c r="I1800" t="n">
-        <v>8597</v>
+        <v>10314.2</v>
       </c>
       <c r="J1800" t="n">
-        <v>2436.2</v>
+        <v>719</v>
       </c>
       <c r="K1800" t="n">
         <v>38095.2</v>
@@ -65820,10 +65820,10 @@
         <v>3288.5</v>
       </c>
       <c r="I1801" t="n">
-        <v>8717</v>
+        <v>10455</v>
       </c>
       <c r="J1801" t="n">
-        <v>2121.4</v>
+        <v>383.4</v>
       </c>
       <c r="K1801" t="n">
         <v>39216.3</v>
@@ -65855,10 +65855,10 @@
         <v>2869.9</v>
       </c>
       <c r="I1802" t="n">
-        <v>8843.700000000001</v>
+        <v>10550.9</v>
       </c>
       <c r="J1802" t="n">
-        <v>2126.9</v>
+        <v>419.8</v>
       </c>
       <c r="K1802" t="n">
         <v>37717.3</v>
@@ -65890,10 +65890,10 @@
         <v>3481.4</v>
       </c>
       <c r="I1803" t="n">
-        <v>8975.9</v>
+        <v>10734.2</v>
       </c>
       <c r="J1803" t="n">
-        <v>2293.4</v>
+        <v>535</v>
       </c>
       <c r="K1803" t="n">
         <v>33922.8</v>
@@ -65925,10 +65925,10 @@
         <v>4578.6</v>
       </c>
       <c r="I1804" t="n">
-        <v>8757.200000000001</v>
+        <v>10472.2</v>
       </c>
       <c r="J1804" t="n">
-        <v>2266.8</v>
+        <v>551.8</v>
       </c>
       <c r="K1804" t="n">
         <v>37395.1</v>
@@ -65960,10 +65960,10 @@
         <v>3737.2</v>
       </c>
       <c r="I1805" t="n">
-        <v>8426.4</v>
+        <v>10071.6</v>
       </c>
       <c r="J1805" t="n">
-        <v>2264.5</v>
+        <v>619.3</v>
       </c>
       <c r="K1805" t="n">
         <v>36071.5</v>
@@ -65995,10 +65995,10 @@
         <v>3113.3</v>
       </c>
       <c r="I1806" t="n">
-        <v>8190.9</v>
+        <v>9848.299999999999</v>
       </c>
       <c r="J1806" t="n">
-        <v>2397.1</v>
+        <v>739.7</v>
       </c>
       <c r="K1806" t="n">
         <v>36705</v>
@@ -66030,10 +66030,10 @@
         <v>3011</v>
       </c>
       <c r="I1807" t="n">
-        <v>8292.5</v>
+        <v>9942.6</v>
       </c>
       <c r="J1807" t="n">
-        <v>2361</v>
+        <v>710.8</v>
       </c>
       <c r="K1807" t="n">
         <v>37344.4</v>
@@ -66065,10 +66065,10 @@
         <v>1277</v>
       </c>
       <c r="I1808" t="n">
-        <v>8676.6</v>
+        <v>10332.5</v>
       </c>
       <c r="J1808" t="n">
-        <v>2373.8</v>
+        <v>717.9</v>
       </c>
       <c r="K1808" t="n">
         <v>36446.6</v>
@@ -66100,10 +66100,10 @@
         <v>1956.1</v>
       </c>
       <c r="I1809" t="n">
-        <v>8652.4</v>
+        <v>10281.7</v>
       </c>
       <c r="J1809" t="n">
-        <v>2353.8</v>
+        <v>724.4</v>
       </c>
       <c r="K1809" t="n">
         <v>35246.9</v>
@@ -66135,10 +66135,10 @@
         <v>134.9</v>
       </c>
       <c r="I1810" t="n">
-        <v>8337.799999999999</v>
+        <v>9994.700000000001</v>
       </c>
       <c r="J1810" t="n">
-        <v>2201</v>
+        <v>544.2</v>
       </c>
       <c r="K1810" t="n">
         <v>31038.4</v>
@@ -66170,10 +66170,10 @@
         <v>242.8</v>
       </c>
       <c r="I1811" t="n">
-        <v>8410</v>
+        <v>9961.6</v>
       </c>
       <c r="J1811" t="n">
-        <v>2093.9</v>
+        <v>542.2</v>
       </c>
       <c r="K1811" t="n">
         <v>36561.7</v>
@@ -66205,10 +66205,10 @@
         <v>484</v>
       </c>
       <c r="I1812" t="n">
-        <v>7894.1</v>
+        <v>9440.4</v>
       </c>
       <c r="J1812" t="n">
-        <v>2099.2</v>
+        <v>552.8</v>
       </c>
       <c r="K1812" t="n">
         <v>39793.6</v>
@@ -66240,10 +66240,10 @@
         <v>183.3</v>
       </c>
       <c r="I1813" t="n">
-        <v>7941.4</v>
+        <v>9560.799999999999</v>
       </c>
       <c r="J1813" t="n">
-        <v>2178.6</v>
+        <v>559.2</v>
       </c>
       <c r="K1813" t="n">
         <v>40625.6</v>
@@ -66275,10 +66275,10 @@
         <v>265.6</v>
       </c>
       <c r="I1814" t="n">
-        <v>8165.2</v>
+        <v>9791.4</v>
       </c>
       <c r="J1814" t="n">
-        <v>2197.2</v>
+        <v>571</v>
       </c>
       <c r="K1814" t="n">
         <v>40914</v>
@@ -66310,10 +66310,10 @@
         <v>723.7</v>
       </c>
       <c r="I1815" t="n">
-        <v>7719.7</v>
+        <v>9345</v>
       </c>
       <c r="J1815" t="n">
-        <v>2282.5</v>
+        <v>657.2</v>
       </c>
       <c r="K1815" t="n">
         <v>39449.9</v>
@@ -66345,10 +66345,10 @@
         <v>1924.9</v>
       </c>
       <c r="I1816" t="n">
-        <v>8305.5</v>
+        <v>9960.200000000001</v>
       </c>
       <c r="J1816" t="n">
-        <v>2388.2</v>
+        <v>733.5</v>
       </c>
       <c r="K1816" t="n">
         <v>38988.2</v>
@@ -66380,10 +66380,10 @@
         <v>1858.4</v>
       </c>
       <c r="I1817" t="n">
-        <v>7574.6</v>
+        <v>9233.200000000001</v>
       </c>
       <c r="J1817" t="n">
-        <v>2409.2</v>
+        <v>750.6</v>
       </c>
       <c r="K1817" t="n">
         <v>34872.5</v>
@@ -66415,10 +66415,10 @@
         <v>911.6</v>
       </c>
       <c r="I1818" t="n">
-        <v>8488.6</v>
+        <v>10109.3</v>
       </c>
       <c r="J1818" t="n">
-        <v>2370.4</v>
+        <v>749.7</v>
       </c>
       <c r="K1818" t="n">
         <v>37019.8</v>
@@ -66450,10 +66450,10 @@
         <v>460.4</v>
       </c>
       <c r="I1819" t="n">
-        <v>8502.6</v>
+        <v>10131.2</v>
       </c>
       <c r="J1819" t="n">
-        <v>2365.5</v>
+        <v>736.9</v>
       </c>
       <c r="K1819" t="n">
         <v>36737.1</v>
@@ -66485,10 +66485,10 @@
         <v>24</v>
       </c>
       <c r="I1820" t="n">
-        <v>7366</v>
+        <v>8772.700000000001</v>
       </c>
       <c r="J1820" t="n">
-        <v>2137.3</v>
+        <v>730.7</v>
       </c>
       <c r="K1820" t="n">
         <v>33409.7</v>
@@ -66520,10 +66520,10 @@
         <v>0</v>
       </c>
       <c r="I1821" t="n">
-        <v>7259.9</v>
+        <v>8709.799999999999</v>
       </c>
       <c r="J1821" t="n">
-        <v>2177.4</v>
+        <v>727.4</v>
       </c>
       <c r="K1821" t="n">
         <v>32370.5</v>
@@ -66555,10 +66555,10 @@
         <v>1.6</v>
       </c>
       <c r="I1822" t="n">
-        <v>7904.3</v>
+        <v>9412.700000000001</v>
       </c>
       <c r="J1822" t="n">
-        <v>2267</v>
+        <v>758.6</v>
       </c>
       <c r="K1822" t="n">
         <v>35524.1</v>
@@ -66590,10 +66590,10 @@
         <v>1</v>
       </c>
       <c r="I1823" t="n">
-        <v>7684</v>
+        <v>9387.9</v>
       </c>
       <c r="J1823" t="n">
-        <v>2468.3</v>
+        <v>764.4</v>
       </c>
       <c r="K1823" t="n">
         <v>35336.2</v>
@@ -66625,10 +66625,10 @@
         <v>94.59999999999999</v>
       </c>
       <c r="I1824" t="n">
-        <v>8052.7</v>
+        <v>9667.4</v>
       </c>
       <c r="J1824" t="n">
-        <v>2380.8</v>
+        <v>766.2</v>
       </c>
       <c r="K1824" t="n">
         <v>34113.6</v>
@@ -66660,10 +66660,10 @@
         <v>117.2</v>
       </c>
       <c r="I1825" t="n">
-        <v>8542.1</v>
+        <v>10227</v>
       </c>
       <c r="J1825" t="n">
-        <v>2443.8</v>
+        <v>759</v>
       </c>
       <c r="K1825" t="n">
         <v>34573.8</v>
@@ -66695,10 +66695,10 @@
         <v>251.8</v>
       </c>
       <c r="I1826" t="n">
-        <v>8123.3</v>
+        <v>9781.4</v>
       </c>
       <c r="J1826" t="n">
-        <v>2398.7</v>
+        <v>740.7</v>
       </c>
       <c r="K1826" t="n">
         <v>33905.7</v>
@@ -66730,10 +66730,10 @@
         <v>117.1</v>
       </c>
       <c r="I1827" t="n">
-        <v>7112.3</v>
+        <v>8594.299999999999</v>
       </c>
       <c r="J1827" t="n">
-        <v>2231.7</v>
+        <v>749.6</v>
       </c>
       <c r="K1827" t="n">
         <v>32163.3</v>
@@ -66765,10 +66765,10 @@
         <v>0.4</v>
       </c>
       <c r="I1828" t="n">
-        <v>6862</v>
+        <v>8239.200000000001</v>
       </c>
       <c r="J1828" t="n">
-        <v>2135.4</v>
+        <v>758.2</v>
       </c>
       <c r="K1828" t="n">
         <v>29826</v>
@@ -66800,10 +66800,10 @@
         <v>89.40000000000001</v>
       </c>
       <c r="I1829" t="n">
-        <v>8065.8</v>
+        <v>9104</v>
       </c>
       <c r="J1829" t="n">
-        <v>1787.6</v>
+        <v>749.4</v>
       </c>
       <c r="K1829" t="n">
         <v>31972.9</v>
@@ -66835,10 +66835,10 @@
         <v>1425.5</v>
       </c>
       <c r="I1830" t="n">
-        <v>8334</v>
+        <v>9409.200000000001</v>
       </c>
       <c r="J1830" t="n">
-        <v>1838.1</v>
+        <v>762.8</v>
       </c>
       <c r="K1830" t="n">
         <v>32066.1</v>
@@ -66870,10 +66870,10 @@
         <v>153.1</v>
       </c>
       <c r="I1831" t="n">
-        <v>8052.9</v>
+        <v>9165.200000000001</v>
       </c>
       <c r="J1831" t="n">
-        <v>1867.5</v>
+        <v>755.2</v>
       </c>
       <c r="K1831" t="n">
         <v>29355.7</v>
@@ -66905,10 +66905,10 @@
         <v>101.3</v>
       </c>
       <c r="I1832" t="n">
-        <v>8452.4</v>
+        <v>10133.9</v>
       </c>
       <c r="J1832" t="n">
-        <v>2458.4</v>
+        <v>776.9</v>
       </c>
       <c r="K1832" t="n">
         <v>33718.6</v>
@@ -66940,10 +66940,10 @@
         <v>399.9</v>
       </c>
       <c r="I1833" t="n">
-        <v>8180</v>
+        <v>9864</v>
       </c>
       <c r="J1833" t="n">
-        <v>2457.2</v>
+        <v>773.2</v>
       </c>
       <c r="K1833" t="n">
         <v>34819.1</v>
@@ -66975,10 +66975,10 @@
         <v>88.2</v>
       </c>
       <c r="I1834" t="n">
-        <v>8376.4</v>
+        <v>10044.8</v>
       </c>
       <c r="J1834" t="n">
-        <v>2433.5</v>
+        <v>765</v>
       </c>
       <c r="K1834" t="n">
         <v>34925.6</v>
@@ -67010,10 +67010,10 @@
         <v>638.1</v>
       </c>
       <c r="I1835" t="n">
-        <v>8470.5</v>
+        <v>10010.7</v>
       </c>
       <c r="J1835" t="n">
-        <v>2313.7</v>
+        <v>773.5</v>
       </c>
       <c r="K1835" t="n">
         <v>36233.2</v>
@@ -67045,10 +67045,10 @@
         <v>2443.5</v>
       </c>
       <c r="I1836" t="n">
-        <v>8444.700000000001</v>
+        <v>9518.299999999999</v>
       </c>
       <c r="J1836" t="n">
-        <v>1821.4</v>
+        <v>747.8</v>
       </c>
       <c r="K1836" t="n">
         <v>38110.8</v>
@@ -67080,10 +67080,10 @@
         <v>259.6</v>
       </c>
       <c r="I1837" t="n">
-        <v>8781.299999999999</v>
+        <v>9859.200000000001</v>
       </c>
       <c r="J1837" t="n">
-        <v>1821.8</v>
+        <v>743.9</v>
       </c>
       <c r="K1837" t="n">
         <v>33761</v>
@@ -67115,10 +67115,10 @@
         <v>158.3</v>
       </c>
       <c r="I1838" t="n">
-        <v>8447.200000000001</v>
+        <v>9452.200000000001</v>
       </c>
       <c r="J1838" t="n">
-        <v>1733.4</v>
+        <v>728.4</v>
       </c>
       <c r="K1838" t="n">
         <v>30181.8</v>
@@ -67150,10 +67150,10 @@
         <v>508.2</v>
       </c>
       <c r="I1839" t="n">
-        <v>9056.5</v>
+        <v>10131.5</v>
       </c>
       <c r="J1839" t="n">
-        <v>1805.4</v>
+        <v>730.4</v>
       </c>
       <c r="K1839" t="n">
         <v>35513.4</v>
@@ -67185,10 +67185,10 @@
         <v>1383</v>
       </c>
       <c r="I1840" t="n">
-        <v>8542.4</v>
+        <v>9618.799999999999</v>
       </c>
       <c r="J1840" t="n">
-        <v>1814.9</v>
+        <v>738.5</v>
       </c>
       <c r="K1840" t="n">
         <v>37517.5</v>
@@ -67220,13 +67220,13 @@
         <v>81.8</v>
       </c>
       <c r="I1841" t="n">
-        <v>8854.5</v>
+        <v>9934.6</v>
       </c>
       <c r="J1841" t="n">
-        <v>1817.6</v>
+        <v>737.5</v>
       </c>
       <c r="K1841" t="n">
-        <v>36736.1</v>
+        <v>36736.2</v>
       </c>
     </row>
     <row r="1842">
@@ -67255,10 +67255,10 @@
         <v>82</v>
       </c>
       <c r="I1842" t="n">
-        <v>8638.5</v>
+        <v>9711.799999999999</v>
       </c>
       <c r="J1842" t="n">
-        <v>1798.4</v>
+        <v>725.1</v>
       </c>
       <c r="K1842" t="n">
         <v>37096.6</v>
@@ -67290,10 +67290,10 @@
         <v>1341.2</v>
       </c>
       <c r="I1843" t="n">
-        <v>8765.6</v>
+        <v>9836.6</v>
       </c>
       <c r="J1843" t="n">
-        <v>1827.2</v>
+        <v>756.2</v>
       </c>
       <c r="K1843" t="n">
         <v>36646</v>
@@ -67325,10 +67325,10 @@
         <v>116.5</v>
       </c>
       <c r="I1844" t="n">
-        <v>8817</v>
+        <v>9894</v>
       </c>
       <c r="J1844" t="n">
-        <v>1808.9</v>
+        <v>731.9</v>
       </c>
       <c r="K1844" t="n">
         <v>32117.1</v>
@@ -67360,10 +67360,10 @@
         <v>56.6</v>
       </c>
       <c r="I1845" t="n">
-        <v>8889.9</v>
+        <v>9968.799999999999</v>
       </c>
       <c r="J1845" t="n">
-        <v>1812.8</v>
+        <v>733.9</v>
       </c>
       <c r="K1845" t="n">
         <v>31165.5</v>
@@ -67395,10 +67395,10 @@
         <v>165.1</v>
       </c>
       <c r="I1846" t="n">
-        <v>8694.700000000001</v>
+        <v>9681.700000000001</v>
       </c>
       <c r="J1846" t="n">
-        <v>1718.9</v>
+        <v>731.9</v>
       </c>
       <c r="K1846" t="n">
         <v>33755.8</v>
@@ -67430,10 +67430,10 @@
         <v>93.2</v>
       </c>
       <c r="I1847" t="n">
-        <v>8662.6</v>
+        <v>9703</v>
       </c>
       <c r="J1847" t="n">
-        <v>1774.9</v>
+        <v>734.5</v>
       </c>
       <c r="K1847" t="n">
         <v>34508.3</v>
@@ -67465,10 +67465,10 @@
         <v>109.4</v>
       </c>
       <c r="I1848" t="n">
-        <v>8868.4</v>
+        <v>9946.700000000001</v>
       </c>
       <c r="J1848" t="n">
-        <v>1803.8</v>
+        <v>725.5</v>
       </c>
       <c r="K1848" t="n">
         <v>35793.4</v>
@@ -67500,10 +67500,10 @@
         <v>91.40000000000001</v>
       </c>
       <c r="I1849" t="n">
-        <v>8958.4</v>
+        <v>10015.5</v>
       </c>
       <c r="J1849" t="n">
-        <v>1776.1</v>
+        <v>719</v>
       </c>
       <c r="K1849" t="n">
         <v>36849.9</v>
@@ -67535,10 +67535,10 @@
         <v>1109.4</v>
       </c>
       <c r="I1850" t="n">
-        <v>8824</v>
+        <v>9899.4</v>
       </c>
       <c r="J1850" t="n">
-        <v>1806.4</v>
+        <v>731</v>
       </c>
       <c r="K1850" t="n">
         <v>38675.5</v>
@@ -67570,10 +67570,10 @@
         <v>2451.1</v>
       </c>
       <c r="I1851" t="n">
-        <v>8915.1</v>
+        <v>9986.200000000001</v>
       </c>
       <c r="J1851" t="n">
-        <v>1818.7</v>
+        <v>747.6</v>
       </c>
       <c r="K1851" t="n">
         <v>37019.2</v>
@@ -67605,10 +67605,10 @@
         <v>513.9</v>
       </c>
       <c r="I1852" t="n">
-        <v>8690.799999999999</v>
+        <v>9763.1</v>
       </c>
       <c r="J1852" t="n">
-        <v>1816.7</v>
+        <v>744.4</v>
       </c>
       <c r="K1852" t="n">
         <v>33026.3</v>
@@ -67640,10 +67640,10 @@
         <v>4234.7</v>
       </c>
       <c r="I1853" t="n">
-        <v>8653.200000000001</v>
+        <v>9723.200000000001</v>
       </c>
       <c r="J1853" t="n">
-        <v>1791.8</v>
+        <v>721.8</v>
       </c>
       <c r="K1853" t="n">
         <v>38457.2</v>
@@ -67675,10 +67675,10 @@
         <v>1821.8</v>
       </c>
       <c r="I1854" t="n">
-        <v>8345.5</v>
+        <v>9411.4</v>
       </c>
       <c r="J1854" t="n">
-        <v>1785.9</v>
+        <v>720</v>
       </c>
       <c r="K1854" t="n">
         <v>39314.8</v>
@@ -67710,10 +67710,10 @@
         <v>1004</v>
       </c>
       <c r="I1855" t="n">
-        <v>8303.6</v>
+        <v>9367.200000000001</v>
       </c>
       <c r="J1855" t="n">
-        <v>1795.9</v>
+        <v>732.2</v>
       </c>
       <c r="K1855" t="n">
         <v>38644</v>
@@ -67745,10 +67745,10 @@
         <v>93.7</v>
       </c>
       <c r="I1856" t="n">
-        <v>7985.5</v>
+        <v>9049</v>
       </c>
       <c r="J1856" t="n">
-        <v>1805</v>
+        <v>741.5</v>
       </c>
       <c r="K1856" t="n">
         <v>38201.1</v>
@@ -67780,10 +67780,10 @@
         <v>355</v>
       </c>
       <c r="I1857" t="n">
-        <v>8536.5</v>
+        <v>9607.1</v>
       </c>
       <c r="J1857" t="n">
-        <v>1814.1</v>
+        <v>743.5</v>
       </c>
       <c r="K1857" t="n">
         <v>37359.9</v>
@@ -67815,10 +67815,10 @@
         <v>1704.4</v>
       </c>
       <c r="I1858" t="n">
-        <v>9091.6</v>
+        <v>10159.1</v>
       </c>
       <c r="J1858" t="n">
-        <v>1809.9</v>
+        <v>742.4</v>
       </c>
       <c r="K1858" t="n">
         <v>35216.8</v>
@@ -67850,10 +67850,10 @@
         <v>44.3</v>
       </c>
       <c r="I1859" t="n">
-        <v>6519.4</v>
+        <v>9646.799999999999</v>
       </c>
       <c r="J1859" t="n">
-        <v>3885.6</v>
+        <v>758.2</v>
       </c>
       <c r="K1859" t="n">
         <v>29464.5</v>
@@ -67885,10 +67885,10 @@
         <v>144.3</v>
       </c>
       <c r="I1860" t="n">
-        <v>6385.4</v>
+        <v>9692.1</v>
       </c>
       <c r="J1860" t="n">
-        <v>4071.9</v>
+        <v>765.2</v>
       </c>
       <c r="K1860" t="n">
         <v>31926.7</v>
@@ -67920,10 +67920,10 @@
         <v>483.5</v>
       </c>
       <c r="I1861" t="n">
-        <v>6559.1</v>
+        <v>9909.4</v>
       </c>
       <c r="J1861" t="n">
-        <v>4103.9</v>
+        <v>753.6</v>
       </c>
       <c r="K1861" t="n">
         <v>35747.6</v>
@@ -67955,10 +67955,10 @@
         <v>159.3</v>
       </c>
       <c r="I1862" t="n">
-        <v>6258.4</v>
+        <v>9624.6</v>
       </c>
       <c r="J1862" t="n">
-        <v>4118.5</v>
+        <v>752.3</v>
       </c>
       <c r="K1862" t="n">
         <v>34508.9</v>
@@ -67990,10 +67990,10 @@
         <v>118.8</v>
       </c>
       <c r="I1863" t="n">
-        <v>6263.6</v>
+        <v>9628.799999999999</v>
       </c>
       <c r="J1863" t="n">
-        <v>4117.5</v>
+        <v>752.3</v>
       </c>
       <c r="K1863" t="n">
         <v>34859</v>
@@ -68025,10 +68025,10 @@
         <v>211.3</v>
       </c>
       <c r="I1864" t="n">
-        <v>6071.6</v>
+        <v>9433.799999999999</v>
       </c>
       <c r="J1864" t="n">
-        <v>4120.8</v>
+        <v>758.6</v>
       </c>
       <c r="K1864" t="n">
         <v>34869.1</v>
@@ -68060,10 +68060,10 @@
         <v>99.09999999999999</v>
       </c>
       <c r="I1865" t="n">
-        <v>6583.8</v>
+        <v>9944.1</v>
       </c>
       <c r="J1865" t="n">
-        <v>4118.8</v>
+        <v>758.5</v>
       </c>
       <c r="K1865" t="n">
         <v>30256.1</v>
@@ -68095,10 +68095,10 @@
         <v>834.5</v>
       </c>
       <c r="I1866" t="n">
-        <v>6499.2</v>
+        <v>9862</v>
       </c>
       <c r="J1866" t="n">
-        <v>4120.5</v>
+        <v>757.8</v>
       </c>
       <c r="K1866" t="n">
         <v>29785.2</v>
@@ -68130,10 +68130,10 @@
         <v>132</v>
       </c>
       <c r="I1867" t="n">
-        <v>6510.2</v>
+        <v>9871</v>
       </c>
       <c r="J1867" t="n">
-        <v>4115.1</v>
+        <v>754.3</v>
       </c>
       <c r="K1867" t="n">
         <v>32942.1</v>
@@ -68165,10 +68165,10 @@
         <v>364.4</v>
       </c>
       <c r="I1868" t="n">
-        <v>6217.2</v>
+        <v>9297.4</v>
       </c>
       <c r="J1868" t="n">
-        <v>3833.6</v>
+        <v>753.4</v>
       </c>
       <c r="K1868" t="n">
         <v>33895</v>
@@ -68200,10 +68200,10 @@
         <v>474.2</v>
       </c>
       <c r="I1869" t="n">
-        <v>6590.7</v>
+        <v>9953.700000000001</v>
       </c>
       <c r="J1869" t="n">
-        <v>4101.6</v>
+        <v>738.6</v>
       </c>
       <c r="K1869" t="n">
         <v>35065.3</v>
@@ -68235,10 +68235,10 @@
         <v>171.4</v>
       </c>
       <c r="I1870" t="n">
-        <v>6456.5</v>
+        <v>9816.700000000001</v>
       </c>
       <c r="J1870" t="n">
-        <v>4098.7</v>
+        <v>738.6</v>
       </c>
       <c r="K1870" t="n">
         <v>34449.1</v>
@@ -68270,10 +68270,10 @@
         <v>97.2</v>
       </c>
       <c r="I1871" t="n">
-        <v>6506.8</v>
+        <v>9867</v>
       </c>
       <c r="J1871" t="n">
-        <v>4110.4</v>
+        <v>750.2</v>
       </c>
       <c r="K1871" t="n">
         <v>35022.1</v>
@@ -68305,10 +68305,10 @@
         <v>196.4</v>
       </c>
       <c r="I1872" t="n">
-        <v>6667.9</v>
+        <v>9798.200000000001</v>
       </c>
       <c r="J1872" t="n">
-        <v>3879.3</v>
+        <v>749</v>
       </c>
       <c r="K1872" t="n">
         <v>34545.8</v>
@@ -68340,10 +68340,10 @@
         <v>882.6</v>
       </c>
       <c r="I1873" t="n">
-        <v>6382.1</v>
+        <v>9740.6</v>
       </c>
       <c r="J1873" t="n">
-        <v>4102.2</v>
+        <v>743.7</v>
       </c>
       <c r="K1873" t="n">
         <v>28831.3</v>
@@ -68375,10 +68375,10 @@
         <v>2329.3</v>
       </c>
       <c r="I1874" t="n">
-        <v>6642</v>
+        <v>9151.1</v>
       </c>
       <c r="J1874" t="n">
-        <v>3238.1</v>
+        <v>729</v>
       </c>
       <c r="K1874" t="n">
         <v>34897.8</v>
@@ -68410,10 +68410,10 @@
         <v>1874.9</v>
       </c>
       <c r="I1875" t="n">
-        <v>6542.9</v>
+        <v>9007</v>
       </c>
       <c r="J1875" t="n">
-        <v>3209.8</v>
+        <v>745.7</v>
       </c>
       <c r="K1875" t="n">
         <v>34429.3</v>
@@ -68445,10 +68445,10 @@
         <v>1557.9</v>
       </c>
       <c r="I1876" t="n">
-        <v>6652.2</v>
+        <v>9998</v>
       </c>
       <c r="J1876" t="n">
-        <v>4094.5</v>
+        <v>748.6</v>
       </c>
       <c r="K1876" t="n">
         <v>35058</v>
@@ -68480,10 +68480,10 @@
         <v>2239.4</v>
       </c>
       <c r="I1877" t="n">
-        <v>6557.1</v>
+        <v>9884.4</v>
       </c>
       <c r="J1877" t="n">
-        <v>4072.4</v>
+        <v>745.1</v>
       </c>
       <c r="K1877" t="n">
         <v>35563</v>
@@ -68515,10 +68515,10 @@
         <v>2991.8</v>
       </c>
       <c r="I1878" t="n">
-        <v>6706.2</v>
+        <v>10078.9</v>
       </c>
       <c r="J1878" t="n">
-        <v>4106.8</v>
+        <v>734.2</v>
       </c>
       <c r="K1878" t="n">
         <v>36756.4</v>
@@ -68550,10 +68550,10 @@
         <v>3005.5</v>
       </c>
       <c r="I1879" t="n">
-        <v>6679.2</v>
+        <v>10047</v>
       </c>
       <c r="J1879" t="n">
-        <v>4086.9</v>
+        <v>719</v>
       </c>
       <c r="K1879" t="n">
         <v>35268.8</v>
@@ -68585,10 +68585,10 @@
         <v>526.9</v>
       </c>
       <c r="I1880" t="n">
-        <v>6507.1</v>
+        <v>9864.1</v>
       </c>
       <c r="J1880" t="n">
-        <v>4069.8</v>
+        <v>712.8</v>
       </c>
       <c r="K1880" t="n">
         <v>31329.3</v>
@@ -68620,10 +68620,10 @@
         <v>525.2</v>
       </c>
       <c r="I1881" t="n">
-        <v>6156.6</v>
+        <v>9404.799999999999</v>
       </c>
       <c r="J1881" t="n">
-        <v>3980.5</v>
+        <v>732.3</v>
       </c>
       <c r="K1881" t="n">
         <v>33931.7</v>
@@ -68655,10 +68655,10 @@
         <v>725.4</v>
       </c>
       <c r="I1882" t="n">
-        <v>5912.4</v>
+        <v>9108</v>
       </c>
       <c r="J1882" t="n">
-        <v>3953.2</v>
+        <v>757.6</v>
       </c>
       <c r="K1882" t="n">
         <v>36216.2</v>
@@ -68690,10 +68690,10 @@
         <v>867.9</v>
       </c>
       <c r="I1883" t="n">
-        <v>6316</v>
+        <v>9731.200000000001</v>
       </c>
       <c r="J1883" t="n">
-        <v>4159.2</v>
+        <v>743.9</v>
       </c>
       <c r="K1883" t="n">
         <v>37655.8</v>
@@ -68725,10 +68725,10 @@
         <v>2634.2</v>
       </c>
       <c r="I1884" t="n">
-        <v>5849.5</v>
+        <v>9181.9</v>
       </c>
       <c r="J1884" t="n">
-        <v>4066.8</v>
+        <v>734.5</v>
       </c>
       <c r="K1884" t="n">
         <v>37711.1</v>
@@ -68760,10 +68760,10 @@
         <v>2629.5</v>
       </c>
       <c r="I1885" t="n">
-        <v>5898.9</v>
+        <v>9257.5</v>
       </c>
       <c r="J1885" t="n">
-        <v>4094.5</v>
+        <v>735.9</v>
       </c>
       <c r="K1885" t="n">
         <v>36814.4</v>
@@ -68795,10 +68795,10 @@
         <v>483.9</v>
       </c>
       <c r="I1886" t="n">
-        <v>6235.7</v>
+        <v>9585.4</v>
       </c>
       <c r="J1886" t="n">
-        <v>4075</v>
+        <v>725.3</v>
       </c>
       <c r="K1886" t="n">
         <v>34148.6</v>
@@ -68830,10 +68830,10 @@
         <v>891.4</v>
       </c>
       <c r="I1887" t="n">
-        <v>6086</v>
+        <v>9377.1</v>
       </c>
       <c r="J1887" t="n">
-        <v>4005</v>
+        <v>713.9</v>
       </c>
       <c r="K1887" t="n">
         <v>30475.8</v>
@@ -68865,10 +68865,10 @@
         <v>1953.9</v>
       </c>
       <c r="I1888" t="n">
-        <v>6221.3</v>
+        <v>9563.9</v>
       </c>
       <c r="J1888" t="n">
-        <v>4061.9</v>
+        <v>719.2</v>
       </c>
       <c r="K1888" t="n">
         <v>35353.6</v>
@@ -68900,10 +68900,10 @@
         <v>3231.1</v>
       </c>
       <c r="I1889" t="n">
-        <v>5127.6</v>
+        <v>8495.5</v>
       </c>
       <c r="J1889" t="n">
-        <v>4077.5</v>
+        <v>709.6</v>
       </c>
       <c r="K1889" t="n">
         <v>37099</v>
@@ -68935,10 +68935,10 @@
         <v>3153.2</v>
       </c>
       <c r="I1890" t="n">
-        <v>6178.4</v>
+        <v>9531.4</v>
       </c>
       <c r="J1890" t="n">
-        <v>4082.5</v>
+        <v>729.5</v>
       </c>
       <c r="K1890" t="n">
         <v>37306</v>
@@ -68970,10 +68970,10 @@
         <v>3212.8</v>
       </c>
       <c r="I1891" t="n">
-        <v>6022.3</v>
+        <v>9387.200000000001</v>
       </c>
       <c r="J1891" t="n">
-        <v>4092.2</v>
+        <v>727.3</v>
       </c>
       <c r="K1891" t="n">
         <v>37401.2</v>
@@ -69005,10 +69005,10 @@
         <v>3214.6</v>
       </c>
       <c r="I1892" t="n">
-        <v>6469.7</v>
+        <v>9843.5</v>
       </c>
       <c r="J1892" t="n">
-        <v>4102</v>
+        <v>728.3</v>
       </c>
       <c r="K1892" t="n">
         <v>38253.4</v>
@@ -69040,10 +69040,10 @@
         <v>3865.8</v>
       </c>
       <c r="I1893" t="n">
-        <v>6588</v>
+        <v>10176.4</v>
       </c>
       <c r="J1893" t="n">
-        <v>4304.3</v>
+        <v>715.9</v>
       </c>
       <c r="K1893" t="n">
         <v>38130.9</v>
@@ -69075,10 +69075,10 @@
         <v>1255.5</v>
       </c>
       <c r="I1894" t="n">
-        <v>6607.2</v>
+        <v>10681.2</v>
       </c>
       <c r="J1894" t="n">
-        <v>4802</v>
+        <v>728</v>
       </c>
       <c r="K1894" t="n">
         <v>32638.5</v>
@@ -69110,10 +69110,10 @@
         <v>2670.3</v>
       </c>
       <c r="I1895" t="n">
-        <v>6288.8</v>
+        <v>10307.5</v>
       </c>
       <c r="J1895" t="n">
-        <v>4740.2</v>
+        <v>721.5</v>
       </c>
       <c r="K1895" t="n">
         <v>37913.3</v>
@@ -69145,10 +69145,10 @@
         <v>2936.5</v>
       </c>
       <c r="I1896" t="n">
-        <v>6504</v>
+        <v>10548.6</v>
       </c>
       <c r="J1896" t="n">
-        <v>4759.8</v>
+        <v>715.2</v>
       </c>
       <c r="K1896" t="n">
         <v>38982.5</v>
@@ -69180,10 +69180,10 @@
         <v>5008.3</v>
       </c>
       <c r="I1897" t="n">
-        <v>6686.2</v>
+        <v>10714.6</v>
       </c>
       <c r="J1897" t="n">
-        <v>4743.8</v>
+        <v>715.4</v>
       </c>
       <c r="K1897" t="n">
         <v>41161.8</v>
@@ -69215,10 +69215,10 @@
         <v>4290.1</v>
       </c>
       <c r="I1898" t="n">
-        <v>6667.8</v>
+        <v>10647</v>
       </c>
       <c r="J1898" t="n">
-        <v>4690</v>
+        <v>710.8</v>
       </c>
       <c r="K1898" t="n">
         <v>40029.7</v>
@@ -69250,10 +69250,10 @@
         <v>3474</v>
       </c>
       <c r="I1899" t="n">
-        <v>6804.1</v>
+        <v>10709.4</v>
       </c>
       <c r="J1899" t="n">
-        <v>4615.2</v>
+        <v>709.9</v>
       </c>
       <c r="K1899" t="n">
         <v>40912.5</v>
@@ -69285,10 +69285,10 @@
         <v>1309.4</v>
       </c>
       <c r="I1900" t="n">
-        <v>6394.3</v>
+        <v>10396.6</v>
       </c>
       <c r="J1900" t="n">
-        <v>4720.5</v>
+        <v>718.2</v>
       </c>
       <c r="K1900" t="n">
         <v>37299.1</v>
@@ -69320,10 +69320,10 @@
         <v>2059.3</v>
       </c>
       <c r="I1901" t="n">
-        <v>5560</v>
+        <v>9460.700000000001</v>
       </c>
       <c r="J1901" t="n">
-        <v>4620.4</v>
+        <v>719.7</v>
       </c>
       <c r="K1901" t="n">
         <v>35601.4</v>
@@ -69355,10 +69355,10 @@
         <v>4056.3</v>
       </c>
       <c r="I1902" t="n">
-        <v>6894.9</v>
+        <v>10901.6</v>
       </c>
       <c r="J1902" t="n">
-        <v>4725.6</v>
+        <v>718.9</v>
       </c>
       <c r="K1902" t="n">
         <v>40746.6</v>
@@ -69390,10 +69390,10 @@
         <v>3144.1</v>
       </c>
       <c r="I1903" t="n">
-        <v>7113.3</v>
+        <v>10993.9</v>
       </c>
       <c r="J1903" t="n">
-        <v>4624.9</v>
+        <v>744.3</v>
       </c>
       <c r="K1903" t="n">
         <v>40215.8</v>
@@ -69425,10 +69425,10 @@
         <v>1113.8</v>
       </c>
       <c r="I1904" t="n">
-        <v>6648.9</v>
+        <v>9543.1</v>
       </c>
       <c r="J1904" t="n">
-        <v>3628.3</v>
+        <v>734.2</v>
       </c>
       <c r="K1904" t="n">
         <v>39137.3</v>
@@ -69460,10 +69460,10 @@
         <v>1292.5</v>
       </c>
       <c r="I1905" t="n">
-        <v>6675.7</v>
+        <v>9579.200000000001</v>
       </c>
       <c r="J1905" t="n">
-        <v>3636.8</v>
+        <v>733.4</v>
       </c>
       <c r="K1905" t="n">
         <v>40009.2</v>
@@ -69495,10 +69495,10 @@
         <v>750.3</v>
       </c>
       <c r="I1906" t="n">
-        <v>5652.4</v>
+        <v>8529.5</v>
       </c>
       <c r="J1906" t="n">
-        <v>3610</v>
+        <v>732.8</v>
       </c>
       <c r="K1906" t="n">
         <v>39722.9</v>
@@ -69530,10 +69530,10 @@
         <v>295.3</v>
       </c>
       <c r="I1907" t="n">
-        <v>6290.6</v>
+        <v>10007.3</v>
       </c>
       <c r="J1907" t="n">
-        <v>4446.8</v>
+        <v>730.1</v>
       </c>
       <c r="K1907" t="n">
         <v>37161.1</v>
@@ -69565,10 +69565,10 @@
         <v>40.8</v>
       </c>
       <c r="I1908" t="n">
-        <v>7005.7</v>
+        <v>10122.7</v>
       </c>
       <c r="J1908" t="n">
-        <v>3854.1</v>
+        <v>737.1</v>
       </c>
       <c r="K1908" t="n">
         <v>33699</v>
@@ -69600,10 +69600,10 @@
         <v>1249.4</v>
       </c>
       <c r="I1909" t="n">
-        <v>7236.1</v>
+        <v>10156.5</v>
       </c>
       <c r="J1909" t="n">
-        <v>3657.5</v>
+        <v>737.1</v>
       </c>
       <c r="K1909" t="n">
         <v>38577.7</v>
@@ -69635,10 +69635,10 @@
         <v>1197.7</v>
       </c>
       <c r="I1910" t="n">
-        <v>6574.4</v>
+        <v>10136</v>
       </c>
       <c r="J1910" t="n">
-        <v>4290.2</v>
+        <v>728.5</v>
       </c>
       <c r="K1910" t="n">
         <v>40117</v>
@@ -69670,10 +69670,10 @@
         <v>1533.5</v>
       </c>
       <c r="I1911" t="n">
-        <v>6430.8</v>
+        <v>10466.4</v>
       </c>
       <c r="J1911" t="n">
-        <v>4763.4</v>
+        <v>727.9</v>
       </c>
       <c r="K1911" t="n">
         <v>40809.4</v>
@@ -69705,10 +69705,10 @@
         <v>1086.5</v>
       </c>
       <c r="I1912" t="n">
-        <v>7120.4</v>
+        <v>11161.6</v>
       </c>
       <c r="J1912" t="n">
-        <v>4766.5</v>
+        <v>725.3</v>
       </c>
       <c r="K1912" t="n">
         <v>40433</v>
@@ -69740,10 +69740,10 @@
         <v>1713.8</v>
       </c>
       <c r="I1913" t="n">
-        <v>7236.5</v>
+        <v>11266.9</v>
       </c>
       <c r="J1913" t="n">
-        <v>4752.9</v>
+        <v>722.5</v>
       </c>
       <c r="K1913" t="n">
         <v>39872.4</v>
@@ -69775,10 +69775,10 @@
         <v>229</v>
       </c>
       <c r="I1914" t="n">
-        <v>6887.1</v>
+        <v>10927.6</v>
       </c>
       <c r="J1914" t="n">
-        <v>4751</v>
+        <v>710.6</v>
       </c>
       <c r="K1914" t="n">
         <v>36464</v>
@@ -69810,10 +69810,10 @@
         <v>146.2</v>
       </c>
       <c r="I1915" t="n">
-        <v>5952</v>
+        <v>9672.4</v>
       </c>
       <c r="J1915" t="n">
-        <v>4427.5</v>
+        <v>707</v>
       </c>
       <c r="K1915" t="n">
         <v>33900.6</v>
@@ -69845,10 +69845,10 @@
         <v>558.6</v>
       </c>
       <c r="I1916" t="n">
-        <v>6417.4</v>
+        <v>10446.4</v>
       </c>
       <c r="J1916" t="n">
-        <v>4743.2</v>
+        <v>714.1</v>
       </c>
       <c r="K1916" t="n">
         <v>38341</v>
@@ -69880,10 +69880,10 @@
         <v>513.7</v>
       </c>
       <c r="I1917" t="n">
-        <v>6861.2</v>
+        <v>10918.5</v>
       </c>
       <c r="J1917" t="n">
-        <v>4778.2</v>
+        <v>721</v>
       </c>
       <c r="K1917" t="n">
         <v>37649.1</v>
@@ -69915,10 +69915,10 @@
         <v>53</v>
       </c>
       <c r="I1918" t="n">
-        <v>7347.1</v>
+        <v>11377.4</v>
       </c>
       <c r="J1918" t="n">
-        <v>4756.2</v>
+        <v>726</v>
       </c>
       <c r="K1918" t="n">
         <v>35674</v>
@@ -69950,10 +69950,10 @@
         <v>76.8</v>
       </c>
       <c r="I1919" t="n">
-        <v>7145</v>
+        <v>10937</v>
       </c>
       <c r="J1919" t="n">
-        <v>4514.1</v>
+        <v>722.1</v>
       </c>
       <c r="K1919" t="n">
         <v>33532.6</v>
@@ -69985,10 +69985,10 @@
         <v>0</v>
       </c>
       <c r="I1920" t="n">
-        <v>7447.1</v>
+        <v>11495.8</v>
       </c>
       <c r="J1920" t="n">
-        <v>4759.3</v>
+        <v>710.6</v>
       </c>
       <c r="K1920" t="n">
         <v>31897.8</v>
@@ -70020,10 +70020,10 @@
         <v>112.8</v>
       </c>
       <c r="I1921" t="n">
-        <v>6910.8</v>
+        <v>10894.8</v>
       </c>
       <c r="J1921" t="n">
-        <v>4698.6</v>
+        <v>714.6</v>
       </c>
       <c r="K1921" t="n">
         <v>32312.2</v>
@@ -70055,10 +70055,10 @@
         <v>611.3</v>
       </c>
       <c r="I1922" t="n">
-        <v>6574.1</v>
+        <v>10457.4</v>
       </c>
       <c r="J1922" t="n">
-        <v>4589.6</v>
+        <v>706.2</v>
       </c>
       <c r="K1922" t="n">
         <v>32089.6</v>
@@ -70090,10 +70090,10 @@
         <v>1151.7</v>
       </c>
       <c r="I1923" t="n">
-        <v>6380.4</v>
+        <v>10419.1</v>
       </c>
       <c r="J1923" t="n">
-        <v>4748.8</v>
+        <v>710.2</v>
       </c>
       <c r="K1923" t="n">
         <v>37942.6</v>
@@ -70125,10 +70125,10 @@
         <v>557.7</v>
       </c>
       <c r="I1924" t="n">
-        <v>7340.6</v>
+        <v>11307.7</v>
       </c>
       <c r="J1924" t="n">
-        <v>4673.1</v>
+        <v>706.1</v>
       </c>
       <c r="K1924" t="n">
         <v>40933.5</v>
@@ -70160,10 +70160,10 @@
         <v>1328.6</v>
       </c>
       <c r="I1925" t="n">
-        <v>7103.3</v>
+        <v>11105.5</v>
       </c>
       <c r="J1925" t="n">
-        <v>4708.1</v>
+        <v>705.9</v>
       </c>
       <c r="K1925" t="n">
         <v>42103.2</v>
@@ -70195,10 +70195,10 @@
         <v>732.4</v>
       </c>
       <c r="I1926" t="n">
-        <v>6491.9</v>
+        <v>10518.2</v>
       </c>
       <c r="J1926" t="n">
-        <v>4719.6</v>
+        <v>693.3</v>
       </c>
       <c r="K1926" t="n">
         <v>42417.1</v>
@@ -70230,10 +70230,10 @@
         <v>1422</v>
       </c>
       <c r="I1927" t="n">
-        <v>6183.3</v>
+        <v>10134</v>
       </c>
       <c r="J1927" t="n">
-        <v>4615</v>
+        <v>664.3</v>
       </c>
       <c r="K1927" t="n">
         <v>42152.2</v>
@@ -70265,10 +70265,10 @@
         <v>317</v>
       </c>
       <c r="I1928" t="n">
-        <v>6368</v>
+        <v>10393.5</v>
       </c>
       <c r="J1928" t="n">
-        <v>4715.4</v>
+        <v>689.9</v>
       </c>
       <c r="K1928" t="n">
         <v>38949.6</v>
@@ -70300,10 +70300,10 @@
         <v>535</v>
       </c>
       <c r="I1929" t="n">
-        <v>6474.1</v>
+        <v>10442.6</v>
       </c>
       <c r="J1929" t="n">
-        <v>4664.5</v>
+        <v>696</v>
       </c>
       <c r="K1929" t="n">
         <v>35595.5</v>
@@ -70335,10 +70335,10 @@
         <v>1319.6</v>
       </c>
       <c r="I1930" t="n">
-        <v>7150.1</v>
+        <v>11173.1</v>
       </c>
       <c r="J1930" t="n">
-        <v>4724.7</v>
+        <v>701.6</v>
       </c>
       <c r="K1930" t="n">
         <v>39060.9</v>
@@ -70370,10 +70370,10 @@
         <v>2088.7</v>
       </c>
       <c r="I1931" t="n">
-        <v>6495.4</v>
+        <v>10476.3</v>
       </c>
       <c r="J1931" t="n">
-        <v>4688.1</v>
+        <v>707.2</v>
       </c>
       <c r="K1931" t="n">
         <v>40454.4</v>
@@ -70405,10 +70405,10 @@
         <v>1909.2</v>
       </c>
       <c r="I1932" t="n">
-        <v>6956.9</v>
+        <v>10966.2</v>
       </c>
       <c r="J1932" t="n">
-        <v>4721.5</v>
+        <v>712.2</v>
       </c>
       <c r="K1932" t="n">
         <v>41401.8</v>
@@ -70440,10 +70440,10 @@
         <v>1859.6</v>
       </c>
       <c r="I1933" t="n">
-        <v>7237.2</v>
+        <v>11259.5</v>
       </c>
       <c r="J1933" t="n">
-        <v>4735.8</v>
+        <v>713.4</v>
       </c>
       <c r="K1933" t="n">
         <v>41735.4</v>
@@ -70475,10 +70475,10 @@
         <v>3072.9</v>
       </c>
       <c r="I1934" t="n">
-        <v>7349</v>
+        <v>11379.1</v>
       </c>
       <c r="J1934" t="n">
-        <v>4751.1</v>
+        <v>721</v>
       </c>
       <c r="K1934" t="n">
         <v>42632.5</v>
@@ -70510,10 +70510,10 @@
         <v>2545.8</v>
       </c>
       <c r="I1935" t="n">
-        <v>7435.2</v>
+        <v>11458.1</v>
       </c>
       <c r="J1935" t="n">
-        <v>4745</v>
+        <v>722</v>
       </c>
       <c r="K1935" t="n">
         <v>40134.4</v>
@@ -70545,10 +70545,10 @@
         <v>2482</v>
       </c>
       <c r="I1936" t="n">
-        <v>7179.4</v>
+        <v>11189.7</v>
       </c>
       <c r="J1936" t="n">
-        <v>4389.1</v>
+        <v>378.9</v>
       </c>
       <c r="K1936" t="n">
         <v>37465.3</v>
@@ -70580,10 +70580,10 @@
         <v>3461.8</v>
       </c>
       <c r="I1937" t="n">
-        <v>7368.3</v>
+        <v>11363.6</v>
       </c>
       <c r="J1937" t="n">
-        <v>4355.7</v>
+        <v>360.4</v>
       </c>
       <c r="K1937" t="n">
         <v>41478.5</v>
@@ -70615,10 +70615,10 @@
         <v>4665.7</v>
       </c>
       <c r="I1938" t="n">
-        <v>6734.2</v>
+        <v>10349.8</v>
       </c>
       <c r="J1938" t="n">
-        <v>3975.8</v>
+        <v>360.2</v>
       </c>
       <c r="K1938" t="n">
         <v>42712.5</v>
@@ -70650,10 +70650,10 @@
         <v>6465</v>
       </c>
       <c r="I1939" t="n">
-        <v>6476.9</v>
+        <v>9273.9</v>
       </c>
       <c r="J1939" t="n">
-        <v>3234.9</v>
+        <v>437.9</v>
       </c>
       <c r="K1939" t="n">
         <v>42971.5</v>
@@ -70685,10 +70685,10 @@
         <v>5269.4</v>
       </c>
       <c r="I1940" t="n">
-        <v>6103.8</v>
+        <v>9726.299999999999</v>
       </c>
       <c r="J1940" t="n">
-        <v>4233.4</v>
+        <v>610.9</v>
       </c>
       <c r="K1940" t="n">
         <v>42237.1</v>
@@ -70720,10 +70720,10 @@
         <v>3308.2</v>
       </c>
       <c r="I1941" t="n">
-        <v>5774</v>
+        <v>9518</v>
       </c>
       <c r="J1941" t="n">
-        <v>4487.9</v>
+        <v>744</v>
       </c>
       <c r="K1941" t="n">
         <v>40730.2</v>
@@ -70755,10 +70755,10 @@
         <v>5350.6</v>
       </c>
       <c r="I1942" t="n">
-        <v>6247.8</v>
+        <v>10154.8</v>
       </c>
       <c r="J1942" t="n">
-        <v>4636.7</v>
+        <v>729.8</v>
       </c>
       <c r="K1942" t="n">
         <v>40110.2</v>
@@ -70790,10 +70790,10 @@
         <v>5716.4</v>
       </c>
       <c r="I1943" t="n">
-        <v>6178.7</v>
+        <v>10111.9</v>
       </c>
       <c r="J1943" t="n">
-        <v>4657.3</v>
+        <v>724.1</v>
       </c>
       <c r="K1943" t="n">
         <v>36624.8</v>
@@ -70825,10 +70825,10 @@
         <v>7882.8</v>
       </c>
       <c r="I1944" t="n">
-        <v>5945.8</v>
+        <v>9868.9</v>
       </c>
       <c r="J1944" t="n">
-        <v>4639.1</v>
+        <v>716.1</v>
       </c>
       <c r="K1944" t="n">
         <v>40799.5</v>
@@ -70860,10 +70860,10 @@
         <v>7541.5</v>
       </c>
       <c r="I1945" t="n">
-        <v>6266.6</v>
+        <v>10151.3</v>
       </c>
       <c r="J1945" t="n">
-        <v>4609.9</v>
+        <v>725.2</v>
       </c>
       <c r="K1945" t="n">
         <v>41000.7</v>
@@ -70895,10 +70895,10 @@
         <v>4113.9</v>
       </c>
       <c r="I1946" t="n">
-        <v>6958.2</v>
+        <v>10862</v>
       </c>
       <c r="J1946" t="n">
-        <v>4630.3</v>
+        <v>726.6</v>
       </c>
       <c r="K1946" t="n">
         <v>37793.6</v>
@@ -70930,10 +70930,10 @@
         <v>4677.8</v>
       </c>
       <c r="I1947" t="n">
-        <v>7074.8</v>
+        <v>10998.4</v>
       </c>
       <c r="J1947" t="n">
-        <v>4677</v>
+        <v>753.4</v>
       </c>
       <c r="K1947" t="n">
         <v>38739.1</v>
@@ -70965,10 +70965,10 @@
         <v>8118.4</v>
       </c>
       <c r="I1948" t="n">
-        <v>1477.6</v>
+        <v>2708.8</v>
       </c>
       <c r="J1948" t="n">
-        <v>1968.2</v>
+        <v>737</v>
       </c>
       <c r="K1948" t="n">
         <v>37524.8</v>
@@ -71000,10 +71000,10 @@
         <v>6903.6</v>
       </c>
       <c r="I1949" t="n">
-        <v>1454.8</v>
+        <v>2699.2</v>
       </c>
       <c r="J1949" t="n">
-        <v>1975.4</v>
+        <v>731</v>
       </c>
       <c r="K1949" t="n">
         <v>36956.7</v>
@@ -71035,10 +71035,10 @@
         <v>6605.8</v>
       </c>
       <c r="I1950" t="n">
-        <v>1236.8</v>
+        <v>2463</v>
       </c>
       <c r="J1950" t="n">
-        <v>1953.8</v>
+        <v>727.6</v>
       </c>
       <c r="K1950" t="n">
         <v>33586.5</v>
@@ -71070,10 +71070,10 @@
         <v>7094.5</v>
       </c>
       <c r="I1951" t="n">
-        <v>1296</v>
+        <v>2520</v>
       </c>
       <c r="J1951" t="n">
-        <v>1963.1</v>
+        <v>739.1</v>
       </c>
       <c r="K1951" t="n">
         <v>37610.4</v>
@@ -71105,10 +71105,10 @@
         <v>8582.6</v>
       </c>
       <c r="I1952" t="n">
-        <v>1415.3</v>
+        <v>2653.1</v>
       </c>
       <c r="J1952" t="n">
-        <v>1977.9</v>
+        <v>740.1</v>
       </c>
       <c r="K1952" t="n">
         <v>38627.5</v>
@@ -71140,10 +71140,10 @@
         <v>10145.6</v>
       </c>
       <c r="I1953" t="n">
-        <v>1411.4</v>
+        <v>2635.4</v>
       </c>
       <c r="J1953" t="n">
-        <v>1965</v>
+        <v>741</v>
       </c>
       <c r="K1953" t="n">
         <v>39067</v>
@@ -71175,10 +71175,10 @@
         <v>8788.5</v>
       </c>
       <c r="I1954" t="n">
-        <v>1428.2</v>
+        <v>2626.8</v>
       </c>
       <c r="J1954" t="n">
-        <v>1931.2</v>
+        <v>732.7</v>
       </c>
       <c r="K1954" t="n">
         <v>39306.8</v>
@@ -71210,10 +71210,10 @@
         <v>9532.1</v>
       </c>
       <c r="I1955" t="n">
-        <v>1377.5</v>
+        <v>2598</v>
       </c>
       <c r="J1955" t="n">
-        <v>1951.5</v>
+        <v>731</v>
       </c>
       <c r="K1955" t="n">
         <v>39665.2</v>
@@ -71245,10 +71245,10 @@
         <v>9146.299999999999</v>
       </c>
       <c r="I1956" t="n">
-        <v>1430.2</v>
+        <v>2644.7</v>
       </c>
       <c r="J1956" t="n">
-        <v>1962.6</v>
+        <v>748.1</v>
       </c>
       <c r="K1956" t="n">
         <v>38431.7</v>
@@ -71280,10 +71280,10 @@
         <v>7410.9</v>
       </c>
       <c r="I1957" t="n">
-        <v>1306.8</v>
+        <v>2526.9</v>
       </c>
       <c r="J1957" t="n">
-        <v>1947.6</v>
+        <v>727.5</v>
       </c>
       <c r="K1957" t="n">
         <v>32882.8</v>
@@ -71315,10 +71315,10 @@
         <v>9608.5</v>
       </c>
       <c r="I1958" t="n">
-        <v>1421.6</v>
+        <v>2659.7</v>
       </c>
       <c r="J1958" t="n">
-        <v>1969.7</v>
+        <v>731.6</v>
       </c>
       <c r="K1958" t="n">
         <v>38141.8</v>
@@ -71350,10 +71350,10 @@
         <v>10250.6</v>
       </c>
       <c r="I1959" t="n">
-        <v>1436.4</v>
+        <v>2659.8</v>
       </c>
       <c r="J1959" t="n">
-        <v>1951</v>
+        <v>727.7</v>
       </c>
       <c r="K1959" t="n">
         <v>38656.6</v>
@@ -71385,10 +71385,10 @@
         <v>9075.9</v>
       </c>
       <c r="I1960" t="n">
-        <v>1321</v>
+        <v>2514.2</v>
       </c>
       <c r="J1960" t="n">
-        <v>1915</v>
+        <v>721.8</v>
       </c>
       <c r="K1960" t="n">
         <v>38329.1</v>
@@ -71420,10 +71420,10 @@
         <v>7249.2</v>
       </c>
       <c r="I1961" t="n">
-        <v>1654.5</v>
+        <v>2864.5</v>
       </c>
       <c r="J1961" t="n">
-        <v>1938.3</v>
+        <v>728.3</v>
       </c>
       <c r="K1961" t="n">
         <v>38068.7</v>
@@ -71455,10 +71455,10 @@
         <v>6800.5</v>
       </c>
       <c r="I1962" t="n">
-        <v>1504.2</v>
+        <v>2688.2</v>
       </c>
       <c r="J1962" t="n">
-        <v>1912.5</v>
+        <v>728.5</v>
       </c>
       <c r="K1962" t="n">
         <v>38188</v>
@@ -71490,10 +71490,10 @@
         <v>5680.9</v>
       </c>
       <c r="I1963" t="n">
-        <v>1406.2</v>
+        <v>2616.4</v>
       </c>
       <c r="J1963" t="n">
-        <v>1938.2</v>
+        <v>728</v>
       </c>
       <c r="K1963" t="n">
         <v>35905.6</v>
@@ -71525,10 +71525,10 @@
         <v>6619.2</v>
       </c>
       <c r="I1964" t="n">
-        <v>1190.2</v>
+        <v>2412.9</v>
       </c>
       <c r="J1964" t="n">
-        <v>1951.2</v>
+        <v>728.5</v>
       </c>
       <c r="K1964" t="n">
         <v>32372.1</v>
@@ -71560,10 +71560,10 @@
         <v>8412.9</v>
       </c>
       <c r="I1965" t="n">
-        <v>1242.2</v>
+        <v>2429.7</v>
       </c>
       <c r="J1965" t="n">
-        <v>1906.5</v>
+        <v>719</v>
       </c>
       <c r="K1965" t="n">
         <v>38296.5</v>
@@ -71595,10 +71595,10 @@
         <v>9987.6</v>
       </c>
       <c r="I1966" t="n">
-        <v>1338.1</v>
+        <v>2521.1</v>
       </c>
       <c r="J1966" t="n">
-        <v>1900.5</v>
+        <v>717.4</v>
       </c>
       <c r="K1966" t="n">
         <v>40748.4</v>
@@ -71630,10 +71630,10 @@
         <v>9918.4</v>
       </c>
       <c r="I1967" t="n">
-        <v>1345.5</v>
+        <v>2440.9</v>
       </c>
       <c r="J1967" t="n">
-        <v>1820.2</v>
+        <v>724.8</v>
       </c>
       <c r="K1967" t="n">
         <v>40800.8</v>
@@ -71665,10 +71665,10 @@
         <v>8275</v>
       </c>
       <c r="I1968" t="n">
-        <v>1274.5</v>
+        <v>2263.7</v>
       </c>
       <c r="J1968" t="n">
-        <v>1715.3</v>
+        <v>726.2</v>
       </c>
       <c r="K1968" t="n">
         <v>39702.1</v>
@@ -71700,10 +71700,10 @@
         <v>8615.1</v>
       </c>
       <c r="I1969" t="n">
-        <v>1234.9</v>
+        <v>2286.9</v>
       </c>
       <c r="J1969" t="n">
-        <v>1781.4</v>
+        <v>729.4</v>
       </c>
       <c r="K1969" t="n">
         <v>39672.1</v>
@@ -71735,10 +71735,10 @@
         <v>7814.1</v>
       </c>
       <c r="I1970" t="n">
-        <v>1343.6</v>
+        <v>2396.6</v>
       </c>
       <c r="J1970" t="n">
-        <v>1779.4</v>
+        <v>726.5</v>
       </c>
       <c r="K1970" t="n">
         <v>37874.1</v>
@@ -71770,10 +71770,10 @@
         <v>8232.1</v>
       </c>
       <c r="I1971" t="n">
-        <v>1196.6</v>
+        <v>2224.5</v>
       </c>
       <c r="J1971" t="n">
-        <v>1750.1</v>
+        <v>722.1</v>
       </c>
       <c r="K1971" t="n">
         <v>33367.4</v>
@@ -71805,10 +71805,10 @@
         <v>8583</v>
       </c>
       <c r="I1972" t="n">
-        <v>1213.4</v>
+        <v>2306.9</v>
       </c>
       <c r="J1972" t="n">
-        <v>1829.4</v>
+        <v>735.9</v>
       </c>
       <c r="K1972" t="n">
         <v>37666.2</v>
@@ -71840,10 +71840,10 @@
         <v>7808.7</v>
       </c>
       <c r="I1973" t="n">
-        <v>1205.7</v>
+        <v>2342.9</v>
       </c>
       <c r="J1973" t="n">
-        <v>1854.4</v>
+        <v>717.1</v>
       </c>
       <c r="K1973" t="n">
         <v>39811.2</v>
@@ -71875,10 +71875,10 @@
         <v>7210.3</v>
       </c>
       <c r="I1974" t="n">
-        <v>1157.5</v>
+        <v>2211.7</v>
       </c>
       <c r="J1974" t="n">
-        <v>1795.6</v>
+        <v>741.3</v>
       </c>
       <c r="K1974" t="n">
         <v>39218.7</v>
@@ -71910,10 +71910,10 @@
         <v>4803.7</v>
       </c>
       <c r="I1975" t="n">
-        <v>1352.8</v>
+        <v>2488.2</v>
       </c>
       <c r="J1975" t="n">
-        <v>1873.8</v>
+        <v>738.5</v>
       </c>
       <c r="K1975" t="n">
         <v>39005</v>
@@ -71945,10 +71945,10 @@
         <v>4345.2</v>
       </c>
       <c r="I1976" t="n">
-        <v>1120</v>
+        <v>2166.3</v>
       </c>
       <c r="J1976" t="n">
-        <v>1803.2</v>
+        <v>756.8</v>
       </c>
       <c r="K1976" t="n">
         <v>37086.7</v>
@@ -71980,10 +71980,10 @@
         <v>3012.8</v>
       </c>
       <c r="I1977" t="n">
-        <v>905.4</v>
+        <v>2204.2</v>
       </c>
       <c r="J1977" t="n">
-        <v>2047.9</v>
+        <v>749.1</v>
       </c>
       <c r="K1977" t="n">
         <v>34510.9</v>
@@ -72015,10 +72015,10 @@
         <v>4198.6</v>
       </c>
       <c r="I1978" t="n">
-        <v>902.9</v>
+        <v>2476.6</v>
       </c>
       <c r="J1978" t="n">
-        <v>2314.1</v>
+        <v>740.4</v>
       </c>
       <c r="K1978" t="n">
         <v>31437.3</v>
@@ -76305,7 +76305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M69"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76377,2789 +76377,821 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>44197</v>
+        <v>45658</v>
       </c>
       <c r="B2" t="n">
-        <v>22.011</v>
+        <v>21.97</v>
       </c>
       <c r="C2" t="n">
-        <v>44.174</v>
+        <v>48.999</v>
       </c>
       <c r="D2" t="n">
-        <v>20.063</v>
+        <v>29.888</v>
       </c>
       <c r="E2" t="n">
-        <v>445.687</v>
+        <v>462.057</v>
       </c>
       <c r="F2" t="n">
-        <v>2.58</v>
+        <v>1.741</v>
       </c>
       <c r="G2" t="n">
-        <v>311.144</v>
+        <v>309.857</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.41</v>
+        <v>6.563</v>
       </c>
       <c r="J2" t="n">
-        <v>95.2</v>
+        <v>82.547</v>
       </c>
       <c r="K2" t="n">
-        <v>9.446999999999999</v>
+        <v>94.58199999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>13.916</v>
+        <v>13.332</v>
       </c>
       <c r="M2" t="n">
-        <v>0.048</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>44228</v>
+        <v>45689</v>
       </c>
       <c r="B3" t="n">
-        <v>20.555</v>
+        <v>21.72</v>
       </c>
       <c r="C3" t="n">
-        <v>27.037</v>
+        <v>34.754</v>
       </c>
       <c r="D3" t="n">
-        <v>19.518</v>
+        <v>33.385</v>
       </c>
       <c r="E3" t="n">
-        <v>333.286</v>
+        <v>337.905</v>
       </c>
       <c r="F3" t="n">
-        <v>2.364</v>
+        <v>1.525</v>
       </c>
       <c r="G3" t="n">
-        <v>292.601</v>
+        <v>272.134</v>
       </c>
       <c r="H3" t="n">
-        <v>0.034</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1.162</v>
+        <v>7.177</v>
       </c>
       <c r="J3" t="n">
-        <v>194.663</v>
+        <v>130.177</v>
       </c>
       <c r="K3" t="n">
-        <v>32.985</v>
+        <v>132.811</v>
       </c>
       <c r="L3" t="n">
-        <v>35.029</v>
+        <v>18.397</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>44256</v>
+        <v>45717</v>
       </c>
       <c r="B4" t="n">
-        <v>22.957</v>
+        <v>23.534</v>
       </c>
       <c r="C4" t="n">
-        <v>36.509</v>
+        <v>24.771</v>
       </c>
       <c r="D4" t="n">
-        <v>22.659</v>
+        <v>41.246</v>
       </c>
       <c r="E4" t="n">
-        <v>336.139</v>
+        <v>331.408</v>
       </c>
       <c r="F4" t="n">
-        <v>2.271</v>
+        <v>1.57</v>
       </c>
       <c r="G4" t="n">
-        <v>312.942</v>
+        <v>303.23</v>
       </c>
       <c r="H4" t="n">
-        <v>0.024</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1.274</v>
+        <v>8.103</v>
       </c>
       <c r="J4" t="n">
-        <v>249.303</v>
+        <v>223.594</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>158.181</v>
       </c>
       <c r="L4" t="n">
-        <v>26.1</v>
+        <v>65.411</v>
       </c>
       <c r="M4" t="n">
-        <v>0.254</v>
+        <v>0.314</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>44287</v>
+        <v>45748</v>
       </c>
       <c r="B5" t="n">
-        <v>21.464</v>
+        <v>22.586</v>
       </c>
       <c r="C5" t="n">
-        <v>18.913</v>
+        <v>29.27</v>
       </c>
       <c r="D5" t="n">
-        <v>19.332</v>
+        <v>41.448</v>
       </c>
       <c r="E5" t="n">
-        <v>333.449</v>
+        <v>298.094</v>
       </c>
       <c r="F5" t="n">
-        <v>2.343</v>
+        <v>1.433</v>
       </c>
       <c r="G5" t="n">
-        <v>290.407</v>
+        <v>264.249</v>
       </c>
       <c r="H5" t="n">
-        <v>0.019</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1.349</v>
+        <v>8.039</v>
       </c>
       <c r="J5" t="n">
-        <v>241.298</v>
+        <v>226.874</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>153.058</v>
       </c>
       <c r="L5" t="n">
-        <v>23.566</v>
+        <v>81.60899999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>0.131</v>
+        <v>3.069</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>44317</v>
+        <v>45778</v>
       </c>
       <c r="B6" t="n">
-        <v>22.49</v>
+        <v>22.903</v>
       </c>
       <c r="C6" t="n">
-        <v>18.383</v>
+        <v>10.256</v>
       </c>
       <c r="D6" t="n">
-        <v>17.894</v>
+        <v>39.64</v>
       </c>
       <c r="E6" t="n">
-        <v>438.406</v>
+        <v>275.326</v>
       </c>
       <c r="F6" t="n">
-        <v>2.628</v>
+        <v>1.492</v>
       </c>
       <c r="G6" t="n">
-        <v>68.462</v>
+        <v>150.926</v>
       </c>
       <c r="H6" t="n">
-        <v>0.081</v>
+        <v>0.007</v>
       </c>
       <c r="I6" t="n">
-        <v>1.425</v>
+        <v>8.159000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>396.481</v>
+        <v>360.372</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>159.684</v>
       </c>
       <c r="L6" t="n">
-        <v>16.895</v>
+        <v>106.196</v>
       </c>
       <c r="M6" t="n">
-        <v>0.018</v>
+        <v>1.955</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>44348</v>
+        <v>45809</v>
       </c>
       <c r="B7" t="n">
-        <v>20.233</v>
+        <v>21.89</v>
       </c>
       <c r="C7" t="n">
-        <v>5.028</v>
+        <v>13.741</v>
       </c>
       <c r="D7" t="n">
-        <v>16.803</v>
+        <v>34.942</v>
       </c>
       <c r="E7" t="n">
-        <v>491.214</v>
+        <v>470.748</v>
       </c>
       <c r="F7" t="n">
-        <v>2.502</v>
+        <v>1.973</v>
       </c>
       <c r="G7" t="n">
-        <v>0.333</v>
+        <v>31.635</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="I7" t="n">
-        <v>0.925</v>
+        <v>7.452</v>
       </c>
       <c r="J7" t="n">
-        <v>410.12</v>
+        <v>300.557</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>135.612</v>
       </c>
       <c r="L7" t="n">
-        <v>26.382</v>
+        <v>39.842</v>
       </c>
       <c r="M7" t="n">
-        <v>0.014</v>
+        <v>0.284</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>44378</v>
+        <v>45839</v>
       </c>
       <c r="B8" t="n">
-        <v>22.581</v>
+        <v>23.257</v>
       </c>
       <c r="C8" t="n">
-        <v>32.216</v>
+        <v>38.201</v>
       </c>
       <c r="D8" t="n">
-        <v>19.926</v>
+        <v>44.005</v>
       </c>
       <c r="E8" t="n">
-        <v>645.341</v>
+        <v>480.194</v>
       </c>
       <c r="F8" t="n">
-        <v>2.37</v>
+        <v>1.871</v>
       </c>
       <c r="G8" t="n">
-        <v>0.391</v>
+        <v>5.241</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.446</v>
+        <v>8.198</v>
       </c>
       <c r="J8" t="n">
-        <v>244.067</v>
+        <v>282.769</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>153.438</v>
       </c>
       <c r="L8" t="n">
-        <v>30.855</v>
+        <v>49.87</v>
       </c>
       <c r="M8" t="n">
-        <v>0.452</v>
+        <v>0.627</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>44409</v>
+        <v>45870</v>
       </c>
       <c r="B9" t="n">
-        <v>22.419</v>
+        <v>23.108</v>
       </c>
       <c r="C9" t="n">
-        <v>15.392</v>
+        <v>22.445</v>
       </c>
       <c r="D9" t="n">
-        <v>17.837</v>
+        <v>48.6</v>
       </c>
       <c r="E9" t="n">
-        <v>693.437</v>
+        <v>432.895</v>
       </c>
       <c r="F9" t="n">
-        <v>2.17</v>
+        <v>1.95</v>
       </c>
       <c r="G9" t="n">
-        <v>0.355</v>
+        <v>0.352</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>1.301</v>
+        <v>8.843999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>240.735</v>
+        <v>378.223</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>153.711</v>
       </c>
       <c r="L9" t="n">
-        <v>8.974</v>
+        <v>50.641</v>
       </c>
       <c r="M9" t="n">
-        <v>0.106</v>
+        <v>0.427</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>44440</v>
+        <v>45901</v>
       </c>
       <c r="B10" t="n">
-        <v>22.098</v>
+        <v>22.695</v>
       </c>
       <c r="C10" t="n">
-        <v>10.063</v>
+        <v>9.087</v>
       </c>
       <c r="D10" t="n">
-        <v>18.122</v>
+        <v>47.886</v>
       </c>
       <c r="E10" t="n">
-        <v>777.482</v>
+        <v>613.097</v>
       </c>
       <c r="F10" t="n">
-        <v>1.724</v>
+        <v>1.935</v>
       </c>
       <c r="G10" t="n">
-        <v>0.369</v>
+        <v>0.375</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0.977</v>
+        <v>8.035</v>
       </c>
       <c r="J10" t="n">
-        <v>162.768</v>
+        <v>256.552</v>
       </c>
       <c r="K10" t="n">
-        <v>0.064</v>
+        <v>119.114</v>
       </c>
       <c r="L10" t="n">
-        <v>17.079</v>
+        <v>48.85</v>
       </c>
       <c r="M10" t="n">
-        <v>0.197</v>
+        <v>0.134</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>44470</v>
+        <v>45931</v>
       </c>
       <c r="B11" t="n">
-        <v>23.03</v>
+        <v>22.926</v>
       </c>
       <c r="C11" t="n">
-        <v>17.125</v>
+        <v>20.103</v>
       </c>
       <c r="D11" t="n">
-        <v>17.816</v>
+        <v>51.515</v>
       </c>
       <c r="E11" t="n">
-        <v>586.974</v>
+        <v>768.662</v>
       </c>
       <c r="F11" t="n">
-        <v>2.21</v>
+        <v>1.869</v>
       </c>
       <c r="G11" t="n">
-        <v>0.594</v>
+        <v>0.992</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1.555</v>
+        <v>7.336</v>
       </c>
       <c r="J11" t="n">
-        <v>245.764</v>
+        <v>169.939</v>
       </c>
       <c r="K11" t="n">
-        <v>134.741</v>
+        <v>77.03400000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>12.902</v>
+        <v>33.853</v>
       </c>
       <c r="M11" t="n">
-        <v>0.034</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>44501</v>
+        <v>45962</v>
       </c>
       <c r="B12" t="n">
-        <v>22.307</v>
+        <v>21.876</v>
       </c>
       <c r="C12" t="n">
-        <v>57.366</v>
+        <v>45.011</v>
       </c>
       <c r="D12" t="n">
-        <v>19.777</v>
+        <v>56.897</v>
       </c>
       <c r="E12" t="n">
-        <v>478.17</v>
+        <v>525.735</v>
       </c>
       <c r="F12" t="n">
-        <v>1.94</v>
+        <v>1.804</v>
       </c>
       <c r="G12" t="n">
-        <v>149.314</v>
+        <v>86.831</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>1.57</v>
+        <v>8.471</v>
       </c>
       <c r="J12" t="n">
-        <v>190.567</v>
+        <v>149.939</v>
       </c>
       <c r="K12" t="n">
-        <v>85.923</v>
+        <v>141.538</v>
       </c>
       <c r="L12" t="n">
-        <v>6.408</v>
+        <v>53.186</v>
       </c>
       <c r="M12" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.219</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>44531</v>
+        <v>45992</v>
       </c>
       <c r="B13" t="n">
-        <v>22.824</v>
+        <v>20.587</v>
       </c>
       <c r="C13" t="n">
-        <v>41.589</v>
+        <v>46.164</v>
       </c>
       <c r="D13" t="n">
-        <v>19.852</v>
+        <v>59.754</v>
       </c>
       <c r="E13" t="n">
-        <v>400.709</v>
+        <v>477.397</v>
       </c>
       <c r="F13" t="n">
-        <v>1.767</v>
+        <v>1.692</v>
       </c>
       <c r="G13" t="n">
-        <v>291.18</v>
+        <v>246.23</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>1.502</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>199.335</v>
+        <v>90.279</v>
       </c>
       <c r="K13" t="n">
-        <v>42.697</v>
+        <v>133.266</v>
       </c>
       <c r="L13" t="n">
-        <v>8.382999999999999</v>
+        <v>72.15900000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>1.415</v>
+        <v>0.832</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>44562</v>
+        <v>46023</v>
       </c>
       <c r="B14" t="n">
-        <v>22.338</v>
+        <v>22.894</v>
       </c>
       <c r="C14" t="n">
-        <v>40.451</v>
+        <v>49.022</v>
       </c>
       <c r="D14" t="n">
-        <v>20.085</v>
+        <v>64.934</v>
       </c>
       <c r="E14" t="n">
-        <v>397.793</v>
+        <v>386.336</v>
       </c>
       <c r="F14" t="n">
-        <v>1.516</v>
+        <v>1.564</v>
       </c>
       <c r="G14" t="n">
-        <v>277.067</v>
+        <v>286.809</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1.392</v>
+        <v>8.544</v>
       </c>
       <c r="J14" t="n">
-        <v>228.142</v>
+        <v>142.053</v>
       </c>
       <c r="K14" t="n">
-        <v>68.759</v>
+        <v>140.59</v>
       </c>
       <c r="L14" t="n">
-        <v>7.112</v>
+        <v>22.789</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>0.075</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>44593</v>
+        <v>46054</v>
       </c>
       <c r="B15" t="n">
-        <v>20.152</v>
+        <v>20.846</v>
       </c>
       <c r="C15" t="n">
-        <v>40.829</v>
+        <v>39.189</v>
       </c>
       <c r="D15" t="n">
-        <v>20.186</v>
+        <v>65.81100000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>368.174</v>
+        <v>294.239</v>
       </c>
       <c r="F15" t="n">
-        <v>1.476</v>
+        <v>1.199</v>
       </c>
       <c r="G15" t="n">
-        <v>262.225</v>
+        <v>258.7</v>
       </c>
       <c r="H15" t="n">
-        <v>0.051</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>1.401</v>
+        <v>8.361000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>181.125</v>
+        <v>160.131</v>
       </c>
       <c r="K15" t="n">
-        <v>101.974</v>
+        <v>114.146</v>
       </c>
       <c r="L15" t="n">
-        <v>9.372999999999999</v>
+        <v>24.834</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>0.739</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>44621</v>
+        <v>46082</v>
       </c>
       <c r="B16" t="n">
-        <v>22.835</v>
+        <v>22.393</v>
       </c>
       <c r="C16" t="n">
-        <v>33.063</v>
+        <v>42.25</v>
       </c>
       <c r="D16" t="n">
-        <v>21.962</v>
+        <v>82.15300000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>345.007</v>
+        <v>339.815</v>
       </c>
       <c r="F16" t="n">
-        <v>1.394</v>
+        <v>1.267</v>
       </c>
       <c r="G16" t="n">
-        <v>299.389</v>
+        <v>294.355</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1.558</v>
+        <v>12.5</v>
       </c>
       <c r="J16" t="n">
-        <v>224.255</v>
+        <v>207.886</v>
       </c>
       <c r="K16" t="n">
-        <v>129.005</v>
+        <v>148.341</v>
       </c>
       <c r="L16" t="n">
-        <v>27.988</v>
+        <v>59.518</v>
       </c>
       <c r="M16" t="n">
-        <v>1.474</v>
+        <v>0.306</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>44652</v>
+        <v>46113</v>
       </c>
       <c r="B17" t="n">
-        <v>20.641</v>
+        <v>20.01</v>
       </c>
       <c r="C17" t="n">
-        <v>19.592</v>
+        <v>26.822</v>
       </c>
       <c r="D17" t="n">
-        <v>19.355</v>
+        <v>83.438</v>
       </c>
       <c r="E17" t="n">
-        <v>338.485</v>
+        <v>346.877</v>
       </c>
       <c r="F17" t="n">
-        <v>1.605</v>
+        <v>1.189</v>
       </c>
       <c r="G17" t="n">
-        <v>275.639</v>
+        <v>289.189</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>1.51</v>
+        <v>13.702</v>
       </c>
       <c r="J17" t="n">
-        <v>211.329</v>
+        <v>219.886</v>
       </c>
       <c r="K17" t="n">
-        <v>115.665</v>
+        <v>130.488</v>
       </c>
       <c r="L17" t="n">
-        <v>17.692</v>
+        <v>76.38500000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>0.272</v>
+        <v>2.183</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>44682</v>
+        <v>46143</v>
       </c>
       <c r="B18" t="n">
-        <v>24.262</v>
+        <v>22.639</v>
       </c>
       <c r="C18" t="n">
-        <v>10.177</v>
+        <v>13.289</v>
       </c>
       <c r="D18" t="n">
-        <v>17.749</v>
+        <v>84.899</v>
       </c>
       <c r="E18" t="n">
-        <v>361.912</v>
+        <v>297.202</v>
       </c>
       <c r="F18" t="n">
-        <v>1.47</v>
+        <v>1.24</v>
       </c>
       <c r="G18" t="n">
-        <v>81.358</v>
+        <v>212.182</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0.65</v>
+        <v>13.105</v>
       </c>
       <c r="J18" t="n">
-        <v>224.741</v>
+        <v>317.901</v>
       </c>
       <c r="K18" t="n">
-        <v>75.57299999999999</v>
+        <v>92.622</v>
       </c>
       <c r="L18" t="n">
-        <v>39.416</v>
+        <v>138.529</v>
       </c>
       <c r="M18" t="n">
-        <v>0.767</v>
+        <v>3.134</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>44713</v>
+        <v>46174</v>
       </c>
       <c r="B19" t="n">
-        <v>24.421</v>
+        <v>21.955</v>
       </c>
       <c r="C19" t="n">
-        <v>16.892</v>
+        <v>18.88</v>
       </c>
       <c r="D19" t="n">
-        <v>14.317</v>
+        <v>86.604</v>
       </c>
       <c r="E19" t="n">
-        <v>730.107</v>
+        <v>404.361</v>
       </c>
       <c r="F19" t="n">
-        <v>1.612</v>
+        <v>1.15</v>
       </c>
       <c r="G19" t="n">
-        <v>10.145</v>
+        <v>49.085</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8149999999999999</v>
+        <v>13.49</v>
       </c>
       <c r="J19" t="n">
-        <v>40.767</v>
+        <v>427.98</v>
       </c>
       <c r="K19" t="n">
-        <v>72.005</v>
+        <v>156.217</v>
       </c>
       <c r="L19" t="n">
-        <v>10.234</v>
+        <v>55.6</v>
       </c>
       <c r="M19" t="n">
-        <v>0.061</v>
+        <v>0.492</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>44743</v>
+        <v>46204</v>
       </c>
       <c r="B20" t="n">
-        <v>23.927</v>
+        <v>21.982</v>
       </c>
       <c r="C20" t="n">
-        <v>33.169</v>
+        <v>44.917</v>
       </c>
       <c r="D20" t="n">
-        <v>19.421</v>
+        <v>114.561</v>
       </c>
       <c r="E20" t="n">
-        <v>744.51</v>
+        <v>440.934</v>
       </c>
       <c r="F20" t="n">
-        <v>1.49</v>
+        <v>1.158</v>
       </c>
       <c r="G20" t="n">
-        <v>0.056</v>
+        <v>0.172</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0.198</v>
+        <v>13.979</v>
       </c>
       <c r="J20" t="n">
-        <v>49.728</v>
+        <v>466.945</v>
       </c>
       <c r="K20" t="n">
-        <v>96.685</v>
+        <v>160.421</v>
       </c>
       <c r="L20" t="n">
-        <v>13.473</v>
+        <v>85.465</v>
       </c>
       <c r="M20" t="n">
-        <v>0.486</v>
+        <v>1.513</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>44774</v>
+        <v>46235</v>
       </c>
       <c r="B21" t="n">
-        <v>25.476</v>
+        <v>21.939</v>
       </c>
       <c r="C21" t="n">
-        <v>17.851</v>
+        <v>49.784</v>
       </c>
       <c r="D21" t="n">
-        <v>19.306</v>
+        <v>142.278</v>
       </c>
       <c r="E21" t="n">
-        <v>805.553</v>
+        <v>322.693</v>
       </c>
       <c r="F21" t="n">
-        <v>1.438</v>
+        <v>1.274</v>
       </c>
       <c r="G21" t="n">
-        <v>0.119</v>
+        <v>0.267</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0.189</v>
+        <v>11.5</v>
       </c>
       <c r="J21" t="n">
-        <v>29.67</v>
+        <v>478.143</v>
       </c>
       <c r="K21" t="n">
-        <v>118.613</v>
+        <v>159.7</v>
       </c>
       <c r="L21" t="n">
-        <v>4.701</v>
+        <v>127.417</v>
       </c>
       <c r="M21" t="n">
-        <v>0.156</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="n">
-        <v>44805</v>
-      </c>
-      <c r="B22" t="n">
-        <v>24.477</v>
-      </c>
-      <c r="C22" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="D22" t="n">
-        <v>12.416</v>
-      </c>
-      <c r="E22" t="n">
-        <v>870.042</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1.622</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.199</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.604</v>
-      </c>
-      <c r="J22" t="n">
-        <v>6.776</v>
-      </c>
-      <c r="K22" t="n">
-        <v>91.395</v>
-      </c>
-      <c r="L22" t="n">
-        <v>5.865</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="n">
-        <v>44835</v>
-      </c>
-      <c r="B23" t="n">
-        <v>20.928</v>
-      </c>
-      <c r="C23" t="n">
-        <v>19.682</v>
-      </c>
-      <c r="D23" t="n">
-        <v>16.158</v>
-      </c>
-      <c r="E23" t="n">
-        <v>815.663</v>
-      </c>
-      <c r="F23" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="J23" t="n">
-        <v>52.492</v>
-      </c>
-      <c r="K23" t="n">
-        <v>72.40900000000001</v>
-      </c>
-      <c r="L23" t="n">
-        <v>11.909</v>
-      </c>
-      <c r="M23" t="n">
-        <v>2.051</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="n">
-        <v>44866</v>
-      </c>
-      <c r="B24" t="n">
-        <v>25.371</v>
-      </c>
-      <c r="C24" t="n">
-        <v>31.357</v>
-      </c>
-      <c r="D24" t="n">
-        <v>18.09</v>
-      </c>
-      <c r="E24" t="n">
-        <v>606.4109999999999</v>
-      </c>
-      <c r="F24" t="n">
-        <v>1.686</v>
-      </c>
-      <c r="G24" t="n">
-        <v>146.62</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.418</v>
-      </c>
-      <c r="J24" t="n">
-        <v>60.766</v>
-      </c>
-      <c r="K24" t="n">
-        <v>76.47799999999999</v>
-      </c>
-      <c r="L24" t="n">
-        <v>14.624</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0.614</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="n">
-        <v>44896</v>
-      </c>
-      <c r="B25" t="n">
-        <v>27.16</v>
-      </c>
-      <c r="C25" t="n">
-        <v>46.983</v>
-      </c>
-      <c r="D25" t="n">
-        <v>20.823</v>
-      </c>
-      <c r="E25" t="n">
-        <v>558.561</v>
-      </c>
-      <c r="F25" t="n">
-        <v>1.891</v>
-      </c>
-      <c r="G25" t="n">
-        <v>286.733</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.426</v>
-      </c>
-      <c r="J25" t="n">
-        <v>49.447</v>
-      </c>
-      <c r="K25" t="n">
-        <v>45.057</v>
-      </c>
-      <c r="L25" t="n">
-        <v>7.346</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0.306</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="n">
-        <v>44927</v>
-      </c>
-      <c r="B26" t="n">
-        <v>27.708</v>
-      </c>
-      <c r="C26" t="n">
-        <v>39.438</v>
-      </c>
-      <c r="D26" t="n">
-        <v>21.86</v>
-      </c>
-      <c r="E26" t="n">
-        <v>403.736</v>
-      </c>
-      <c r="F26" t="n">
-        <v>1.761</v>
-      </c>
-      <c r="G26" t="n">
-        <v>310.601</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>80.496</v>
-      </c>
-      <c r="K26" t="n">
-        <v>82.999</v>
-      </c>
-      <c r="L26" t="n">
-        <v>9.412000000000001</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="n">
-        <v>44958</v>
-      </c>
-      <c r="B27" t="n">
-        <v>22.512</v>
-      </c>
-      <c r="C27" t="n">
-        <v>40.921</v>
-      </c>
-      <c r="D27" t="n">
-        <v>20.973</v>
-      </c>
-      <c r="E27" t="n">
-        <v>352.671</v>
-      </c>
-      <c r="F27" t="n">
-        <v>1.649</v>
-      </c>
-      <c r="G27" t="n">
-        <v>293.532</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
-        <v>45.655</v>
-      </c>
-      <c r="K27" t="n">
-        <v>63.78</v>
-      </c>
-      <c r="L27" t="n">
-        <v>24.768</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0.249</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="n">
-        <v>44986</v>
-      </c>
-      <c r="B28" t="n">
-        <v>24.808</v>
-      </c>
-      <c r="C28" t="n">
-        <v>22.566</v>
-      </c>
-      <c r="D28" t="n">
-        <v>22.796</v>
-      </c>
-      <c r="E28" t="n">
-        <v>310.138</v>
-      </c>
-      <c r="F28" t="n">
-        <v>1.931</v>
-      </c>
-      <c r="G28" t="n">
-        <v>327.681</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
-        <v>106.54</v>
-      </c>
-      <c r="K28" t="n">
-        <v>54.667</v>
-      </c>
-      <c r="L28" t="n">
-        <v>52.319</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0.215</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="n">
-        <v>45017</v>
-      </c>
-      <c r="B29" t="n">
-        <v>23.253</v>
-      </c>
-      <c r="C29" t="n">
-        <v>17.712</v>
-      </c>
-      <c r="D29" t="n">
-        <v>21.86</v>
-      </c>
-      <c r="E29" t="n">
-        <v>274.773</v>
-      </c>
-      <c r="F29" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="G29" t="n">
-        <v>248.055</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
-        <v>150.573</v>
-      </c>
-      <c r="K29" t="n">
-        <v>87.907</v>
-      </c>
-      <c r="L29" t="n">
-        <v>62.476</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0.581</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="n">
-        <v>45047</v>
-      </c>
-      <c r="B30" t="n">
-        <v>22.263</v>
-      </c>
-      <c r="C30" t="n">
-        <v>16.361</v>
-      </c>
-      <c r="D30" t="n">
-        <v>19.964</v>
-      </c>
-      <c r="E30" t="n">
-        <v>300.306</v>
-      </c>
-      <c r="F30" t="n">
-        <v>1.775</v>
-      </c>
-      <c r="G30" t="n">
-        <v>43.071</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="n">
-        <v>358.366</v>
-      </c>
-      <c r="K30" t="n">
-        <v>161.244</v>
-      </c>
-      <c r="L30" t="n">
-        <v>89.005</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0.62</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="n">
-        <v>45078</v>
-      </c>
-      <c r="B31" t="n">
-        <v>23.116</v>
-      </c>
-      <c r="C31" t="n">
-        <v>8.419</v>
-      </c>
-      <c r="D31" t="n">
-        <v>19.143</v>
-      </c>
-      <c r="E31" t="n">
-        <v>290.746</v>
-      </c>
-      <c r="F31" t="n">
-        <v>2.083</v>
-      </c>
-      <c r="G31" t="n">
-        <v>5.438</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
-        <v>364.768</v>
-      </c>
-      <c r="K31" t="n">
-        <v>148.551</v>
-      </c>
-      <c r="L31" t="n">
-        <v>99.018</v>
-      </c>
-      <c r="M31" t="n">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="n">
-        <v>45108</v>
-      </c>
-      <c r="B32" t="n">
-        <v>23.67</v>
-      </c>
-      <c r="C32" t="n">
-        <v>35.664</v>
-      </c>
-      <c r="D32" t="n">
-        <v>20.906</v>
-      </c>
-      <c r="E32" t="n">
-        <v>504.3</v>
-      </c>
-      <c r="F32" t="n">
-        <v>2.115</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0.547</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="n">
-        <v>253.895</v>
-      </c>
-      <c r="K32" t="n">
-        <v>146.736</v>
-      </c>
-      <c r="L32" t="n">
-        <v>41.086</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0.843</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="n">
-        <v>45139</v>
-      </c>
-      <c r="B33" t="n">
-        <v>23.515</v>
-      </c>
-      <c r="C33" t="n">
-        <v>24.062</v>
-      </c>
-      <c r="D33" t="n">
-        <v>20.316</v>
-      </c>
-      <c r="E33" t="n">
-        <v>598.876</v>
-      </c>
-      <c r="F33" t="n">
-        <v>2.363</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="n">
-        <v>278.031</v>
-      </c>
-      <c r="K33" t="n">
-        <v>158.362</v>
-      </c>
-      <c r="L33" t="n">
-        <v>47.525</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0.607</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="n">
-        <v>45170</v>
-      </c>
-      <c r="B34" t="n">
-        <v>22.933</v>
-      </c>
-      <c r="C34" t="n">
-        <v>20.441</v>
-      </c>
-      <c r="D34" t="n">
-        <v>21.095</v>
-      </c>
-      <c r="E34" t="n">
-        <v>657.735</v>
-      </c>
-      <c r="F34" t="n">
-        <v>2.153</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0.528</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="n">
-        <v>223.428</v>
-      </c>
-      <c r="K34" t="n">
-        <v>146.618</v>
-      </c>
-      <c r="L34" t="n">
-        <v>35.872</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0.5639999999999999</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="n">
-        <v>45200</v>
-      </c>
-      <c r="B35" t="n">
-        <v>24.198</v>
-      </c>
-      <c r="C35" t="n">
-        <v>24.687</v>
-      </c>
-      <c r="D35" t="n">
-        <v>17.228</v>
-      </c>
-      <c r="E35" t="n">
-        <v>694.674</v>
-      </c>
-      <c r="F35" t="n">
-        <v>2.189</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0.624</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" t="n">
-        <v>191.441</v>
-      </c>
-      <c r="K35" t="n">
-        <v>65.642</v>
-      </c>
-      <c r="L35" t="n">
-        <v>21.032</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0.082</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="n">
-        <v>45231</v>
-      </c>
-      <c r="B36" t="n">
-        <v>23.17</v>
-      </c>
-      <c r="C36" t="n">
-        <v>45.063</v>
-      </c>
-      <c r="D36" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="E36" t="n">
-        <v>684.1609999999999</v>
-      </c>
-      <c r="F36" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="G36" t="n">
-        <v>132.355</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="n">
-        <v>152.534</v>
-      </c>
-      <c r="K36" t="n">
-        <v>47.33</v>
-      </c>
-      <c r="L36" t="n">
-        <v>31.759</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0.296</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="n">
-        <v>45261</v>
-      </c>
-      <c r="B37" t="n">
-        <v>24.292</v>
-      </c>
-      <c r="C37" t="n">
-        <v>48.625</v>
-      </c>
-      <c r="D37" t="n">
-        <v>21.677</v>
-      </c>
-      <c r="E37" t="n">
-        <v>499.763</v>
-      </c>
-      <c r="F37" t="n">
-        <v>1.796</v>
-      </c>
-      <c r="G37" t="n">
-        <v>262.485</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="n">
-        <v>100.52</v>
-      </c>
-      <c r="K37" t="n">
-        <v>88.43000000000001</v>
-      </c>
-      <c r="L37" t="n">
-        <v>46.692</v>
-      </c>
-      <c r="M37" t="n">
-        <v>2.028</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="n">
-        <v>45292</v>
-      </c>
-      <c r="B38" t="n">
-        <v>23.109</v>
-      </c>
-      <c r="C38" t="n">
-        <v>33.349</v>
-      </c>
-      <c r="D38" t="n">
-        <v>22.151</v>
-      </c>
-      <c r="E38" t="n">
-        <v>321.263</v>
-      </c>
-      <c r="F38" t="n">
-        <v>1.669</v>
-      </c>
-      <c r="G38" t="n">
-        <v>290.517</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="J38" t="n">
-        <v>184.284</v>
-      </c>
-      <c r="K38" t="n">
-        <v>151.879</v>
-      </c>
-      <c r="L38" t="n">
-        <v>56.854</v>
-      </c>
-      <c r="M38" t="n">
-        <v>2.657</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="n">
-        <v>45323</v>
-      </c>
-      <c r="B39" t="n">
-        <v>23.417</v>
-      </c>
-      <c r="C39" t="n">
-        <v>29.639</v>
-      </c>
-      <c r="D39" t="n">
-        <v>23.062</v>
-      </c>
-      <c r="E39" t="n">
-        <v>280.901</v>
-      </c>
-      <c r="F39" t="n">
-        <v>1.683</v>
-      </c>
-      <c r="G39" t="n">
-        <v>280.96</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0.5679999999999999</v>
-      </c>
-      <c r="J39" t="n">
-        <v>203.61</v>
-      </c>
-      <c r="K39" t="n">
-        <v>124.206</v>
-      </c>
-      <c r="L39" t="n">
-        <v>51.474</v>
-      </c>
-      <c r="M39" t="n">
-        <v>1.114</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="n">
-        <v>45352</v>
-      </c>
-      <c r="B40" t="n">
-        <v>23.858</v>
-      </c>
-      <c r="C40" t="n">
-        <v>17.326</v>
-      </c>
-      <c r="D40" t="n">
-        <v>23.568</v>
-      </c>
-      <c r="E40" t="n">
-        <v>225.456</v>
-      </c>
-      <c r="F40" t="n">
-        <v>1.761</v>
-      </c>
-      <c r="G40" t="n">
-        <v>302.073</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" t="n">
-        <v>5.151</v>
-      </c>
-      <c r="J40" t="n">
-        <v>203.948</v>
-      </c>
-      <c r="K40" t="n">
-        <v>158.498</v>
-      </c>
-      <c r="L40" t="n">
-        <v>139.033</v>
-      </c>
-      <c r="M40" t="n">
-        <v>9.894</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="n">
-        <v>45383</v>
-      </c>
-      <c r="B41" t="n">
-        <v>20.969</v>
-      </c>
-      <c r="C41" t="n">
-        <v>22.886</v>
-      </c>
-      <c r="D41" t="n">
-        <v>21.282</v>
-      </c>
-      <c r="E41" t="n">
-        <v>235.92</v>
-      </c>
-      <c r="F41" t="n">
-        <v>1.563</v>
-      </c>
-      <c r="G41" t="n">
-        <v>280.555</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" t="n">
-        <v>7.61</v>
-      </c>
-      <c r="J41" t="n">
-        <v>219.725</v>
-      </c>
-      <c r="K41" t="n">
-        <v>156.054</v>
-      </c>
-      <c r="L41" t="n">
-        <v>154.019</v>
-      </c>
-      <c r="M41" t="n">
-        <v>9.557</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="n">
-        <v>45413</v>
-      </c>
-      <c r="B42" t="n">
-        <v>23.408</v>
-      </c>
-      <c r="C42" t="n">
-        <v>5.305</v>
-      </c>
-      <c r="D42" t="n">
-        <v>19.724</v>
-      </c>
-      <c r="E42" t="n">
-        <v>229.413</v>
-      </c>
-      <c r="F42" t="n">
-        <v>1.453</v>
-      </c>
-      <c r="G42" t="n">
-        <v>140.033</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="n">
-        <v>8.975</v>
-      </c>
-      <c r="J42" t="n">
-        <v>358.409</v>
-      </c>
-      <c r="K42" t="n">
-        <v>162.704</v>
-      </c>
-      <c r="L42" t="n">
-        <v>182.421</v>
-      </c>
-      <c r="M42" t="n">
-        <v>9.708</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="n">
-        <v>45444</v>
-      </c>
-      <c r="B43" t="n">
-        <v>22.938</v>
-      </c>
-      <c r="C43" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="D43" t="n">
-        <v>15.034</v>
-      </c>
-      <c r="E43" t="n">
-        <v>401.414</v>
-      </c>
-      <c r="F43" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="G43" t="n">
-        <v>23.199</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>8.061</v>
-      </c>
-      <c r="J43" t="n">
-        <v>376.13</v>
-      </c>
-      <c r="K43" t="n">
-        <v>147.088</v>
-      </c>
-      <c r="L43" t="n">
-        <v>86.31100000000001</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0.991</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="n">
-        <v>45474</v>
-      </c>
-      <c r="B44" t="n">
-        <v>23.191</v>
-      </c>
-      <c r="C44" t="n">
-        <v>27.177</v>
-      </c>
-      <c r="D44" t="n">
-        <v>21.287</v>
-      </c>
-      <c r="E44" t="n">
-        <v>588.893</v>
-      </c>
-      <c r="F44" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="n">
-        <v>7.194</v>
-      </c>
-      <c r="J44" t="n">
-        <v>302.944</v>
-      </c>
-      <c r="K44" t="n">
-        <v>143.142</v>
-      </c>
-      <c r="L44" t="n">
-        <v>23.233</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0.044</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="n">
-        <v>45505</v>
-      </c>
-      <c r="B45" t="n">
-        <v>23.02</v>
-      </c>
-      <c r="C45" t="n">
-        <v>25.12</v>
-      </c>
-      <c r="D45" t="n">
-        <v>22.913</v>
-      </c>
-      <c r="E45" t="n">
-        <v>615.386</v>
-      </c>
-      <c r="F45" t="n">
-        <v>1.262</v>
-      </c>
-      <c r="G45" t="n">
-        <v>0.597</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
-        <v>7.936</v>
-      </c>
-      <c r="J45" t="n">
-        <v>248.011</v>
-      </c>
-      <c r="K45" t="n">
-        <v>142.311</v>
-      </c>
-      <c r="L45" t="n">
-        <v>31.722</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0.282</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="n">
-        <v>45536</v>
-      </c>
-      <c r="B46" t="n">
-        <v>22.485</v>
-      </c>
-      <c r="C46" t="n">
-        <v>5.266</v>
-      </c>
-      <c r="D46" t="n">
-        <v>19.838</v>
-      </c>
-      <c r="E46" t="n">
-        <v>624.831</v>
-      </c>
-      <c r="F46" t="n">
-        <v>1.435</v>
-      </c>
-      <c r="G46" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
-        <v>7.874</v>
-      </c>
-      <c r="J46" t="n">
-        <v>193.962</v>
-      </c>
-      <c r="K46" t="n">
-        <v>145.715</v>
-      </c>
-      <c r="L46" t="n">
-        <v>55.449</v>
-      </c>
-      <c r="M46" t="n">
-        <v>1.581</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="n">
-        <v>45566</v>
-      </c>
-      <c r="B47" t="n">
-        <v>22.834</v>
-      </c>
-      <c r="C47" t="n">
-        <v>32.099</v>
-      </c>
-      <c r="D47" t="n">
-        <v>21.657</v>
-      </c>
-      <c r="E47" t="n">
-        <v>658.889</v>
-      </c>
-      <c r="F47" t="n">
-        <v>1.473</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="I47" t="n">
-        <v>8.884</v>
-      </c>
-      <c r="J47" t="n">
-        <v>187.776</v>
-      </c>
-      <c r="K47" t="n">
-        <v>151.526</v>
-      </c>
-      <c r="L47" t="n">
-        <v>31.784</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0.156</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="4" t="n">
-        <v>45597</v>
-      </c>
-      <c r="B48" t="n">
-        <v>22.638</v>
-      </c>
-      <c r="C48" t="n">
-        <v>27.79</v>
-      </c>
-      <c r="D48" t="n">
-        <v>19.348</v>
-      </c>
-      <c r="E48" t="n">
-        <v>599.473</v>
-      </c>
-      <c r="F48" t="n">
-        <v>1.665</v>
-      </c>
-      <c r="G48" t="n">
-        <v>57.351</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="n">
-        <v>5.796</v>
-      </c>
-      <c r="J48" t="n">
-        <v>164.476</v>
-      </c>
-      <c r="K48" t="n">
-        <v>130.281</v>
-      </c>
-      <c r="L48" t="n">
-        <v>18.852</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0.241</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="4" t="n">
-        <v>45627</v>
-      </c>
-      <c r="B49" t="n">
-        <v>23.17</v>
-      </c>
-      <c r="C49" t="n">
-        <v>54.276</v>
-      </c>
-      <c r="D49" t="n">
-        <v>22.24</v>
-      </c>
-      <c r="E49" t="n">
-        <v>552.3339999999999</v>
-      </c>
-      <c r="F49" t="n">
-        <v>1.694</v>
-      </c>
-      <c r="G49" t="n">
-        <v>274.575</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="I49" t="n">
-        <v>6.205</v>
-      </c>
-      <c r="J49" t="n">
-        <v>45.331</v>
-      </c>
-      <c r="K49" t="n">
-        <v>42.946</v>
-      </c>
-      <c r="L49" t="n">
-        <v>13.03</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0.043</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="n">
-        <v>45658</v>
-      </c>
-      <c r="B50" t="n">
-        <v>21.97</v>
-      </c>
-      <c r="C50" t="n">
-        <v>48.999</v>
-      </c>
-      <c r="D50" t="n">
-        <v>29.888</v>
-      </c>
-      <c r="E50" t="n">
-        <v>462.057</v>
-      </c>
-      <c r="F50" t="n">
-        <v>1.741</v>
-      </c>
-      <c r="G50" t="n">
-        <v>309.857</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" t="n">
-        <v>6.563</v>
-      </c>
-      <c r="J50" t="n">
-        <v>82.547</v>
-      </c>
-      <c r="K50" t="n">
-        <v>94.58199999999999</v>
-      </c>
-      <c r="L50" t="n">
-        <v>13.332</v>
-      </c>
-      <c r="M50" t="n">
-        <v>0.016</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="n">
-        <v>45689</v>
-      </c>
-      <c r="B51" t="n">
-        <v>21.72</v>
-      </c>
-      <c r="C51" t="n">
-        <v>34.754</v>
-      </c>
-      <c r="D51" t="n">
-        <v>33.385</v>
-      </c>
-      <c r="E51" t="n">
-        <v>337.905</v>
-      </c>
-      <c r="F51" t="n">
-        <v>1.525</v>
-      </c>
-      <c r="G51" t="n">
-        <v>272.134</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" t="n">
-        <v>7.177</v>
-      </c>
-      <c r="J51" t="n">
-        <v>130.177</v>
-      </c>
-      <c r="K51" t="n">
-        <v>132.811</v>
-      </c>
-      <c r="L51" t="n">
-        <v>18.397</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0.025</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="n">
-        <v>45717</v>
-      </c>
-      <c r="B52" t="n">
-        <v>23.534</v>
-      </c>
-      <c r="C52" t="n">
-        <v>24.771</v>
-      </c>
-      <c r="D52" t="n">
-        <v>41.246</v>
-      </c>
-      <c r="E52" t="n">
-        <v>331.408</v>
-      </c>
-      <c r="F52" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="G52" t="n">
-        <v>303.23</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" t="n">
-        <v>8.103</v>
-      </c>
-      <c r="J52" t="n">
-        <v>223.594</v>
-      </c>
-      <c r="K52" t="n">
-        <v>158.181</v>
-      </c>
-      <c r="L52" t="n">
-        <v>65.411</v>
-      </c>
-      <c r="M52" t="n">
-        <v>0.314</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="n">
-        <v>45748</v>
-      </c>
-      <c r="B53" t="n">
-        <v>22.586</v>
-      </c>
-      <c r="C53" t="n">
-        <v>29.27</v>
-      </c>
-      <c r="D53" t="n">
-        <v>41.448</v>
-      </c>
-      <c r="E53" t="n">
-        <v>298.094</v>
-      </c>
-      <c r="F53" t="n">
-        <v>1.433</v>
-      </c>
-      <c r="G53" t="n">
-        <v>264.249</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" t="n">
-        <v>8.039</v>
-      </c>
-      <c r="J53" t="n">
-        <v>226.874</v>
-      </c>
-      <c r="K53" t="n">
-        <v>153.058</v>
-      </c>
-      <c r="L53" t="n">
-        <v>81.60899999999999</v>
-      </c>
-      <c r="M53" t="n">
-        <v>3.069</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="n">
-        <v>45778</v>
-      </c>
-      <c r="B54" t="n">
-        <v>22.903</v>
-      </c>
-      <c r="C54" t="n">
-        <v>10.256</v>
-      </c>
-      <c r="D54" t="n">
-        <v>39.64</v>
-      </c>
-      <c r="E54" t="n">
-        <v>275.326</v>
-      </c>
-      <c r="F54" t="n">
-        <v>1.492</v>
-      </c>
-      <c r="G54" t="n">
-        <v>150.926</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="I54" t="n">
-        <v>8.159000000000001</v>
-      </c>
-      <c r="J54" t="n">
-        <v>360.372</v>
-      </c>
-      <c r="K54" t="n">
-        <v>159.684</v>
-      </c>
-      <c r="L54" t="n">
-        <v>106.196</v>
-      </c>
-      <c r="M54" t="n">
-        <v>1.955</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="n">
-        <v>45809</v>
-      </c>
-      <c r="B55" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="C55" t="n">
-        <v>13.741</v>
-      </c>
-      <c r="D55" t="n">
-        <v>34.942</v>
-      </c>
-      <c r="E55" t="n">
-        <v>470.748</v>
-      </c>
-      <c r="F55" t="n">
-        <v>1.973</v>
-      </c>
-      <c r="G55" t="n">
-        <v>31.635</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I55" t="n">
-        <v>7.452</v>
-      </c>
-      <c r="J55" t="n">
-        <v>300.557</v>
-      </c>
-      <c r="K55" t="n">
-        <v>135.612</v>
-      </c>
-      <c r="L55" t="n">
-        <v>39.842</v>
-      </c>
-      <c r="M55" t="n">
-        <v>0.284</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="4" t="n">
-        <v>45839</v>
-      </c>
-      <c r="B56" t="n">
-        <v>23.257</v>
-      </c>
-      <c r="C56" t="n">
-        <v>38.201</v>
-      </c>
-      <c r="D56" t="n">
-        <v>44.005</v>
-      </c>
-      <c r="E56" t="n">
-        <v>480.194</v>
-      </c>
-      <c r="F56" t="n">
-        <v>1.871</v>
-      </c>
-      <c r="G56" t="n">
-        <v>5.241</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" t="n">
-        <v>8.198</v>
-      </c>
-      <c r="J56" t="n">
-        <v>282.769</v>
-      </c>
-      <c r="K56" t="n">
-        <v>153.438</v>
-      </c>
-      <c r="L56" t="n">
-        <v>49.87</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0.627</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="4" t="n">
-        <v>45870</v>
-      </c>
-      <c r="B57" t="n">
-        <v>23.108</v>
-      </c>
-      <c r="C57" t="n">
-        <v>22.445</v>
-      </c>
-      <c r="D57" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="E57" t="n">
-        <v>432.895</v>
-      </c>
-      <c r="F57" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="G57" t="n">
-        <v>0.352</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="n">
-        <v>8.843999999999999</v>
-      </c>
-      <c r="J57" t="n">
-        <v>378.223</v>
-      </c>
-      <c r="K57" t="n">
-        <v>153.711</v>
-      </c>
-      <c r="L57" t="n">
-        <v>50.641</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0.427</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="4" t="n">
-        <v>45901</v>
-      </c>
-      <c r="B58" t="n">
-        <v>22.695</v>
-      </c>
-      <c r="C58" t="n">
-        <v>9.087</v>
-      </c>
-      <c r="D58" t="n">
-        <v>47.886</v>
-      </c>
-      <c r="E58" t="n">
-        <v>613.097</v>
-      </c>
-      <c r="F58" t="n">
-        <v>1.935</v>
-      </c>
-      <c r="G58" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
-        <v>8.035</v>
-      </c>
-      <c r="J58" t="n">
-        <v>256.552</v>
-      </c>
-      <c r="K58" t="n">
-        <v>119.114</v>
-      </c>
-      <c r="L58" t="n">
-        <v>48.85</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0.134</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="4" t="n">
-        <v>45931</v>
-      </c>
-      <c r="B59" t="n">
-        <v>22.926</v>
-      </c>
-      <c r="C59" t="n">
-        <v>20.103</v>
-      </c>
-      <c r="D59" t="n">
-        <v>51.515</v>
-      </c>
-      <c r="E59" t="n">
-        <v>768.662</v>
-      </c>
-      <c r="F59" t="n">
-        <v>1.869</v>
-      </c>
-      <c r="G59" t="n">
-        <v>0.992</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" t="n">
-        <v>7.336</v>
-      </c>
-      <c r="J59" t="n">
-        <v>169.939</v>
-      </c>
-      <c r="K59" t="n">
-        <v>77.03400000000001</v>
-      </c>
-      <c r="L59" t="n">
-        <v>33.853</v>
-      </c>
-      <c r="M59" t="n">
-        <v>1.05</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="4" t="n">
-        <v>45962</v>
-      </c>
-      <c r="B60" t="n">
-        <v>21.876</v>
-      </c>
-      <c r="C60" t="n">
-        <v>45.011</v>
-      </c>
-      <c r="D60" t="n">
-        <v>56.897</v>
-      </c>
-      <c r="E60" t="n">
-        <v>525.735</v>
-      </c>
-      <c r="F60" t="n">
-        <v>1.804</v>
-      </c>
-      <c r="G60" t="n">
-        <v>86.831</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="n">
-        <v>8.471</v>
-      </c>
-      <c r="J60" t="n">
-        <v>149.939</v>
-      </c>
-      <c r="K60" t="n">
-        <v>141.538</v>
-      </c>
-      <c r="L60" t="n">
-        <v>53.186</v>
-      </c>
-      <c r="M60" t="n">
-        <v>0.219</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="4" t="n">
-        <v>45992</v>
-      </c>
-      <c r="B61" t="n">
-        <v>20.587</v>
-      </c>
-      <c r="C61" t="n">
-        <v>46.164</v>
-      </c>
-      <c r="D61" t="n">
-        <v>59.754</v>
-      </c>
-      <c r="E61" t="n">
-        <v>477.397</v>
-      </c>
-      <c r="F61" t="n">
-        <v>1.692</v>
-      </c>
-      <c r="G61" t="n">
-        <v>246.23</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" t="n">
-        <v>8.369999999999999</v>
-      </c>
-      <c r="J61" t="n">
-        <v>90.279</v>
-      </c>
-      <c r="K61" t="n">
-        <v>133.266</v>
-      </c>
-      <c r="L61" t="n">
-        <v>72.15900000000001</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0.832</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="4" t="n">
-        <v>46023</v>
-      </c>
-      <c r="B62" t="n">
-        <v>22.894</v>
-      </c>
-      <c r="C62" t="n">
-        <v>49.022</v>
-      </c>
-      <c r="D62" t="n">
-        <v>64.934</v>
-      </c>
-      <c r="E62" t="n">
-        <v>386.336</v>
-      </c>
-      <c r="F62" t="n">
-        <v>1.564</v>
-      </c>
-      <c r="G62" t="n">
-        <v>286.809</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" t="n">
-        <v>8.544</v>
-      </c>
-      <c r="J62" t="n">
-        <v>142.053</v>
-      </c>
-      <c r="K62" t="n">
-        <v>140.59</v>
-      </c>
-      <c r="L62" t="n">
-        <v>22.789</v>
-      </c>
-      <c r="M62" t="n">
-        <v>0.075</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="4" t="n">
-        <v>46054</v>
-      </c>
-      <c r="B63" t="n">
-        <v>20.846</v>
-      </c>
-      <c r="C63" t="n">
-        <v>39.189</v>
-      </c>
-      <c r="D63" t="n">
-        <v>65.81100000000001</v>
-      </c>
-      <c r="E63" t="n">
-        <v>294.239</v>
-      </c>
-      <c r="F63" t="n">
-        <v>1.199</v>
-      </c>
-      <c r="G63" t="n">
-        <v>258.7</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" t="n">
-        <v>8.361000000000001</v>
-      </c>
-      <c r="J63" t="n">
-        <v>160.131</v>
-      </c>
-      <c r="K63" t="n">
-        <v>114.146</v>
-      </c>
-      <c r="L63" t="n">
-        <v>24.834</v>
-      </c>
-      <c r="M63" t="n">
-        <v>0.739</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="4" t="n">
-        <v>46082</v>
-      </c>
-      <c r="B64" t="n">
-        <v>22.393</v>
-      </c>
-      <c r="C64" t="n">
-        <v>42.25</v>
-      </c>
-      <c r="D64" t="n">
-        <v>82.15300000000001</v>
-      </c>
-      <c r="E64" t="n">
-        <v>339.815</v>
-      </c>
-      <c r="F64" t="n">
-        <v>1.267</v>
-      </c>
-      <c r="G64" t="n">
-        <v>294.355</v>
-      </c>
-      <c r="H64" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="J64" t="n">
-        <v>207.886</v>
-      </c>
-      <c r="K64" t="n">
-        <v>148.341</v>
-      </c>
-      <c r="L64" t="n">
-        <v>59.518</v>
-      </c>
-      <c r="M64" t="n">
-        <v>0.306</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B65" t="n">
-        <v>20.01</v>
-      </c>
-      <c r="C65" t="n">
-        <v>26.822</v>
-      </c>
-      <c r="D65" t="n">
-        <v>83.438</v>
-      </c>
-      <c r="E65" t="n">
-        <v>346.877</v>
-      </c>
-      <c r="F65" t="n">
-        <v>1.189</v>
-      </c>
-      <c r="G65" t="n">
-        <v>289.189</v>
-      </c>
-      <c r="H65" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" t="n">
-        <v>13.702</v>
-      </c>
-      <c r="J65" t="n">
-        <v>219.886</v>
-      </c>
-      <c r="K65" t="n">
-        <v>130.488</v>
-      </c>
-      <c r="L65" t="n">
-        <v>76.38500000000001</v>
-      </c>
-      <c r="M65" t="n">
-        <v>2.183</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="4" t="n">
-        <v>46143</v>
-      </c>
-      <c r="B66" t="n">
-        <v>22.639</v>
-      </c>
-      <c r="C66" t="n">
-        <v>13.289</v>
-      </c>
-      <c r="D66" t="n">
-        <v>84.899</v>
-      </c>
-      <c r="E66" t="n">
-        <v>297.202</v>
-      </c>
-      <c r="F66" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="G66" t="n">
-        <v>212.182</v>
-      </c>
-      <c r="H66" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" t="n">
-        <v>13.105</v>
-      </c>
-      <c r="J66" t="n">
-        <v>317.901</v>
-      </c>
-      <c r="K66" t="n">
-        <v>92.622</v>
-      </c>
-      <c r="L66" t="n">
-        <v>138.529</v>
-      </c>
-      <c r="M66" t="n">
-        <v>3.134</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="4" t="n">
-        <v>46174</v>
-      </c>
-      <c r="B67" t="n">
-        <v>21.955</v>
-      </c>
-      <c r="C67" t="n">
-        <v>18.88</v>
-      </c>
-      <c r="D67" t="n">
-        <v>86.604</v>
-      </c>
-      <c r="E67" t="n">
-        <v>404.361</v>
-      </c>
-      <c r="F67" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="G67" t="n">
-        <v>49.085</v>
-      </c>
-      <c r="H67" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" t="n">
-        <v>13.49</v>
-      </c>
-      <c r="J67" t="n">
-        <v>427.98</v>
-      </c>
-      <c r="K67" t="n">
-        <v>156.217</v>
-      </c>
-      <c r="L67" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="M67" t="n">
-        <v>0.492</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="4" t="n">
-        <v>46204</v>
-      </c>
-      <c r="B68" t="n">
-        <v>21.982</v>
-      </c>
-      <c r="C68" t="n">
-        <v>44.917</v>
-      </c>
-      <c r="D68" t="n">
-        <v>114.561</v>
-      </c>
-      <c r="E68" t="n">
-        <v>440.934</v>
-      </c>
-      <c r="F68" t="n">
-        <v>1.158</v>
-      </c>
-      <c r="G68" t="n">
-        <v>0.172</v>
-      </c>
-      <c r="H68" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" t="n">
-        <v>13.979</v>
-      </c>
-      <c r="J68" t="n">
-        <v>466.945</v>
-      </c>
-      <c r="K68" t="n">
-        <v>160.421</v>
-      </c>
-      <c r="L68" t="n">
-        <v>85.465</v>
-      </c>
-      <c r="M68" t="n">
-        <v>1.513</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="4" t="n">
-        <v>46235</v>
-      </c>
-      <c r="B69" t="n">
-        <v>21.939</v>
-      </c>
-      <c r="C69" t="n">
-        <v>49.784</v>
-      </c>
-      <c r="D69" t="n">
-        <v>142.278</v>
-      </c>
-      <c r="E69" t="n">
-        <v>322.693</v>
-      </c>
-      <c r="F69" t="n">
-        <v>1.274</v>
-      </c>
-      <c r="G69" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="H69" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="J69" t="n">
-        <v>478.143</v>
-      </c>
-      <c r="K69" t="n">
-        <v>159.7</v>
-      </c>
-      <c r="L69" t="n">
-        <v>127.417</v>
-      </c>
-      <c r="M69" t="n">
         <v>3.877</v>
       </c>
     </row>

--- a/output/Data and Chart Outputs/guatemala_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/guatemala_power_generation_daily.xlsx
@@ -2736,19 +2736,19 @@
         <v>46266</v>
       </c>
       <c r="B70" t="n">
-        <v>342.7019</v>
+        <v>342.6863</v>
       </c>
       <c r="C70" t="n">
         <v>9.561999999999999</v>
       </c>
       <c r="D70" t="n">
-        <v>24.7702</v>
+        <v>24.7707</v>
       </c>
       <c r="E70" t="n">
         <v>96.8703</v>
       </c>
       <c r="F70" t="n">
-        <v>540.8733000000001</v>
+        <v>540.881</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -76264,19 +76264,19 @@
         <v>46295</v>
       </c>
       <c r="B2100" t="n">
-        <v>14680.6</v>
+        <v>14665</v>
       </c>
       <c r="C2100" t="n">
         <v>336.5</v>
       </c>
       <c r="D2100" t="n">
-        <v>58.9</v>
+        <v>59.4</v>
       </c>
       <c r="E2100" t="n">
         <v>2912.9</v>
       </c>
       <c r="F2100" t="n">
-        <v>15976.8</v>
+        <v>15984.5</v>
       </c>
       <c r="G2100" t="n">
         <v>0</v>
@@ -76291,7 +76291,7 @@
         <v>656.4</v>
       </c>
       <c r="K2100" t="n">
-        <v>40380.9</v>
+        <v>40373.4</v>
       </c>
     </row>
   </sheetData>
@@ -76305,7 +76305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76377,821 +76377,2789 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>45658</v>
+        <v>44197</v>
       </c>
       <c r="B2" t="n">
-        <v>21.97</v>
+        <v>22.011</v>
       </c>
       <c r="C2" t="n">
-        <v>48.999</v>
+        <v>44.174</v>
       </c>
       <c r="D2" t="n">
-        <v>29.888</v>
+        <v>20.063</v>
       </c>
       <c r="E2" t="n">
-        <v>462.057</v>
+        <v>445.687</v>
       </c>
       <c r="F2" t="n">
-        <v>1.741</v>
+        <v>2.58</v>
       </c>
       <c r="G2" t="n">
-        <v>309.857</v>
+        <v>311.144</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>6.563</v>
+        <v>0.41</v>
       </c>
       <c r="J2" t="n">
-        <v>82.547</v>
+        <v>95.2</v>
       </c>
       <c r="K2" t="n">
-        <v>94.58199999999999</v>
+        <v>9.446999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>13.332</v>
+        <v>13.916</v>
       </c>
       <c r="M2" t="n">
-        <v>0.016</v>
+        <v>0.048</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>45689</v>
+        <v>44228</v>
       </c>
       <c r="B3" t="n">
-        <v>21.72</v>
+        <v>20.555</v>
       </c>
       <c r="C3" t="n">
-        <v>34.754</v>
+        <v>27.037</v>
       </c>
       <c r="D3" t="n">
-        <v>33.385</v>
+        <v>19.518</v>
       </c>
       <c r="E3" t="n">
-        <v>337.905</v>
+        <v>333.286</v>
       </c>
       <c r="F3" t="n">
-        <v>1.525</v>
+        <v>2.364</v>
       </c>
       <c r="G3" t="n">
-        <v>272.134</v>
+        <v>292.601</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>0.034</v>
       </c>
       <c r="I3" t="n">
-        <v>7.177</v>
+        <v>1.162</v>
       </c>
       <c r="J3" t="n">
-        <v>130.177</v>
+        <v>194.663</v>
       </c>
       <c r="K3" t="n">
-        <v>132.811</v>
+        <v>32.985</v>
       </c>
       <c r="L3" t="n">
-        <v>18.397</v>
+        <v>35.029</v>
       </c>
       <c r="M3" t="n">
-        <v>0.025</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>45717</v>
+        <v>44256</v>
       </c>
       <c r="B4" t="n">
-        <v>23.534</v>
+        <v>22.957</v>
       </c>
       <c r="C4" t="n">
-        <v>24.771</v>
+        <v>36.509</v>
       </c>
       <c r="D4" t="n">
-        <v>41.246</v>
+        <v>22.659</v>
       </c>
       <c r="E4" t="n">
-        <v>331.408</v>
+        <v>336.139</v>
       </c>
       <c r="F4" t="n">
-        <v>1.57</v>
+        <v>2.271</v>
       </c>
       <c r="G4" t="n">
-        <v>303.23</v>
+        <v>312.942</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="I4" t="n">
-        <v>8.103</v>
+        <v>1.274</v>
       </c>
       <c r="J4" t="n">
-        <v>223.594</v>
+        <v>249.303</v>
       </c>
       <c r="K4" t="n">
-        <v>158.181</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>65.411</v>
+        <v>26.1</v>
       </c>
       <c r="M4" t="n">
-        <v>0.314</v>
+        <v>0.254</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>45748</v>
+        <v>44287</v>
       </c>
       <c r="B5" t="n">
-        <v>22.586</v>
+        <v>21.464</v>
       </c>
       <c r="C5" t="n">
-        <v>29.27</v>
+        <v>18.913</v>
       </c>
       <c r="D5" t="n">
-        <v>41.448</v>
+        <v>19.332</v>
       </c>
       <c r="E5" t="n">
-        <v>298.094</v>
+        <v>333.449</v>
       </c>
       <c r="F5" t="n">
-        <v>1.433</v>
+        <v>2.343</v>
       </c>
       <c r="G5" t="n">
-        <v>264.249</v>
+        <v>290.407</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.019</v>
       </c>
       <c r="I5" t="n">
-        <v>8.039</v>
+        <v>1.349</v>
       </c>
       <c r="J5" t="n">
-        <v>226.874</v>
+        <v>241.298</v>
       </c>
       <c r="K5" t="n">
-        <v>153.058</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>81.60899999999999</v>
+        <v>23.566</v>
       </c>
       <c r="M5" t="n">
-        <v>3.069</v>
+        <v>0.131</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>45778</v>
+        <v>44317</v>
       </c>
       <c r="B6" t="n">
-        <v>22.903</v>
+        <v>22.49</v>
       </c>
       <c r="C6" t="n">
-        <v>10.256</v>
+        <v>18.383</v>
       </c>
       <c r="D6" t="n">
-        <v>39.64</v>
+        <v>17.894</v>
       </c>
       <c r="E6" t="n">
-        <v>275.326</v>
+        <v>438.406</v>
       </c>
       <c r="F6" t="n">
-        <v>1.492</v>
+        <v>2.628</v>
       </c>
       <c r="G6" t="n">
-        <v>150.926</v>
+        <v>68.462</v>
       </c>
       <c r="H6" t="n">
-        <v>0.007</v>
+        <v>0.081</v>
       </c>
       <c r="I6" t="n">
-        <v>8.159000000000001</v>
+        <v>1.425</v>
       </c>
       <c r="J6" t="n">
-        <v>360.372</v>
+        <v>396.481</v>
       </c>
       <c r="K6" t="n">
-        <v>159.684</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>106.196</v>
+        <v>16.895</v>
       </c>
       <c r="M6" t="n">
-        <v>1.955</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>45809</v>
+        <v>44348</v>
       </c>
       <c r="B7" t="n">
-        <v>21.89</v>
+        <v>20.233</v>
       </c>
       <c r="C7" t="n">
-        <v>13.741</v>
+        <v>5.028</v>
       </c>
       <c r="D7" t="n">
-        <v>34.942</v>
+        <v>16.803</v>
       </c>
       <c r="E7" t="n">
-        <v>470.748</v>
+        <v>491.214</v>
       </c>
       <c r="F7" t="n">
-        <v>1.973</v>
+        <v>2.502</v>
       </c>
       <c r="G7" t="n">
-        <v>31.635</v>
+        <v>0.333</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>7.452</v>
+        <v>0.925</v>
       </c>
       <c r="J7" t="n">
-        <v>300.557</v>
+        <v>410.12</v>
       </c>
       <c r="K7" t="n">
-        <v>135.612</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>39.842</v>
+        <v>26.382</v>
       </c>
       <c r="M7" t="n">
-        <v>0.284</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>45839</v>
+        <v>44378</v>
       </c>
       <c r="B8" t="n">
-        <v>23.257</v>
+        <v>22.581</v>
       </c>
       <c r="C8" t="n">
-        <v>38.201</v>
+        <v>32.216</v>
       </c>
       <c r="D8" t="n">
-        <v>44.005</v>
+        <v>19.926</v>
       </c>
       <c r="E8" t="n">
-        <v>480.194</v>
+        <v>645.341</v>
       </c>
       <c r="F8" t="n">
-        <v>1.871</v>
+        <v>2.37</v>
       </c>
       <c r="G8" t="n">
-        <v>5.241</v>
+        <v>0.391</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>8.198</v>
+        <v>0.446</v>
       </c>
       <c r="J8" t="n">
-        <v>282.769</v>
+        <v>244.067</v>
       </c>
       <c r="K8" t="n">
-        <v>153.438</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>49.87</v>
+        <v>30.855</v>
       </c>
       <c r="M8" t="n">
-        <v>0.627</v>
+        <v>0.452</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>45870</v>
+        <v>44409</v>
       </c>
       <c r="B9" t="n">
-        <v>23.108</v>
+        <v>22.419</v>
       </c>
       <c r="C9" t="n">
-        <v>22.445</v>
+        <v>15.392</v>
       </c>
       <c r="D9" t="n">
-        <v>48.6</v>
+        <v>17.837</v>
       </c>
       <c r="E9" t="n">
-        <v>432.895</v>
+        <v>693.437</v>
       </c>
       <c r="F9" t="n">
-        <v>1.95</v>
+        <v>2.17</v>
       </c>
       <c r="G9" t="n">
-        <v>0.352</v>
+        <v>0.355</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>8.843999999999999</v>
+        <v>1.301</v>
       </c>
       <c r="J9" t="n">
-        <v>378.223</v>
+        <v>240.735</v>
       </c>
       <c r="K9" t="n">
-        <v>153.711</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>50.641</v>
+        <v>8.974</v>
       </c>
       <c r="M9" t="n">
-        <v>0.427</v>
+        <v>0.106</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>45901</v>
+        <v>44440</v>
       </c>
       <c r="B10" t="n">
-        <v>22.695</v>
+        <v>22.098</v>
       </c>
       <c r="C10" t="n">
-        <v>9.087</v>
+        <v>10.063</v>
       </c>
       <c r="D10" t="n">
-        <v>47.886</v>
+        <v>18.122</v>
       </c>
       <c r="E10" t="n">
-        <v>613.097</v>
+        <v>777.482</v>
       </c>
       <c r="F10" t="n">
-        <v>1.935</v>
+        <v>1.724</v>
       </c>
       <c r="G10" t="n">
-        <v>0.375</v>
+        <v>0.369</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>8.035</v>
+        <v>0.977</v>
       </c>
       <c r="J10" t="n">
-        <v>256.552</v>
+        <v>162.768</v>
       </c>
       <c r="K10" t="n">
-        <v>119.114</v>
+        <v>0.064</v>
       </c>
       <c r="L10" t="n">
-        <v>48.85</v>
+        <v>17.079</v>
       </c>
       <c r="M10" t="n">
-        <v>0.134</v>
+        <v>0.197</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>45931</v>
+        <v>44470</v>
       </c>
       <c r="B11" t="n">
-        <v>22.926</v>
+        <v>23.03</v>
       </c>
       <c r="C11" t="n">
-        <v>20.103</v>
+        <v>17.125</v>
       </c>
       <c r="D11" t="n">
-        <v>51.515</v>
+        <v>17.816</v>
       </c>
       <c r="E11" t="n">
-        <v>768.662</v>
+        <v>586.974</v>
       </c>
       <c r="F11" t="n">
-        <v>1.869</v>
+        <v>2.21</v>
       </c>
       <c r="G11" t="n">
-        <v>0.992</v>
+        <v>0.594</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>7.336</v>
+        <v>1.555</v>
       </c>
       <c r="J11" t="n">
-        <v>169.939</v>
+        <v>245.764</v>
       </c>
       <c r="K11" t="n">
-        <v>77.03400000000001</v>
+        <v>134.741</v>
       </c>
       <c r="L11" t="n">
-        <v>33.853</v>
+        <v>12.902</v>
       </c>
       <c r="M11" t="n">
-        <v>1.05</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>45962</v>
+        <v>44501</v>
       </c>
       <c r="B12" t="n">
-        <v>21.876</v>
+        <v>22.307</v>
       </c>
       <c r="C12" t="n">
-        <v>45.011</v>
+        <v>57.366</v>
       </c>
       <c r="D12" t="n">
-        <v>56.897</v>
+        <v>19.777</v>
       </c>
       <c r="E12" t="n">
-        <v>525.735</v>
+        <v>478.17</v>
       </c>
       <c r="F12" t="n">
-        <v>1.804</v>
+        <v>1.94</v>
       </c>
       <c r="G12" t="n">
-        <v>86.831</v>
+        <v>149.314</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>8.471</v>
+        <v>1.57</v>
       </c>
       <c r="J12" t="n">
-        <v>149.939</v>
+        <v>190.567</v>
       </c>
       <c r="K12" t="n">
-        <v>141.538</v>
+        <v>85.923</v>
       </c>
       <c r="L12" t="n">
-        <v>53.186</v>
+        <v>6.408</v>
       </c>
       <c r="M12" t="n">
-        <v>0.219</v>
+        <v>0.08799999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>45992</v>
+        <v>44531</v>
       </c>
       <c r="B13" t="n">
-        <v>20.587</v>
+        <v>22.824</v>
       </c>
       <c r="C13" t="n">
-        <v>46.164</v>
+        <v>41.589</v>
       </c>
       <c r="D13" t="n">
-        <v>59.754</v>
+        <v>19.852</v>
       </c>
       <c r="E13" t="n">
-        <v>477.397</v>
+        <v>400.709</v>
       </c>
       <c r="F13" t="n">
-        <v>1.692</v>
+        <v>1.767</v>
       </c>
       <c r="G13" t="n">
-        <v>246.23</v>
+        <v>291.18</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>8.369999999999999</v>
+        <v>1.502</v>
       </c>
       <c r="J13" t="n">
-        <v>90.279</v>
+        <v>199.335</v>
       </c>
       <c r="K13" t="n">
-        <v>133.266</v>
+        <v>42.697</v>
       </c>
       <c r="L13" t="n">
-        <v>72.15900000000001</v>
+        <v>8.382999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>0.832</v>
+        <v>1.415</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46023</v>
+        <v>44562</v>
       </c>
       <c r="B14" t="n">
-        <v>22.894</v>
+        <v>22.338</v>
       </c>
       <c r="C14" t="n">
-        <v>49.022</v>
+        <v>40.451</v>
       </c>
       <c r="D14" t="n">
-        <v>64.934</v>
+        <v>20.085</v>
       </c>
       <c r="E14" t="n">
-        <v>386.336</v>
+        <v>397.793</v>
       </c>
       <c r="F14" t="n">
-        <v>1.564</v>
+        <v>1.516</v>
       </c>
       <c r="G14" t="n">
-        <v>286.809</v>
+        <v>277.067</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>8.544</v>
+        <v>1.392</v>
       </c>
       <c r="J14" t="n">
-        <v>142.053</v>
+        <v>228.142</v>
       </c>
       <c r="K14" t="n">
-        <v>140.59</v>
+        <v>68.759</v>
       </c>
       <c r="L14" t="n">
-        <v>22.789</v>
+        <v>7.112</v>
       </c>
       <c r="M14" t="n">
-        <v>0.075</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46054</v>
+        <v>44593</v>
       </c>
       <c r="B15" t="n">
-        <v>20.846</v>
+        <v>20.152</v>
       </c>
       <c r="C15" t="n">
-        <v>39.189</v>
+        <v>40.829</v>
       </c>
       <c r="D15" t="n">
-        <v>65.81100000000001</v>
+        <v>20.186</v>
       </c>
       <c r="E15" t="n">
-        <v>294.239</v>
+        <v>368.174</v>
       </c>
       <c r="F15" t="n">
-        <v>1.199</v>
+        <v>1.476</v>
       </c>
       <c r="G15" t="n">
-        <v>258.7</v>
+        <v>262.225</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>0.051</v>
       </c>
       <c r="I15" t="n">
-        <v>8.361000000000001</v>
+        <v>1.401</v>
       </c>
       <c r="J15" t="n">
-        <v>160.131</v>
+        <v>181.125</v>
       </c>
       <c r="K15" t="n">
-        <v>114.146</v>
+        <v>101.974</v>
       </c>
       <c r="L15" t="n">
-        <v>24.834</v>
+        <v>9.372999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>0.739</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46082</v>
+        <v>44621</v>
       </c>
       <c r="B16" t="n">
-        <v>22.393</v>
+        <v>22.835</v>
       </c>
       <c r="C16" t="n">
-        <v>42.25</v>
+        <v>33.063</v>
       </c>
       <c r="D16" t="n">
-        <v>82.15300000000001</v>
+        <v>21.962</v>
       </c>
       <c r="E16" t="n">
-        <v>339.815</v>
+        <v>345.007</v>
       </c>
       <c r="F16" t="n">
-        <v>1.267</v>
+        <v>1.394</v>
       </c>
       <c r="G16" t="n">
-        <v>294.355</v>
+        <v>299.389</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>12.5</v>
+        <v>1.558</v>
       </c>
       <c r="J16" t="n">
-        <v>207.886</v>
+        <v>224.255</v>
       </c>
       <c r="K16" t="n">
-        <v>148.341</v>
+        <v>129.005</v>
       </c>
       <c r="L16" t="n">
-        <v>59.518</v>
+        <v>27.988</v>
       </c>
       <c r="M16" t="n">
-        <v>0.306</v>
+        <v>1.474</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>46113</v>
+        <v>44652</v>
       </c>
       <c r="B17" t="n">
-        <v>20.01</v>
+        <v>20.641</v>
       </c>
       <c r="C17" t="n">
-        <v>26.822</v>
+        <v>19.592</v>
       </c>
       <c r="D17" t="n">
-        <v>83.438</v>
+        <v>19.355</v>
       </c>
       <c r="E17" t="n">
-        <v>346.877</v>
+        <v>338.485</v>
       </c>
       <c r="F17" t="n">
-        <v>1.189</v>
+        <v>1.605</v>
       </c>
       <c r="G17" t="n">
-        <v>289.189</v>
+        <v>275.639</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>13.702</v>
+        <v>1.51</v>
       </c>
       <c r="J17" t="n">
-        <v>219.886</v>
+        <v>211.329</v>
       </c>
       <c r="K17" t="n">
-        <v>130.488</v>
+        <v>115.665</v>
       </c>
       <c r="L17" t="n">
-        <v>76.38500000000001</v>
+        <v>17.692</v>
       </c>
       <c r="M17" t="n">
-        <v>2.183</v>
+        <v>0.272</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>46143</v>
+        <v>44682</v>
       </c>
       <c r="B18" t="n">
-        <v>22.639</v>
+        <v>24.262</v>
       </c>
       <c r="C18" t="n">
-        <v>13.289</v>
+        <v>10.177</v>
       </c>
       <c r="D18" t="n">
-        <v>84.899</v>
+        <v>17.749</v>
       </c>
       <c r="E18" t="n">
-        <v>297.202</v>
+        <v>361.912</v>
       </c>
       <c r="F18" t="n">
-        <v>1.24</v>
+        <v>1.47</v>
       </c>
       <c r="G18" t="n">
-        <v>212.182</v>
+        <v>81.358</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>13.105</v>
+        <v>0.65</v>
       </c>
       <c r="J18" t="n">
-        <v>317.901</v>
+        <v>224.741</v>
       </c>
       <c r="K18" t="n">
-        <v>92.622</v>
+        <v>75.57299999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>138.529</v>
+        <v>39.416</v>
       </c>
       <c r="M18" t="n">
-        <v>3.134</v>
+        <v>0.767</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>46174</v>
+        <v>44713</v>
       </c>
       <c r="B19" t="n">
-        <v>21.955</v>
+        <v>24.421</v>
       </c>
       <c r="C19" t="n">
-        <v>18.88</v>
+        <v>16.892</v>
       </c>
       <c r="D19" t="n">
-        <v>86.604</v>
+        <v>14.317</v>
       </c>
       <c r="E19" t="n">
-        <v>404.361</v>
+        <v>730.107</v>
       </c>
       <c r="F19" t="n">
-        <v>1.15</v>
+        <v>1.612</v>
       </c>
       <c r="G19" t="n">
-        <v>49.085</v>
+        <v>10.145</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>13.49</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>427.98</v>
+        <v>40.767</v>
       </c>
       <c r="K19" t="n">
-        <v>156.217</v>
+        <v>72.005</v>
       </c>
       <c r="L19" t="n">
-        <v>55.6</v>
+        <v>10.234</v>
       </c>
       <c r="M19" t="n">
-        <v>0.492</v>
+        <v>0.061</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>46204</v>
+        <v>44743</v>
       </c>
       <c r="B20" t="n">
-        <v>21.982</v>
+        <v>23.927</v>
       </c>
       <c r="C20" t="n">
-        <v>44.917</v>
+        <v>33.169</v>
       </c>
       <c r="D20" t="n">
-        <v>114.561</v>
+        <v>19.421</v>
       </c>
       <c r="E20" t="n">
-        <v>440.934</v>
+        <v>744.51</v>
       </c>
       <c r="F20" t="n">
-        <v>1.158</v>
+        <v>1.49</v>
       </c>
       <c r="G20" t="n">
-        <v>0.172</v>
+        <v>0.056</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>13.979</v>
+        <v>0.198</v>
       </c>
       <c r="J20" t="n">
-        <v>466.945</v>
+        <v>49.728</v>
       </c>
       <c r="K20" t="n">
-        <v>160.421</v>
+        <v>96.685</v>
       </c>
       <c r="L20" t="n">
-        <v>85.465</v>
+        <v>13.473</v>
       </c>
       <c r="M20" t="n">
-        <v>1.513</v>
+        <v>0.486</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
+        <v>44774</v>
+      </c>
+      <c r="B21" t="n">
+        <v>25.476</v>
+      </c>
+      <c r="C21" t="n">
+        <v>17.851</v>
+      </c>
+      <c r="D21" t="n">
+        <v>19.306</v>
+      </c>
+      <c r="E21" t="n">
+        <v>805.553</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.438</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.189</v>
+      </c>
+      <c r="J21" t="n">
+        <v>29.67</v>
+      </c>
+      <c r="K21" t="n">
+        <v>118.613</v>
+      </c>
+      <c r="L21" t="n">
+        <v>4.701</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.156</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>44805</v>
+      </c>
+      <c r="B22" t="n">
+        <v>24.477</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D22" t="n">
+        <v>12.416</v>
+      </c>
+      <c r="E22" t="n">
+        <v>870.042</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.622</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.199</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="J22" t="n">
+        <v>6.776</v>
+      </c>
+      <c r="K22" t="n">
+        <v>91.395</v>
+      </c>
+      <c r="L22" t="n">
+        <v>5.865</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>44835</v>
+      </c>
+      <c r="B23" t="n">
+        <v>20.928</v>
+      </c>
+      <c r="C23" t="n">
+        <v>19.682</v>
+      </c>
+      <c r="D23" t="n">
+        <v>16.158</v>
+      </c>
+      <c r="E23" t="n">
+        <v>815.663</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="J23" t="n">
+        <v>52.492</v>
+      </c>
+      <c r="K23" t="n">
+        <v>72.40900000000001</v>
+      </c>
+      <c r="L23" t="n">
+        <v>11.909</v>
+      </c>
+      <c r="M23" t="n">
+        <v>2.051</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>44866</v>
+      </c>
+      <c r="B24" t="n">
+        <v>25.371</v>
+      </c>
+      <c r="C24" t="n">
+        <v>31.357</v>
+      </c>
+      <c r="D24" t="n">
+        <v>18.09</v>
+      </c>
+      <c r="E24" t="n">
+        <v>606.4109999999999</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.686</v>
+      </c>
+      <c r="G24" t="n">
+        <v>146.62</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="J24" t="n">
+        <v>60.766</v>
+      </c>
+      <c r="K24" t="n">
+        <v>76.47799999999999</v>
+      </c>
+      <c r="L24" t="n">
+        <v>14.624</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.614</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>44896</v>
+      </c>
+      <c r="B25" t="n">
+        <v>27.16</v>
+      </c>
+      <c r="C25" t="n">
+        <v>46.983</v>
+      </c>
+      <c r="D25" t="n">
+        <v>20.823</v>
+      </c>
+      <c r="E25" t="n">
+        <v>558.561</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.891</v>
+      </c>
+      <c r="G25" t="n">
+        <v>286.733</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.426</v>
+      </c>
+      <c r="J25" t="n">
+        <v>49.447</v>
+      </c>
+      <c r="K25" t="n">
+        <v>45.057</v>
+      </c>
+      <c r="L25" t="n">
+        <v>7.346</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.306</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>44927</v>
+      </c>
+      <c r="B26" t="n">
+        <v>27.708</v>
+      </c>
+      <c r="C26" t="n">
+        <v>39.438</v>
+      </c>
+      <c r="D26" t="n">
+        <v>21.86</v>
+      </c>
+      <c r="E26" t="n">
+        <v>403.736</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.761</v>
+      </c>
+      <c r="G26" t="n">
+        <v>310.601</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>80.496</v>
+      </c>
+      <c r="K26" t="n">
+        <v>82.999</v>
+      </c>
+      <c r="L26" t="n">
+        <v>9.412000000000001</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>44958</v>
+      </c>
+      <c r="B27" t="n">
+        <v>22.512</v>
+      </c>
+      <c r="C27" t="n">
+        <v>40.921</v>
+      </c>
+      <c r="D27" t="n">
+        <v>20.973</v>
+      </c>
+      <c r="E27" t="n">
+        <v>352.671</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.649</v>
+      </c>
+      <c r="G27" t="n">
+        <v>293.532</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>45.655</v>
+      </c>
+      <c r="K27" t="n">
+        <v>63.78</v>
+      </c>
+      <c r="L27" t="n">
+        <v>24.768</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.249</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>44986</v>
+      </c>
+      <c r="B28" t="n">
+        <v>24.808</v>
+      </c>
+      <c r="C28" t="n">
+        <v>22.566</v>
+      </c>
+      <c r="D28" t="n">
+        <v>22.796</v>
+      </c>
+      <c r="E28" t="n">
+        <v>310.138</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.931</v>
+      </c>
+      <c r="G28" t="n">
+        <v>327.681</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>106.54</v>
+      </c>
+      <c r="K28" t="n">
+        <v>54.667</v>
+      </c>
+      <c r="L28" t="n">
+        <v>52.319</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.215</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>45017</v>
+      </c>
+      <c r="B29" t="n">
+        <v>23.253</v>
+      </c>
+      <c r="C29" t="n">
+        <v>17.712</v>
+      </c>
+      <c r="D29" t="n">
+        <v>21.86</v>
+      </c>
+      <c r="E29" t="n">
+        <v>274.773</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="G29" t="n">
+        <v>248.055</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>150.573</v>
+      </c>
+      <c r="K29" t="n">
+        <v>87.907</v>
+      </c>
+      <c r="L29" t="n">
+        <v>62.476</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.581</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>45047</v>
+      </c>
+      <c r="B30" t="n">
+        <v>22.263</v>
+      </c>
+      <c r="C30" t="n">
+        <v>16.361</v>
+      </c>
+      <c r="D30" t="n">
+        <v>19.964</v>
+      </c>
+      <c r="E30" t="n">
+        <v>300.306</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.775</v>
+      </c>
+      <c r="G30" t="n">
+        <v>43.071</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>358.366</v>
+      </c>
+      <c r="K30" t="n">
+        <v>161.244</v>
+      </c>
+      <c r="L30" t="n">
+        <v>89.005</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>45078</v>
+      </c>
+      <c r="B31" t="n">
+        <v>23.116</v>
+      </c>
+      <c r="C31" t="n">
+        <v>8.419</v>
+      </c>
+      <c r="D31" t="n">
+        <v>19.143</v>
+      </c>
+      <c r="E31" t="n">
+        <v>290.746</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.083</v>
+      </c>
+      <c r="G31" t="n">
+        <v>5.438</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>364.768</v>
+      </c>
+      <c r="K31" t="n">
+        <v>148.551</v>
+      </c>
+      <c r="L31" t="n">
+        <v>99.018</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>45108</v>
+      </c>
+      <c r="B32" t="n">
+        <v>23.67</v>
+      </c>
+      <c r="C32" t="n">
+        <v>35.664</v>
+      </c>
+      <c r="D32" t="n">
+        <v>20.906</v>
+      </c>
+      <c r="E32" t="n">
+        <v>504.3</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.115</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.547</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>253.895</v>
+      </c>
+      <c r="K32" t="n">
+        <v>146.736</v>
+      </c>
+      <c r="L32" t="n">
+        <v>41.086</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.843</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>45139</v>
+      </c>
+      <c r="B33" t="n">
+        <v>23.515</v>
+      </c>
+      <c r="C33" t="n">
+        <v>24.062</v>
+      </c>
+      <c r="D33" t="n">
+        <v>20.316</v>
+      </c>
+      <c r="E33" t="n">
+        <v>598.876</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.363</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>278.031</v>
+      </c>
+      <c r="K33" t="n">
+        <v>158.362</v>
+      </c>
+      <c r="L33" t="n">
+        <v>47.525</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.607</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>45170</v>
+      </c>
+      <c r="B34" t="n">
+        <v>22.933</v>
+      </c>
+      <c r="C34" t="n">
+        <v>20.441</v>
+      </c>
+      <c r="D34" t="n">
+        <v>21.095</v>
+      </c>
+      <c r="E34" t="n">
+        <v>657.735</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.153</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.528</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>223.428</v>
+      </c>
+      <c r="K34" t="n">
+        <v>146.618</v>
+      </c>
+      <c r="L34" t="n">
+        <v>35.872</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.5639999999999999</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>45200</v>
+      </c>
+      <c r="B35" t="n">
+        <v>24.198</v>
+      </c>
+      <c r="C35" t="n">
+        <v>24.687</v>
+      </c>
+      <c r="D35" t="n">
+        <v>17.228</v>
+      </c>
+      <c r="E35" t="n">
+        <v>694.674</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.189</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.624</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>191.441</v>
+      </c>
+      <c r="K35" t="n">
+        <v>65.642</v>
+      </c>
+      <c r="L35" t="n">
+        <v>21.032</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.082</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>45231</v>
+      </c>
+      <c r="B36" t="n">
+        <v>23.17</v>
+      </c>
+      <c r="C36" t="n">
+        <v>45.063</v>
+      </c>
+      <c r="D36" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>684.1609999999999</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="G36" t="n">
+        <v>132.355</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>152.534</v>
+      </c>
+      <c r="K36" t="n">
+        <v>47.33</v>
+      </c>
+      <c r="L36" t="n">
+        <v>31.759</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.296</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n">
+        <v>45261</v>
+      </c>
+      <c r="B37" t="n">
+        <v>24.292</v>
+      </c>
+      <c r="C37" t="n">
+        <v>48.625</v>
+      </c>
+      <c r="D37" t="n">
+        <v>21.677</v>
+      </c>
+      <c r="E37" t="n">
+        <v>499.763</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.796</v>
+      </c>
+      <c r="G37" t="n">
+        <v>262.485</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>100.52</v>
+      </c>
+      <c r="K37" t="n">
+        <v>88.43000000000001</v>
+      </c>
+      <c r="L37" t="n">
+        <v>46.692</v>
+      </c>
+      <c r="M37" t="n">
+        <v>2.028</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>45292</v>
+      </c>
+      <c r="B38" t="n">
+        <v>23.109</v>
+      </c>
+      <c r="C38" t="n">
+        <v>33.349</v>
+      </c>
+      <c r="D38" t="n">
+        <v>22.151</v>
+      </c>
+      <c r="E38" t="n">
+        <v>321.263</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.669</v>
+      </c>
+      <c r="G38" t="n">
+        <v>290.517</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="J38" t="n">
+        <v>184.284</v>
+      </c>
+      <c r="K38" t="n">
+        <v>151.879</v>
+      </c>
+      <c r="L38" t="n">
+        <v>56.854</v>
+      </c>
+      <c r="M38" t="n">
+        <v>2.657</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>45323</v>
+      </c>
+      <c r="B39" t="n">
+        <v>23.417</v>
+      </c>
+      <c r="C39" t="n">
+        <v>29.639</v>
+      </c>
+      <c r="D39" t="n">
+        <v>23.062</v>
+      </c>
+      <c r="E39" t="n">
+        <v>280.901</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.683</v>
+      </c>
+      <c r="G39" t="n">
+        <v>280.96</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.5679999999999999</v>
+      </c>
+      <c r="J39" t="n">
+        <v>203.61</v>
+      </c>
+      <c r="K39" t="n">
+        <v>124.206</v>
+      </c>
+      <c r="L39" t="n">
+        <v>51.474</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.114</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n">
+        <v>45352</v>
+      </c>
+      <c r="B40" t="n">
+        <v>23.858</v>
+      </c>
+      <c r="C40" t="n">
+        <v>17.326</v>
+      </c>
+      <c r="D40" t="n">
+        <v>23.568</v>
+      </c>
+      <c r="E40" t="n">
+        <v>225.456</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.761</v>
+      </c>
+      <c r="G40" t="n">
+        <v>302.073</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>5.151</v>
+      </c>
+      <c r="J40" t="n">
+        <v>203.948</v>
+      </c>
+      <c r="K40" t="n">
+        <v>158.498</v>
+      </c>
+      <c r="L40" t="n">
+        <v>139.033</v>
+      </c>
+      <c r="M40" t="n">
+        <v>9.894</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n">
+        <v>45383</v>
+      </c>
+      <c r="B41" t="n">
+        <v>20.969</v>
+      </c>
+      <c r="C41" t="n">
+        <v>22.886</v>
+      </c>
+      <c r="D41" t="n">
+        <v>21.282</v>
+      </c>
+      <c r="E41" t="n">
+        <v>235.92</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.563</v>
+      </c>
+      <c r="G41" t="n">
+        <v>280.555</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="J41" t="n">
+        <v>219.725</v>
+      </c>
+      <c r="K41" t="n">
+        <v>156.054</v>
+      </c>
+      <c r="L41" t="n">
+        <v>154.019</v>
+      </c>
+      <c r="M41" t="n">
+        <v>9.557</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n">
+        <v>45413</v>
+      </c>
+      <c r="B42" t="n">
+        <v>23.408</v>
+      </c>
+      <c r="C42" t="n">
+        <v>5.305</v>
+      </c>
+      <c r="D42" t="n">
+        <v>19.724</v>
+      </c>
+      <c r="E42" t="n">
+        <v>229.413</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.453</v>
+      </c>
+      <c r="G42" t="n">
+        <v>140.033</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>8.975</v>
+      </c>
+      <c r="J42" t="n">
+        <v>358.409</v>
+      </c>
+      <c r="K42" t="n">
+        <v>162.704</v>
+      </c>
+      <c r="L42" t="n">
+        <v>182.421</v>
+      </c>
+      <c r="M42" t="n">
+        <v>9.708</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n">
+        <v>45444</v>
+      </c>
+      <c r="B43" t="n">
+        <v>22.938</v>
+      </c>
+      <c r="C43" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="D43" t="n">
+        <v>15.034</v>
+      </c>
+      <c r="E43" t="n">
+        <v>401.414</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="G43" t="n">
+        <v>23.199</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>8.061</v>
+      </c>
+      <c r="J43" t="n">
+        <v>376.13</v>
+      </c>
+      <c r="K43" t="n">
+        <v>147.088</v>
+      </c>
+      <c r="L43" t="n">
+        <v>86.31100000000001</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.991</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n">
+        <v>45474</v>
+      </c>
+      <c r="B44" t="n">
+        <v>23.191</v>
+      </c>
+      <c r="C44" t="n">
+        <v>27.177</v>
+      </c>
+      <c r="D44" t="n">
+        <v>21.287</v>
+      </c>
+      <c r="E44" t="n">
+        <v>588.893</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>7.194</v>
+      </c>
+      <c r="J44" t="n">
+        <v>302.944</v>
+      </c>
+      <c r="K44" t="n">
+        <v>143.142</v>
+      </c>
+      <c r="L44" t="n">
+        <v>23.233</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.044</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="n">
+        <v>45505</v>
+      </c>
+      <c r="B45" t="n">
+        <v>23.02</v>
+      </c>
+      <c r="C45" t="n">
+        <v>25.12</v>
+      </c>
+      <c r="D45" t="n">
+        <v>22.913</v>
+      </c>
+      <c r="E45" t="n">
+        <v>615.386</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1.262</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.597</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>7.936</v>
+      </c>
+      <c r="J45" t="n">
+        <v>248.011</v>
+      </c>
+      <c r="K45" t="n">
+        <v>142.311</v>
+      </c>
+      <c r="L45" t="n">
+        <v>31.722</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.282</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="n">
+        <v>45536</v>
+      </c>
+      <c r="B46" t="n">
+        <v>22.485</v>
+      </c>
+      <c r="C46" t="n">
+        <v>5.266</v>
+      </c>
+      <c r="D46" t="n">
+        <v>19.838</v>
+      </c>
+      <c r="E46" t="n">
+        <v>624.831</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1.435</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>7.874</v>
+      </c>
+      <c r="J46" t="n">
+        <v>193.962</v>
+      </c>
+      <c r="K46" t="n">
+        <v>145.715</v>
+      </c>
+      <c r="L46" t="n">
+        <v>55.449</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1.581</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="n">
+        <v>45566</v>
+      </c>
+      <c r="B47" t="n">
+        <v>22.834</v>
+      </c>
+      <c r="C47" t="n">
+        <v>32.099</v>
+      </c>
+      <c r="D47" t="n">
+        <v>21.657</v>
+      </c>
+      <c r="E47" t="n">
+        <v>658.889</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1.473</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="I47" t="n">
+        <v>8.884</v>
+      </c>
+      <c r="J47" t="n">
+        <v>187.776</v>
+      </c>
+      <c r="K47" t="n">
+        <v>151.526</v>
+      </c>
+      <c r="L47" t="n">
+        <v>31.784</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.156</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="n">
+        <v>45597</v>
+      </c>
+      <c r="B48" t="n">
+        <v>22.638</v>
+      </c>
+      <c r="C48" t="n">
+        <v>27.79</v>
+      </c>
+      <c r="D48" t="n">
+        <v>19.348</v>
+      </c>
+      <c r="E48" t="n">
+        <v>599.473</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1.665</v>
+      </c>
+      <c r="G48" t="n">
+        <v>57.351</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>5.796</v>
+      </c>
+      <c r="J48" t="n">
+        <v>164.476</v>
+      </c>
+      <c r="K48" t="n">
+        <v>130.281</v>
+      </c>
+      <c r="L48" t="n">
+        <v>18.852</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.241</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="n">
+        <v>45627</v>
+      </c>
+      <c r="B49" t="n">
+        <v>23.17</v>
+      </c>
+      <c r="C49" t="n">
+        <v>54.276</v>
+      </c>
+      <c r="D49" t="n">
+        <v>22.24</v>
+      </c>
+      <c r="E49" t="n">
+        <v>552.3339999999999</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1.694</v>
+      </c>
+      <c r="G49" t="n">
+        <v>274.575</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="I49" t="n">
+        <v>6.205</v>
+      </c>
+      <c r="J49" t="n">
+        <v>45.331</v>
+      </c>
+      <c r="K49" t="n">
+        <v>42.946</v>
+      </c>
+      <c r="L49" t="n">
+        <v>13.03</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.043</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="n">
+        <v>45658</v>
+      </c>
+      <c r="B50" t="n">
+        <v>21.97</v>
+      </c>
+      <c r="C50" t="n">
+        <v>48.999</v>
+      </c>
+      <c r="D50" t="n">
+        <v>29.888</v>
+      </c>
+      <c r="E50" t="n">
+        <v>462.057</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1.741</v>
+      </c>
+      <c r="G50" t="n">
+        <v>309.857</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>6.563</v>
+      </c>
+      <c r="J50" t="n">
+        <v>82.547</v>
+      </c>
+      <c r="K50" t="n">
+        <v>94.58199999999999</v>
+      </c>
+      <c r="L50" t="n">
+        <v>13.332</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.016</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B51" t="n">
+        <v>21.72</v>
+      </c>
+      <c r="C51" t="n">
+        <v>34.754</v>
+      </c>
+      <c r="D51" t="n">
+        <v>33.385</v>
+      </c>
+      <c r="E51" t="n">
+        <v>337.905</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1.525</v>
+      </c>
+      <c r="G51" t="n">
+        <v>272.134</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>7.177</v>
+      </c>
+      <c r="J51" t="n">
+        <v>130.177</v>
+      </c>
+      <c r="K51" t="n">
+        <v>132.811</v>
+      </c>
+      <c r="L51" t="n">
+        <v>18.397</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.025</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B52" t="n">
+        <v>23.534</v>
+      </c>
+      <c r="C52" t="n">
+        <v>24.771</v>
+      </c>
+      <c r="D52" t="n">
+        <v>41.246</v>
+      </c>
+      <c r="E52" t="n">
+        <v>331.408</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G52" t="n">
+        <v>303.23</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>8.103</v>
+      </c>
+      <c r="J52" t="n">
+        <v>223.594</v>
+      </c>
+      <c r="K52" t="n">
+        <v>158.181</v>
+      </c>
+      <c r="L52" t="n">
+        <v>65.411</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0.314</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="n">
+        <v>45748</v>
+      </c>
+      <c r="B53" t="n">
+        <v>22.586</v>
+      </c>
+      <c r="C53" t="n">
+        <v>29.27</v>
+      </c>
+      <c r="D53" t="n">
+        <v>41.448</v>
+      </c>
+      <c r="E53" t="n">
+        <v>298.094</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1.433</v>
+      </c>
+      <c r="G53" t="n">
+        <v>264.249</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>8.039</v>
+      </c>
+      <c r="J53" t="n">
+        <v>226.874</v>
+      </c>
+      <c r="K53" t="n">
+        <v>153.058</v>
+      </c>
+      <c r="L53" t="n">
+        <v>81.60899999999999</v>
+      </c>
+      <c r="M53" t="n">
+        <v>3.069</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="n">
+        <v>45778</v>
+      </c>
+      <c r="B54" t="n">
+        <v>22.903</v>
+      </c>
+      <c r="C54" t="n">
+        <v>10.256</v>
+      </c>
+      <c r="D54" t="n">
+        <v>39.64</v>
+      </c>
+      <c r="E54" t="n">
+        <v>275.326</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1.492</v>
+      </c>
+      <c r="G54" t="n">
+        <v>150.926</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="I54" t="n">
+        <v>8.159000000000001</v>
+      </c>
+      <c r="J54" t="n">
+        <v>360.372</v>
+      </c>
+      <c r="K54" t="n">
+        <v>159.684</v>
+      </c>
+      <c r="L54" t="n">
+        <v>106.196</v>
+      </c>
+      <c r="M54" t="n">
+        <v>1.955</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="n">
+        <v>45809</v>
+      </c>
+      <c r="B55" t="n">
+        <v>21.89</v>
+      </c>
+      <c r="C55" t="n">
+        <v>13.741</v>
+      </c>
+      <c r="D55" t="n">
+        <v>34.942</v>
+      </c>
+      <c r="E55" t="n">
+        <v>470.748</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1.973</v>
+      </c>
+      <c r="G55" t="n">
+        <v>31.635</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I55" t="n">
+        <v>7.452</v>
+      </c>
+      <c r="J55" t="n">
+        <v>300.557</v>
+      </c>
+      <c r="K55" t="n">
+        <v>135.612</v>
+      </c>
+      <c r="L55" t="n">
+        <v>39.842</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.284</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="n">
+        <v>45839</v>
+      </c>
+      <c r="B56" t="n">
+        <v>23.257</v>
+      </c>
+      <c r="C56" t="n">
+        <v>38.201</v>
+      </c>
+      <c r="D56" t="n">
+        <v>44.005</v>
+      </c>
+      <c r="E56" t="n">
+        <v>480.194</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1.871</v>
+      </c>
+      <c r="G56" t="n">
+        <v>5.241</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>8.198</v>
+      </c>
+      <c r="J56" t="n">
+        <v>282.769</v>
+      </c>
+      <c r="K56" t="n">
+        <v>153.438</v>
+      </c>
+      <c r="L56" t="n">
+        <v>49.87</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.627</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="n">
+        <v>45870</v>
+      </c>
+      <c r="B57" t="n">
+        <v>23.108</v>
+      </c>
+      <c r="C57" t="n">
+        <v>22.445</v>
+      </c>
+      <c r="D57" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="E57" t="n">
+        <v>432.895</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>8.843999999999999</v>
+      </c>
+      <c r="J57" t="n">
+        <v>378.223</v>
+      </c>
+      <c r="K57" t="n">
+        <v>153.711</v>
+      </c>
+      <c r="L57" t="n">
+        <v>50.641</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.427</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B58" t="n">
+        <v>22.695</v>
+      </c>
+      <c r="C58" t="n">
+        <v>9.087</v>
+      </c>
+      <c r="D58" t="n">
+        <v>47.886</v>
+      </c>
+      <c r="E58" t="n">
+        <v>613.097</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1.935</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>8.035</v>
+      </c>
+      <c r="J58" t="n">
+        <v>256.552</v>
+      </c>
+      <c r="K58" t="n">
+        <v>119.114</v>
+      </c>
+      <c r="L58" t="n">
+        <v>48.85</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.134</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B59" t="n">
+        <v>22.926</v>
+      </c>
+      <c r="C59" t="n">
+        <v>20.103</v>
+      </c>
+      <c r="D59" t="n">
+        <v>51.515</v>
+      </c>
+      <c r="E59" t="n">
+        <v>768.662</v>
+      </c>
+      <c r="F59" t="n">
+        <v>1.869</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.992</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
+        <v>7.336</v>
+      </c>
+      <c r="J59" t="n">
+        <v>169.939</v>
+      </c>
+      <c r="K59" t="n">
+        <v>77.03400000000001</v>
+      </c>
+      <c r="L59" t="n">
+        <v>33.853</v>
+      </c>
+      <c r="M59" t="n">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B60" t="n">
+        <v>21.876</v>
+      </c>
+      <c r="C60" t="n">
+        <v>45.011</v>
+      </c>
+      <c r="D60" t="n">
+        <v>56.897</v>
+      </c>
+      <c r="E60" t="n">
+        <v>525.735</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1.804</v>
+      </c>
+      <c r="G60" t="n">
+        <v>86.831</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
+        <v>8.471</v>
+      </c>
+      <c r="J60" t="n">
+        <v>149.939</v>
+      </c>
+      <c r="K60" t="n">
+        <v>141.538</v>
+      </c>
+      <c r="L60" t="n">
+        <v>53.186</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.219</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B61" t="n">
+        <v>20.587</v>
+      </c>
+      <c r="C61" t="n">
+        <v>46.164</v>
+      </c>
+      <c r="D61" t="n">
+        <v>59.754</v>
+      </c>
+      <c r="E61" t="n">
+        <v>477.397</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1.692</v>
+      </c>
+      <c r="G61" t="n">
+        <v>246.23</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="J61" t="n">
+        <v>90.279</v>
+      </c>
+      <c r="K61" t="n">
+        <v>133.266</v>
+      </c>
+      <c r="L61" t="n">
+        <v>72.15900000000001</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.832</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B62" t="n">
+        <v>22.894</v>
+      </c>
+      <c r="C62" t="n">
+        <v>49.022</v>
+      </c>
+      <c r="D62" t="n">
+        <v>64.934</v>
+      </c>
+      <c r="E62" t="n">
+        <v>386.336</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1.564</v>
+      </c>
+      <c r="G62" t="n">
+        <v>286.809</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>8.544</v>
+      </c>
+      <c r="J62" t="n">
+        <v>142.053</v>
+      </c>
+      <c r="K62" t="n">
+        <v>140.59</v>
+      </c>
+      <c r="L62" t="n">
+        <v>22.789</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0.075</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B63" t="n">
+        <v>20.846</v>
+      </c>
+      <c r="C63" t="n">
+        <v>39.189</v>
+      </c>
+      <c r="D63" t="n">
+        <v>65.81100000000001</v>
+      </c>
+      <c r="E63" t="n">
+        <v>294.239</v>
+      </c>
+      <c r="F63" t="n">
+        <v>1.199</v>
+      </c>
+      <c r="G63" t="n">
+        <v>258.7</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>8.361000000000001</v>
+      </c>
+      <c r="J63" t="n">
+        <v>160.131</v>
+      </c>
+      <c r="K63" t="n">
+        <v>114.146</v>
+      </c>
+      <c r="L63" t="n">
+        <v>24.834</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0.739</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B64" t="n">
+        <v>22.393</v>
+      </c>
+      <c r="C64" t="n">
+        <v>42.25</v>
+      </c>
+      <c r="D64" t="n">
+        <v>82.15300000000001</v>
+      </c>
+      <c r="E64" t="n">
+        <v>339.815</v>
+      </c>
+      <c r="F64" t="n">
+        <v>1.267</v>
+      </c>
+      <c r="G64" t="n">
+        <v>294.355</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J64" t="n">
+        <v>207.886</v>
+      </c>
+      <c r="K64" t="n">
+        <v>148.341</v>
+      </c>
+      <c r="L64" t="n">
+        <v>59.518</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0.306</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B65" t="n">
+        <v>20.01</v>
+      </c>
+      <c r="C65" t="n">
+        <v>26.822</v>
+      </c>
+      <c r="D65" t="n">
+        <v>83.438</v>
+      </c>
+      <c r="E65" t="n">
+        <v>346.877</v>
+      </c>
+      <c r="F65" t="n">
+        <v>1.189</v>
+      </c>
+      <c r="G65" t="n">
+        <v>289.189</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
+        <v>13.702</v>
+      </c>
+      <c r="J65" t="n">
+        <v>219.886</v>
+      </c>
+      <c r="K65" t="n">
+        <v>130.488</v>
+      </c>
+      <c r="L65" t="n">
+        <v>76.38500000000001</v>
+      </c>
+      <c r="M65" t="n">
+        <v>2.183</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B66" t="n">
+        <v>22.639</v>
+      </c>
+      <c r="C66" t="n">
+        <v>13.289</v>
+      </c>
+      <c r="D66" t="n">
+        <v>84.899</v>
+      </c>
+      <c r="E66" t="n">
+        <v>297.202</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="G66" t="n">
+        <v>212.182</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>13.105</v>
+      </c>
+      <c r="J66" t="n">
+        <v>317.901</v>
+      </c>
+      <c r="K66" t="n">
+        <v>92.622</v>
+      </c>
+      <c r="L66" t="n">
+        <v>138.529</v>
+      </c>
+      <c r="M66" t="n">
+        <v>3.134</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B67" t="n">
+        <v>21.955</v>
+      </c>
+      <c r="C67" t="n">
+        <v>18.88</v>
+      </c>
+      <c r="D67" t="n">
+        <v>86.604</v>
+      </c>
+      <c r="E67" t="n">
+        <v>404.361</v>
+      </c>
+      <c r="F67" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="G67" t="n">
+        <v>49.085</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>13.49</v>
+      </c>
+      <c r="J67" t="n">
+        <v>427.98</v>
+      </c>
+      <c r="K67" t="n">
+        <v>156.217</v>
+      </c>
+      <c r="L67" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0.492</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B68" t="n">
+        <v>21.982</v>
+      </c>
+      <c r="C68" t="n">
+        <v>44.917</v>
+      </c>
+      <c r="D68" t="n">
+        <v>114.561</v>
+      </c>
+      <c r="E68" t="n">
+        <v>440.934</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="n">
+        <v>13.979</v>
+      </c>
+      <c r="J68" t="n">
+        <v>466.945</v>
+      </c>
+      <c r="K68" t="n">
+        <v>160.421</v>
+      </c>
+      <c r="L68" t="n">
+        <v>85.465</v>
+      </c>
+      <c r="M68" t="n">
+        <v>1.513</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="n">
         <v>46235</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B69" t="n">
         <v>21.939</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C69" t="n">
         <v>49.784</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D69" t="n">
         <v>142.278</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E69" t="n">
         <v>322.693</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F69" t="n">
         <v>1.274</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G69" t="n">
         <v>0.267</v>
       </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
         <v>11.5</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J69" t="n">
         <v>478.143</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K69" t="n">
         <v>159.7</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L69" t="n">
         <v>127.417</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M69" t="n">
         <v>3.877</v>
       </c>
     </row>

--- a/output/Data and Chart Outputs/guatemala_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/guatemala_power_generation_daily.xlsx
@@ -161,6 +161,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -373,11 +374,23 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <numFmt formatCode="mmm/yy" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
         <tickLblSkip val="5"/>
@@ -405,6 +418,7 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -419,6 +433,7 @@
     </plotArea>
     <legend>
       <legendPos val="b"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -2736,25 +2751,25 @@
         <v>46266</v>
       </c>
       <c r="B70" t="n">
-        <v>342.6863</v>
+        <v>343.4424</v>
       </c>
       <c r="C70" t="n">
-        <v>9.561999999999999</v>
+        <v>9.5976</v>
       </c>
       <c r="D70" t="n">
-        <v>24.7707</v>
+        <v>24.7714</v>
       </c>
       <c r="E70" t="n">
         <v>96.8703</v>
       </c>
       <c r="F70" t="n">
-        <v>540.881</v>
+        <v>542.4634</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>169.1684</v>
+        <v>170.1702</v>
       </c>
     </row>
   </sheetData>
@@ -76264,34 +76279,34 @@
         <v>46295</v>
       </c>
       <c r="B2100" t="n">
-        <v>14665</v>
+        <v>15421.1</v>
       </c>
       <c r="C2100" t="n">
-        <v>336.5</v>
+        <v>372.1</v>
       </c>
       <c r="D2100" t="n">
-        <v>59.4</v>
+        <v>60.1</v>
       </c>
       <c r="E2100" t="n">
         <v>2912.9</v>
       </c>
       <c r="F2100" t="n">
-        <v>15984.5</v>
+        <v>17566.9</v>
       </c>
       <c r="G2100" t="n">
         <v>0</v>
       </c>
       <c r="H2100" t="n">
-        <v>5758.8</v>
+        <v>6697.5</v>
       </c>
       <c r="I2100" t="n">
         <v>0</v>
       </c>
       <c r="J2100" t="n">
-        <v>656.4</v>
+        <v>719.5</v>
       </c>
       <c r="K2100" t="n">
-        <v>40373.4</v>
+        <v>43750</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/guatemala_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/guatemala_power_generation_daily.xlsx
@@ -156,7 +156,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Guatemala power generation by type (AMM) (to Sep/26)</a:t>
+              <a:t>Guatemala power generation by type (AMM) (to Oct/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -186,12 +186,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$70</f>
+              <f>'Chart'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$70</f>
+              <f>'Chart'!$B$2:$B$71</f>
             </numRef>
           </val>
         </ser>
@@ -214,12 +214,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$70</f>
+              <f>'Chart'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$70</f>
+              <f>'Chart'!$C$2:$C$71</f>
             </numRef>
           </val>
         </ser>
@@ -242,12 +242,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$70</f>
+              <f>'Chart'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$70</f>
+              <f>'Chart'!$D$2:$D$71</f>
             </numRef>
           </val>
         </ser>
@@ -270,12 +270,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$70</f>
+              <f>'Chart'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$70</f>
+              <f>'Chart'!$E$2:$E$71</f>
             </numRef>
           </val>
         </ser>
@@ -298,12 +298,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$70</f>
+              <f>'Chart'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$70</f>
+              <f>'Chart'!$F$2:$F$71</f>
             </numRef>
           </val>
         </ser>
@@ -326,12 +326,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$70</f>
+              <f>'Chart'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$70</f>
+              <f>'Chart'!$G$2:$G$71</f>
             </numRef>
           </val>
         </ser>
@@ -354,12 +354,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$70</f>
+              <f>'Chart'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2:$H$70</f>
+              <f>'Chart'!$H$2:$H$71</f>
             </numRef>
           </val>
         </ser>
@@ -930,7 +930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2770,6 +2770,32 @@
       </c>
       <c r="H70" t="n">
         <v>170.1702</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B71" t="n">
+        <v>23.2677</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0.8897999999999999</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0.1371</v>
+      </c>
+      <c r="E71" t="n">
+        <v>4.279299999999999</v>
+      </c>
+      <c r="F71" t="n">
+        <v>33.9655</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>15.2839</v>
       </c>
     </row>
   </sheetData>
@@ -2784,7 +2810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2100"/>
+  <dimension ref="A1:K2102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76307,6 +76333,76 @@
       </c>
       <c r="K2100" t="n">
         <v>43750</v>
+      </c>
+    </row>
+    <row r="2101">
+      <c r="A2101" s="4" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B2101" t="n">
+        <v>12167.9</v>
+      </c>
+      <c r="C2101" t="n">
+        <v>482.6</v>
+      </c>
+      <c r="D2101" t="n">
+        <v>93</v>
+      </c>
+      <c r="E2101" t="n">
+        <v>2281.2</v>
+      </c>
+      <c r="F2101" t="n">
+        <v>18885.5</v>
+      </c>
+      <c r="G2101" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2101" t="n">
+        <v>8544.700000000001</v>
+      </c>
+      <c r="I2101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2101" t="n">
+        <v>727.7</v>
+      </c>
+      <c r="K2101" t="n">
+        <v>43182.6</v>
+      </c>
+    </row>
+    <row r="2102">
+      <c r="A2102" s="4" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B2102" t="n">
+        <v>11099.8</v>
+      </c>
+      <c r="C2102" t="n">
+        <v>407.2</v>
+      </c>
+      <c r="D2102" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="E2102" t="n">
+        <v>1998.1</v>
+      </c>
+      <c r="F2102" t="n">
+        <v>15080</v>
+      </c>
+      <c r="G2102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2102" t="n">
+        <v>5399.3</v>
+      </c>
+      <c r="I2102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2102" t="n">
+        <v>612.2</v>
+      </c>
+      <c r="K2102" t="n">
+        <v>34640.5</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/guatemala_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/guatemala_power_generation_daily.xlsx
@@ -21,8 +21,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="mmm/yy"/>
+    <numFmt numFmtId="165" formatCode="mmm/yy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -62,12 +62,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -790,7 +791,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
@@ -805,7 +805,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
@@ -841,7 +840,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
@@ -979,7 +977,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -1005,7 +1003,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -1031,7 +1029,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -1057,7 +1055,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -1083,7 +1081,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -1109,7 +1107,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -1135,7 +1133,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -1161,7 +1159,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -1187,7 +1185,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -1213,7 +1211,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -1239,7 +1237,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -1265,7 +1263,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -1291,7 +1289,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -1317,7 +1315,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -1343,7 +1341,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -1369,7 +1367,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -1395,7 +1393,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -1421,7 +1419,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -1447,7 +1445,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -1473,7 +1471,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -1499,7 +1497,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -1525,7 +1523,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -1551,7 +1549,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -1577,7 +1575,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -1603,7 +1601,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -1629,7 +1627,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -1655,7 +1653,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -1681,7 +1679,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -1707,7 +1705,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -1733,7 +1731,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -1759,7 +1757,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -1785,7 +1783,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -1811,7 +1809,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -1837,7 +1835,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -1863,7 +1861,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="5" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -1889,7 +1887,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -1915,7 +1913,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -1941,7 +1939,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -1967,7 +1965,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -1993,7 +1991,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -2019,7 +2017,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -2045,7 +2043,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -2071,7 +2069,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -2097,7 +2095,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -2123,7 +2121,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -2149,7 +2147,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -2175,7 +2173,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -2201,7 +2199,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -2227,7 +2225,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -2253,7 +2251,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -2279,7 +2277,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -2305,7 +2303,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -2331,7 +2329,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="5" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -2357,7 +2355,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="5" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -2383,7 +2381,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -2409,7 +2407,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="5" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -2435,7 +2433,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="5" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -2461,7 +2459,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="5" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -2487,7 +2485,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="5" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -2513,7 +2511,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -2539,7 +2537,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -2565,7 +2563,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="5" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -2591,7 +2589,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="5" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -2617,7 +2615,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="5" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -2643,7 +2641,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="5" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -2669,7 +2667,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="5" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -2695,7 +2693,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
+      <c r="A68" s="5" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -2721,7 +2719,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="n">
+      <c r="A69" s="5" t="n">
         <v>46235</v>
       </c>
       <c r="B69" t="n">
@@ -2747,7 +2745,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="n">
+      <c r="A70" s="5" t="n">
         <v>46266</v>
       </c>
       <c r="B70" t="n">
@@ -2773,7 +2771,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="n">
+      <c r="A71" s="5" t="n">
         <v>46296</v>
       </c>
       <c r="B71" t="n">

--- a/output/Data and Chart Outputs/guatemala_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/guatemala_power_generation_daily.xlsx
@@ -157,7 +157,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Guatemala power generation by type (AMM) (to Oct/26)</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>Guatemala power generation by type (AMM) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -187,12 +188,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$71</f>
+              <f>'Chart'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$71</f>
+              <f>'Chart'!$B$2:$B$70</f>
             </numRef>
           </val>
         </ser>
@@ -215,12 +216,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$71</f>
+              <f>'Chart'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$71</f>
+              <f>'Chart'!$C$2:$C$70</f>
             </numRef>
           </val>
         </ser>
@@ -243,12 +244,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$71</f>
+              <f>'Chart'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$71</f>
+              <f>'Chart'!$D$2:$D$70</f>
             </numRef>
           </val>
         </ser>
@@ -271,12 +272,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$71</f>
+              <f>'Chart'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$71</f>
+              <f>'Chart'!$E$2:$E$70</f>
             </numRef>
           </val>
         </ser>
@@ -299,12 +300,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$71</f>
+              <f>'Chart'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$71</f>
+              <f>'Chart'!$F$2:$F$70</f>
             </numRef>
           </val>
         </ser>
@@ -327,12 +328,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$71</f>
+              <f>'Chart'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$71</f>
+              <f>'Chart'!$G$2:$G$70</f>
             </numRef>
           </val>
         </ser>
@@ -355,12 +356,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$71</f>
+              <f>'Chart'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2:$H$71</f>
+              <f>'Chart'!$H$2:$H$70</f>
             </numRef>
           </val>
         </ser>
@@ -928,7 +929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H71"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -984,10 +985,10 @@
         <v>434.6783</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4199</v>
+        <v>0.4198999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>44.0501</v>
+        <v>44.05010000000001</v>
       </c>
       <c r="E2" t="n">
         <v>17.6922</v>
@@ -1025,7 +1026,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>355.4723999999999</v>
+        <v>355.4724</v>
       </c>
     </row>
     <row r="4">
@@ -1039,7 +1040,7 @@
         <v>1.2736</v>
       </c>
       <c r="D4" t="n">
-        <v>36.3527</v>
+        <v>36.35269999999999</v>
       </c>
       <c r="E4" t="n">
         <v>20.0252</v>
@@ -1077,7 +1078,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>336.5514000000001</v>
+        <v>336.5514</v>
       </c>
     </row>
     <row r="6">
@@ -1123,7 +1124,7 @@
         <v>14.8009</v>
       </c>
       <c r="F7" t="n">
-        <v>407.7174</v>
+        <v>407.7173999999999</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -1140,7 +1141,7 @@
         <v>625.4755</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4431</v>
+        <v>0.4430999999999999</v>
       </c>
       <c r="D8" t="n">
         <v>32.0565</v>
@@ -1163,7 +1164,7 @@
         <v>44409</v>
       </c>
       <c r="B9" t="n">
-        <v>672.0512</v>
+        <v>672.0512000000001</v>
       </c>
       <c r="C9" t="n">
         <v>1.293</v>
@@ -1215,7 +1216,7 @@
         <v>44470</v>
       </c>
       <c r="B11" t="n">
-        <v>569.6804000000001</v>
+        <v>569.6804</v>
       </c>
       <c r="C11" t="n">
         <v>1.5482</v>
@@ -1227,7 +1228,7 @@
         <v>15.1315</v>
       </c>
       <c r="F11" t="n">
-        <v>378.7308</v>
+        <v>378.7308000000001</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -1241,7 +1242,7 @@
         <v>44501</v>
       </c>
       <c r="B12" t="n">
-        <v>462.8098</v>
+        <v>462.8098000000001</v>
       </c>
       <c r="C12" t="n">
         <v>1.59</v>
@@ -1371,7 +1372,7 @@
         <v>44652</v>
       </c>
       <c r="B17" t="n">
-        <v>328.9181</v>
+        <v>328.9180999999999</v>
       </c>
       <c r="C17" t="n">
         <v>1.5049</v>
@@ -1383,7 +1384,7 @@
         <v>16.872</v>
       </c>
       <c r="F17" t="n">
-        <v>325.8591</v>
+        <v>325.8590999999999</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -1397,7 +1398,7 @@
         <v>44682</v>
       </c>
       <c r="B18" t="n">
-        <v>345.6943</v>
+        <v>345.6943000000001</v>
       </c>
       <c r="C18" t="n">
         <v>0.648</v>
@@ -1423,10 +1424,10 @@
         <v>44713</v>
       </c>
       <c r="B19" t="n">
-        <v>703.5581</v>
+        <v>703.5581000000001</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8041</v>
+        <v>0.8041000000000001</v>
       </c>
       <c r="D19" t="n">
         <v>17.0655</v>
@@ -1449,7 +1450,7 @@
         <v>44743</v>
       </c>
       <c r="B20" t="n">
-        <v>722.3920000000001</v>
+        <v>722.3919999999999</v>
       </c>
       <c r="C20" t="n">
         <v>0.1956</v>
@@ -1467,7 +1468,7 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>39.159</v>
+        <v>39.15899999999999</v>
       </c>
     </row>
     <row r="21">
@@ -1493,7 +1494,7 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>31.7767</v>
+        <v>31.77669999999999</v>
       </c>
     </row>
     <row r="22">
@@ -1501,10 +1502,10 @@
         <v>44805</v>
       </c>
       <c r="B22" t="n">
-        <v>840.9362</v>
+        <v>840.9362000000001</v>
       </c>
       <c r="C22" t="n">
-        <v>0.5943999999999999</v>
+        <v>0.5943999999999998</v>
       </c>
       <c r="D22" t="n">
         <v>3.7123</v>
@@ -1513,13 +1514,13 @@
         <v>10.792</v>
       </c>
       <c r="F22" t="n">
-        <v>96.6194</v>
+        <v>96.61939999999998</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>32.1029</v>
+        <v>32.10290000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1530,7 +1531,7 @@
         <v>786.9403000000001</v>
       </c>
       <c r="C23" t="n">
-        <v>0.07659999999999999</v>
+        <v>0.07660000000000003</v>
       </c>
       <c r="D23" t="n">
         <v>19.7183</v>
@@ -1553,13 +1554,13 @@
         <v>44866</v>
       </c>
       <c r="B24" t="n">
-        <v>581.3274</v>
+        <v>581.3273999999999</v>
       </c>
       <c r="C24" t="n">
         <v>0.4202</v>
       </c>
       <c r="D24" t="n">
-        <v>31.3407</v>
+        <v>31.34070000000001</v>
       </c>
       <c r="E24" t="n">
         <v>15.4866</v>
@@ -1571,7 +1572,7 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>189.6247</v>
+        <v>189.6246999999999</v>
       </c>
     </row>
     <row r="25">
@@ -1605,7 +1606,7 @@
         <v>44927</v>
       </c>
       <c r="B26" t="n">
-        <v>384.6021</v>
+        <v>384.6020999999999</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -1631,7 +1632,7 @@
         <v>44958</v>
       </c>
       <c r="B27" t="n">
-        <v>338.3386</v>
+        <v>338.3385999999999</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -1669,7 +1670,7 @@
         <v>18.7276</v>
       </c>
       <c r="F28" t="n">
-        <v>160.8314</v>
+        <v>160.8313999999999</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1701,7 +1702,7 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>334.0617</v>
+        <v>334.0617000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1741,7 +1742,7 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>8.317200000000001</v>
+        <v>8.317200000000003</v>
       </c>
       <c r="E31" t="n">
         <v>15.6779</v>
@@ -1773,7 +1774,7 @@
         <v>16.8406</v>
       </c>
       <c r="F32" t="n">
-        <v>397.3236</v>
+        <v>397.3236000000001</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1793,7 +1794,7 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>24.0841</v>
+        <v>24.08410000000001</v>
       </c>
       <c r="E33" t="n">
         <v>16.505</v>
@@ -1805,7 +1806,7 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>73.97580000000001</v>
+        <v>73.97580000000002</v>
       </c>
     </row>
     <row r="34">
@@ -1813,7 +1814,7 @@
         <v>45170</v>
       </c>
       <c r="B34" t="n">
-        <v>635.657</v>
+        <v>635.6570000000002</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -1831,7 +1832,7 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>61.62719999999999</v>
+        <v>61.6272</v>
       </c>
     </row>
     <row r="35">
@@ -1839,7 +1840,7 @@
         <v>45200</v>
       </c>
       <c r="B35" t="n">
-        <v>665.4331</v>
+        <v>665.4331000000001</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
@@ -1865,13 +1866,13 @@
         <v>45231</v>
       </c>
       <c r="B36" t="n">
-        <v>659.6137</v>
+        <v>659.6137000000001</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>45.10169999999999</v>
+        <v>45.1017</v>
       </c>
       <c r="E36" t="n">
         <v>14.9421</v>
@@ -1897,7 +1898,7 @@
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>48.71279999999999</v>
+        <v>48.7128</v>
       </c>
       <c r="E37" t="n">
         <v>18.1672</v>
@@ -1969,10 +1970,10 @@
         <v>45352</v>
       </c>
       <c r="B40" t="n">
-        <v>214.776</v>
+        <v>214.7760000000001</v>
       </c>
       <c r="C40" t="n">
-        <v>5.1565</v>
+        <v>5.156500000000001</v>
       </c>
       <c r="D40" t="n">
         <v>17.3359</v>
@@ -1981,13 +1982,13 @@
         <v>18.7637</v>
       </c>
       <c r="F40" t="n">
-        <v>362.8572</v>
+        <v>362.8572000000001</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>476.9679</v>
+        <v>476.9679000000001</v>
       </c>
     </row>
     <row r="41">
@@ -1995,10 +1996,10 @@
         <v>45383</v>
       </c>
       <c r="B41" t="n">
-        <v>227.8323</v>
+        <v>227.8322999999999</v>
       </c>
       <c r="C41" t="n">
-        <v>7.5954</v>
+        <v>7.595400000000001</v>
       </c>
       <c r="D41" t="n">
         <v>22.9491</v>
@@ -2007,13 +2008,13 @@
         <v>17.0033</v>
       </c>
       <c r="F41" t="n">
-        <v>375.0534</v>
+        <v>375.0533999999999</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>465.7295999999999</v>
+        <v>465.7296</v>
       </c>
     </row>
     <row r="42">
@@ -2024,10 +2025,10 @@
         <v>220.5018</v>
       </c>
       <c r="C42" t="n">
-        <v>8.948700000000001</v>
+        <v>8.948699999999999</v>
       </c>
       <c r="D42" t="n">
-        <v>5.4319</v>
+        <v>5.431900000000001</v>
       </c>
       <c r="E42" t="n">
         <v>15.4214</v>
@@ -2053,7 +2054,7 @@
         <v>8.0181</v>
       </c>
       <c r="D43" t="n">
-        <v>6.082199999999999</v>
+        <v>6.082200000000001</v>
       </c>
       <c r="E43" t="n">
         <v>11.7029</v>
@@ -2076,7 +2077,7 @@
         <v>561.2749</v>
       </c>
       <c r="C44" t="n">
-        <v>7.1617</v>
+        <v>7.161700000000001</v>
       </c>
       <c r="D44" t="n">
         <v>27.2245</v>
@@ -2091,7 +2092,7 @@
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>48.0732</v>
+        <v>48.07319999999999</v>
       </c>
     </row>
     <row r="45">
@@ -2102,7 +2103,7 @@
         <v>589.2155</v>
       </c>
       <c r="C45" t="n">
-        <v>7.8986</v>
+        <v>7.898599999999999</v>
       </c>
       <c r="D45" t="n">
         <v>25.0783</v>
@@ -2125,13 +2126,13 @@
         <v>45536</v>
       </c>
       <c r="B46" t="n">
-        <v>596.9659</v>
+        <v>596.9658999999999</v>
       </c>
       <c r="C46" t="n">
         <v>7.855300000000001</v>
       </c>
       <c r="D46" t="n">
-        <v>5.2478</v>
+        <v>5.247799999999999</v>
       </c>
       <c r="E46" t="n">
         <v>14.3581</v>
@@ -2151,7 +2152,7 @@
         <v>45566</v>
       </c>
       <c r="B47" t="n">
-        <v>628.4707</v>
+        <v>628.4707000000001</v>
       </c>
       <c r="C47" t="n">
         <v>8.862500000000001</v>
@@ -2177,7 +2178,7 @@
         <v>45597</v>
       </c>
       <c r="B48" t="n">
-        <v>573.357</v>
+        <v>573.3570000000001</v>
       </c>
       <c r="C48" t="n">
         <v>5.770899999999999</v>
@@ -2189,7 +2190,7 @@
         <v>13.8861</v>
       </c>
       <c r="F48" t="n">
-        <v>293.4937</v>
+        <v>293.4936999999999</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -2203,13 +2204,13 @@
         <v>45627</v>
       </c>
       <c r="B49" t="n">
-        <v>531.3296</v>
+        <v>531.3296000000001</v>
       </c>
       <c r="C49" t="n">
-        <v>6.3167</v>
+        <v>6.316699999999999</v>
       </c>
       <c r="D49" t="n">
-        <v>54.3307</v>
+        <v>54.33070000000002</v>
       </c>
       <c r="E49" t="n">
         <v>15.5204</v>
@@ -2232,10 +2233,10 @@
         <v>442.3877</v>
       </c>
       <c r="C50" t="n">
-        <v>6.6757</v>
+        <v>6.675700000000001</v>
       </c>
       <c r="D50" t="n">
-        <v>48.9241</v>
+        <v>48.92409999999999</v>
       </c>
       <c r="E50" t="n">
         <v>20.6406</v>
@@ -2247,7 +2248,7 @@
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>352.398</v>
+        <v>352.3980000000001</v>
       </c>
     </row>
     <row r="51">
@@ -2255,10 +2256,10 @@
         <v>45689</v>
       </c>
       <c r="B51" t="n">
-        <v>321.122</v>
+        <v>321.1220000000001</v>
       </c>
       <c r="C51" t="n">
-        <v>7.282400000000001</v>
+        <v>7.2824</v>
       </c>
       <c r="D51" t="n">
         <v>34.8112</v>
@@ -2281,7 +2282,7 @@
         <v>45717</v>
       </c>
       <c r="B52" t="n">
-        <v>314.7833</v>
+        <v>314.7833000000001</v>
       </c>
       <c r="C52" t="n">
         <v>8.1373</v>
@@ -2299,7 +2300,7 @@
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>395.5353</v>
+        <v>395.5352999999999</v>
       </c>
     </row>
     <row r="53">
@@ -2319,7 +2320,7 @@
         <v>30.094</v>
       </c>
       <c r="F53" t="n">
-        <v>340.3304</v>
+        <v>340.3304000000001</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -2336,7 +2337,7 @@
         <v>263.9033</v>
       </c>
       <c r="C54" t="n">
-        <v>8.146699999999999</v>
+        <v>8.146700000000001</v>
       </c>
       <c r="D54" t="n">
         <v>10.8725</v>
@@ -2362,7 +2363,7 @@
         <v>450.6852</v>
       </c>
       <c r="C55" t="n">
-        <v>7.497199999999999</v>
+        <v>7.4972</v>
       </c>
       <c r="D55" t="n">
         <v>13.9734</v>
@@ -2377,7 +2378,7 @@
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>88.98340000000002</v>
+        <v>88.9834</v>
       </c>
     </row>
     <row r="56">
@@ -2385,7 +2386,7 @@
         <v>45839</v>
       </c>
       <c r="B56" t="n">
-        <v>459.5136</v>
+        <v>459.5136000000001</v>
       </c>
       <c r="C56" t="n">
         <v>8.253</v>
@@ -2420,7 +2421,7 @@
         <v>22.7871</v>
       </c>
       <c r="E57" t="n">
-        <v>33.6402</v>
+        <v>33.64020000000001</v>
       </c>
       <c r="F57" t="n">
         <v>533.0232</v>
@@ -2440,7 +2441,7 @@
         <v>588.7179</v>
       </c>
       <c r="C58" t="n">
-        <v>8.026899999999999</v>
+        <v>8.026900000000001</v>
       </c>
       <c r="D58" t="n">
         <v>9.289</v>
@@ -2449,7 +2450,7 @@
         <v>34.56780000000001</v>
       </c>
       <c r="F58" t="n">
-        <v>376.5557</v>
+        <v>376.5557000000001</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -2472,7 +2473,7 @@
         <v>20.5608</v>
       </c>
       <c r="E59" t="n">
-        <v>38.4732</v>
+        <v>38.47320000000001</v>
       </c>
       <c r="F59" t="n">
         <v>248.6637</v>
@@ -2481,7 +2482,7 @@
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>63.1729</v>
+        <v>63.17290000000001</v>
       </c>
     </row>
     <row r="60">
@@ -2498,7 +2499,7 @@
         <v>45.4614</v>
       </c>
       <c r="E60" t="n">
-        <v>40.5734</v>
+        <v>40.57339999999999</v>
       </c>
       <c r="F60" t="n">
         <v>228.3431</v>
@@ -2507,7 +2508,7 @@
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>228.3753</v>
+        <v>228.3753000000001</v>
       </c>
     </row>
     <row r="61">
@@ -2541,13 +2542,13 @@
         <v>46023</v>
       </c>
       <c r="B62" t="n">
-        <v>369.564</v>
+        <v>369.5640000000001</v>
       </c>
       <c r="C62" t="n">
         <v>8.6065</v>
       </c>
       <c r="D62" t="n">
-        <v>49.3337</v>
+        <v>49.33369999999999</v>
       </c>
       <c r="E62" t="n">
         <v>44.301</v>
@@ -2573,7 +2574,7 @@
         <v>8.414399999999999</v>
       </c>
       <c r="D63" t="n">
-        <v>39.6186</v>
+        <v>39.61859999999999</v>
       </c>
       <c r="E63" t="n">
         <v>45.6215</v>
@@ -2599,13 +2600,13 @@
         <v>12.7066</v>
       </c>
       <c r="D64" t="n">
-        <v>42.743</v>
+        <v>42.74299999999999</v>
       </c>
       <c r="E64" t="n">
-        <v>58.6434</v>
+        <v>58.64339999999999</v>
       </c>
       <c r="F64" t="n">
-        <v>338.0113</v>
+        <v>338.0113000000001</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2619,7 +2620,7 @@
         <v>46113</v>
       </c>
       <c r="B65" t="n">
-        <v>331.8877</v>
+        <v>331.8876999999999</v>
       </c>
       <c r="C65" t="n">
         <v>13.8809</v>
@@ -2628,7 +2629,7 @@
         <v>27.2044</v>
       </c>
       <c r="E65" t="n">
-        <v>58.6102</v>
+        <v>58.61019999999999</v>
       </c>
       <c r="F65" t="n">
         <v>321.7152</v>
@@ -2637,7 +2638,7 @@
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>420.3832</v>
+        <v>420.3832000000001</v>
       </c>
     </row>
     <row r="66">
@@ -2683,7 +2684,7 @@
         <v>59.2709</v>
       </c>
       <c r="F67" t="n">
-        <v>595.5541999999999</v>
+        <v>595.5542</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2697,7 +2698,7 @@
         <v>46204</v>
       </c>
       <c r="B68" t="n">
-        <v>422.2715</v>
+        <v>422.2714999999999</v>
       </c>
       <c r="C68" t="n">
         <v>14.3386</v>
@@ -2706,7 +2707,7 @@
         <v>46.1874</v>
       </c>
       <c r="E68" t="n">
-        <v>79.74680000000001</v>
+        <v>79.74679999999999</v>
       </c>
       <c r="F68" t="n">
         <v>627.2261</v>
@@ -2735,7 +2736,7 @@
         <v>105.6491</v>
       </c>
       <c r="F69" t="n">
-        <v>639.8920000000001</v>
+        <v>639.8920000000002</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2749,13 +2750,13 @@
         <v>46266</v>
       </c>
       <c r="B70" t="n">
-        <v>343.4424</v>
+        <v>343.4423999999999</v>
       </c>
       <c r="C70" t="n">
-        <v>9.5976</v>
+        <v>9.597600000000002</v>
       </c>
       <c r="D70" t="n">
-        <v>24.7714</v>
+        <v>24.77139999999999</v>
       </c>
       <c r="E70" t="n">
         <v>96.8703</v>
@@ -2768,32 +2769,6 @@
       </c>
       <c r="H70" t="n">
         <v>170.1702</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="5" t="n">
-        <v>46296</v>
-      </c>
-      <c r="B71" t="n">
-        <v>23.2677</v>
-      </c>
-      <c r="C71" t="n">
-        <v>0.8897999999999999</v>
-      </c>
-      <c r="D71" t="n">
-        <v>0.1371</v>
-      </c>
-      <c r="E71" t="n">
-        <v>4.279299999999999</v>
-      </c>
-      <c r="F71" t="n">
-        <v>33.9655</v>
-      </c>
-      <c r="G71" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" t="n">
-        <v>15.2839</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/guatemala_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/guatemala_power_generation_daily.xlsx
@@ -21,8 +21,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="mmm/yy"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="mmm/yy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -62,13 +62,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -158,7 +157,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Guatemala power generation by type (AMM) (to Sep/26)</a:t>
+              <a:t>Guatemala power generation by type (AMM) (to Oct/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -188,12 +187,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$70</f>
+              <f>'Chart'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$70</f>
+              <f>'Chart'!$B$2:$B$71</f>
             </numRef>
           </val>
         </ser>
@@ -216,12 +215,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$70</f>
+              <f>'Chart'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$70</f>
+              <f>'Chart'!$C$2:$C$71</f>
             </numRef>
           </val>
         </ser>
@@ -244,12 +243,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$70</f>
+              <f>'Chart'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$70</f>
+              <f>'Chart'!$D$2:$D$71</f>
             </numRef>
           </val>
         </ser>
@@ -272,12 +271,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$70</f>
+              <f>'Chart'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$70</f>
+              <f>'Chart'!$E$2:$E$71</f>
             </numRef>
           </val>
         </ser>
@@ -300,12 +299,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$70</f>
+              <f>'Chart'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$70</f>
+              <f>'Chart'!$F$2:$F$71</f>
             </numRef>
           </val>
         </ser>
@@ -328,12 +327,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$70</f>
+              <f>'Chart'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$70</f>
+              <f>'Chart'!$G$2:$G$71</f>
             </numRef>
           </val>
         </ser>
@@ -356,12 +355,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$70</f>
+              <f>'Chart'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2:$H$70</f>
+              <f>'Chart'!$H$2:$H$71</f>
             </numRef>
           </val>
         </ser>
@@ -792,6 +791,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
@@ -806,6 +806,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
@@ -841,6 +842,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
@@ -929,7 +931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -978,7 +980,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -1004,7 +1006,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -1030,7 +1032,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -1056,7 +1058,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -1082,7 +1084,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -1108,7 +1110,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -1134,7 +1136,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -1160,7 +1162,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -1186,7 +1188,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -1212,7 +1214,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -1238,7 +1240,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -1264,7 +1266,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -1290,7 +1292,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -1316,7 +1318,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -1342,7 +1344,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -1368,7 +1370,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -1394,7 +1396,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -1420,7 +1422,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -1446,7 +1448,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -1472,7 +1474,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -1498,7 +1500,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -1524,7 +1526,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -1550,7 +1552,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -1576,7 +1578,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -1602,7 +1604,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -1628,7 +1630,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -1654,7 +1656,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -1680,7 +1682,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -1706,7 +1708,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -1732,7 +1734,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -1758,7 +1760,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -1784,7 +1786,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -1810,7 +1812,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -1836,7 +1838,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -1862,7 +1864,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -1888,7 +1890,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -1914,7 +1916,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -1940,7 +1942,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="3" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -1966,7 +1968,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -1992,7 +1994,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -2018,7 +2020,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -2044,7 +2046,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -2070,7 +2072,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -2096,7 +2098,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -2122,7 +2124,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -2148,7 +2150,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -2174,7 +2176,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -2200,7 +2202,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -2226,7 +2228,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="n">
+      <c r="A50" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -2252,7 +2254,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="3" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -2278,7 +2280,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="n">
+      <c r="A52" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -2304,7 +2306,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -2330,7 +2332,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n">
+      <c r="A54" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -2356,7 +2358,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -2382,7 +2384,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n">
+      <c r="A56" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -2408,7 +2410,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -2434,7 +2436,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="n">
+      <c r="A58" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -2460,7 +2462,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="n">
+      <c r="A59" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -2486,7 +2488,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="n">
+      <c r="A60" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -2512,7 +2514,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="n">
+      <c r="A61" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -2538,7 +2540,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="n">
+      <c r="A62" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -2564,7 +2566,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="n">
+      <c r="A63" s="3" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -2590,7 +2592,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="n">
+      <c r="A64" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -2616,7 +2618,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="n">
+      <c r="A65" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -2642,7 +2644,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="n">
+      <c r="A66" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -2668,7 +2670,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="n">
+      <c r="A67" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -2694,7 +2696,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="n">
+      <c r="A68" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -2720,7 +2722,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="n">
+      <c r="A69" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="B69" t="n">
@@ -2746,7 +2748,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="5" t="n">
+      <c r="A70" s="3" t="n">
         <v>46266</v>
       </c>
       <c r="B70" t="n">
@@ -2769,6 +2771,32 @@
       </c>
       <c r="H70" t="n">
         <v>170.1702</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B71" t="n">
+        <v>523.1177</v>
+      </c>
+      <c r="C71" t="n">
+        <v>13.0283</v>
+      </c>
+      <c r="D71" t="n">
+        <v>22.7735</v>
+      </c>
+      <c r="E71" t="n">
+        <v>78.053</v>
+      </c>
+      <c r="F71" t="n">
+        <v>353.1659</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>102.3068</v>
       </c>
     </row>
   </sheetData>
@@ -2783,7 +2811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2102"/>
+  <dimension ref="A1:K2127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76348,34 +76376,909 @@
         <v>46297</v>
       </c>
       <c r="B2102" t="n">
-        <v>11099.8</v>
+        <v>13455.4</v>
       </c>
       <c r="C2102" t="n">
-        <v>407.2</v>
+        <v>489.9</v>
       </c>
       <c r="D2102" t="n">
-        <v>44.1</v>
+        <v>39.1</v>
       </c>
       <c r="E2102" t="n">
-        <v>1998.1</v>
+        <v>1997.2</v>
       </c>
       <c r="F2102" t="n">
-        <v>15080</v>
+        <v>18189.8</v>
       </c>
       <c r="G2102" t="n">
         <v>0</v>
       </c>
       <c r="H2102" t="n">
-        <v>5399.3</v>
+        <v>6335</v>
       </c>
       <c r="I2102" t="n">
         <v>0</v>
       </c>
       <c r="J2102" t="n">
-        <v>612.2</v>
+        <v>741.5</v>
       </c>
       <c r="K2102" t="n">
-        <v>34640.5</v>
+        <v>41248</v>
+      </c>
+    </row>
+    <row r="2103">
+      <c r="A2103" s="4" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B2103" t="n">
+        <v>12765.1</v>
+      </c>
+      <c r="C2103" t="n">
+        <v>529.1</v>
+      </c>
+      <c r="D2103" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="E2103" t="n">
+        <v>3221.1</v>
+      </c>
+      <c r="F2103" t="n">
+        <v>16051.8</v>
+      </c>
+      <c r="G2103" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2103" t="n">
+        <v>4272.3</v>
+      </c>
+      <c r="I2103" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2103" t="n">
+        <v>741.6</v>
+      </c>
+      <c r="K2103" t="n">
+        <v>37651.7</v>
+      </c>
+    </row>
+    <row r="2104">
+      <c r="A2104" s="4" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B2104" t="n">
+        <v>18690.6</v>
+      </c>
+      <c r="C2104" t="n">
+        <v>266.6</v>
+      </c>
+      <c r="D2104" t="n">
+        <v>109</v>
+      </c>
+      <c r="E2104" t="n">
+        <v>355.5</v>
+      </c>
+      <c r="F2104" t="n">
+        <v>11861.3</v>
+      </c>
+      <c r="G2104" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2104" t="n">
+        <v>1679.4</v>
+      </c>
+      <c r="I2104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2104" t="n">
+        <v>733.3</v>
+      </c>
+      <c r="K2104" t="n">
+        <v>33695.7</v>
+      </c>
+    </row>
+    <row r="2105">
+      <c r="A2105" s="4" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B2105" t="n">
+        <v>16608.7</v>
+      </c>
+      <c r="C2105" t="n">
+        <v>391.3</v>
+      </c>
+      <c r="D2105" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="E2105" t="n">
+        <v>3898.6</v>
+      </c>
+      <c r="F2105" t="n">
+        <v>14231.5</v>
+      </c>
+      <c r="G2105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2105" t="n">
+        <v>3693.2</v>
+      </c>
+      <c r="I2105" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2105" t="n">
+        <v>727.9</v>
+      </c>
+      <c r="K2105" t="n">
+        <v>39602</v>
+      </c>
+    </row>
+    <row r="2106">
+      <c r="A2106" s="4" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B2106" t="n">
+        <v>18249.7</v>
+      </c>
+      <c r="C2106" t="n">
+        <v>514.1</v>
+      </c>
+      <c r="D2106" t="n">
+        <v>114.5</v>
+      </c>
+      <c r="E2106" t="n">
+        <v>3577.1</v>
+      </c>
+      <c r="F2106" t="n">
+        <v>16775.6</v>
+      </c>
+      <c r="G2106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2106" t="n">
+        <v>4156.1</v>
+      </c>
+      <c r="I2106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2106" t="n">
+        <v>727.6</v>
+      </c>
+      <c r="K2106" t="n">
+        <v>44114.8</v>
+      </c>
+    </row>
+    <row r="2107">
+      <c r="A2107" s="4" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B2107" t="n">
+        <v>19936.2</v>
+      </c>
+      <c r="C2107" t="n">
+        <v>509.8</v>
+      </c>
+      <c r="D2107" t="n">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="E2107" t="n">
+        <v>3014.4</v>
+      </c>
+      <c r="F2107" t="n">
+        <v>16277.5</v>
+      </c>
+      <c r="G2107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2107" t="n">
+        <v>2816.6</v>
+      </c>
+      <c r="I2107" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J2107" t="n">
+        <v>727.9</v>
+      </c>
+      <c r="K2107" t="n">
+        <v>43365.7</v>
+      </c>
+    </row>
+    <row r="2108">
+      <c r="A2108" s="4" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B2108" t="n">
+        <v>19855.4</v>
+      </c>
+      <c r="C2108" t="n">
+        <v>489.8</v>
+      </c>
+      <c r="D2108" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="E2108" t="n">
+        <v>2403.7</v>
+      </c>
+      <c r="F2108" t="n">
+        <v>16834.2</v>
+      </c>
+      <c r="G2108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2108" t="n">
+        <v>3516.6</v>
+      </c>
+      <c r="I2108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2108" t="n">
+        <v>733.2</v>
+      </c>
+      <c r="K2108" t="n">
+        <v>43867.7</v>
+      </c>
+    </row>
+    <row r="2109">
+      <c r="A2109" s="4" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B2109" t="n">
+        <v>22093.5</v>
+      </c>
+      <c r="C2109" t="n">
+        <v>475</v>
+      </c>
+      <c r="D2109" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="E2109" t="n">
+        <v>2738.4</v>
+      </c>
+      <c r="F2109" t="n">
+        <v>15332.9</v>
+      </c>
+      <c r="G2109" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2109" t="n">
+        <v>2743</v>
+      </c>
+      <c r="I2109" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2109" t="n">
+        <v>732.1</v>
+      </c>
+      <c r="K2109" t="n">
+        <v>44236.5</v>
+      </c>
+    </row>
+    <row r="2110">
+      <c r="A2110" s="4" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B2110" t="n">
+        <v>19475.2</v>
+      </c>
+      <c r="C2110" t="n">
+        <v>444.5</v>
+      </c>
+      <c r="D2110" t="n">
+        <v>154.8</v>
+      </c>
+      <c r="E2110" t="n">
+        <v>2634.4</v>
+      </c>
+      <c r="F2110" t="n">
+        <v>16104.8</v>
+      </c>
+      <c r="G2110" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2110" t="n">
+        <v>1911.9</v>
+      </c>
+      <c r="I2110" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2110" t="n">
+        <v>717</v>
+      </c>
+      <c r="K2110" t="n">
+        <v>41442.7</v>
+      </c>
+    </row>
+    <row r="2111">
+      <c r="A2111" s="4" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B2111" t="n">
+        <v>16344.8</v>
+      </c>
+      <c r="C2111" t="n">
+        <v>442.1</v>
+      </c>
+      <c r="D2111" t="n">
+        <v>1152.6</v>
+      </c>
+      <c r="E2111" t="n">
+        <v>3552.6</v>
+      </c>
+      <c r="F2111" t="n">
+        <v>12171.2</v>
+      </c>
+      <c r="G2111" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2111" t="n">
+        <v>2612.4</v>
+      </c>
+      <c r="I2111" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2111" t="n">
+        <v>717.4</v>
+      </c>
+      <c r="K2111" t="n">
+        <v>36992.9</v>
+      </c>
+    </row>
+    <row r="2112">
+      <c r="A2112" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B2112" t="n">
+        <v>18301.7</v>
+      </c>
+      <c r="C2112" t="n">
+        <v>385.1</v>
+      </c>
+      <c r="D2112" t="n">
+        <v>1474.8</v>
+      </c>
+      <c r="E2112" t="n">
+        <v>3452.9</v>
+      </c>
+      <c r="F2112" t="n">
+        <v>12555.1</v>
+      </c>
+      <c r="G2112" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2112" t="n">
+        <v>4913.5</v>
+      </c>
+      <c r="I2112" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2112" t="n">
+        <v>709.1</v>
+      </c>
+      <c r="K2112" t="n">
+        <v>41792.1</v>
+      </c>
+    </row>
+    <row r="2113">
+      <c r="A2113" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B2113" t="n">
+        <v>17060.3</v>
+      </c>
+      <c r="C2113" t="n">
+        <v>436</v>
+      </c>
+      <c r="D2113" t="n">
+        <v>1379.1</v>
+      </c>
+      <c r="E2113" t="n">
+        <v>3313</v>
+      </c>
+      <c r="F2113" t="n">
+        <v>14935</v>
+      </c>
+      <c r="G2113" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2113" t="n">
+        <v>5251.7</v>
+      </c>
+      <c r="I2113" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2113" t="n">
+        <v>708.2</v>
+      </c>
+      <c r="K2113" t="n">
+        <v>43083.2</v>
+      </c>
+    </row>
+    <row r="2114">
+      <c r="A2114" s="4" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B2114" t="n">
+        <v>20676.4</v>
+      </c>
+      <c r="C2114" t="n">
+        <v>434.9</v>
+      </c>
+      <c r="D2114" t="n">
+        <v>1026.4</v>
+      </c>
+      <c r="E2114" t="n">
+        <v>2825</v>
+      </c>
+      <c r="F2114" t="n">
+        <v>13039.9</v>
+      </c>
+      <c r="G2114" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2114" t="n">
+        <v>4189.5</v>
+      </c>
+      <c r="I2114" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2114" t="n">
+        <v>713.8</v>
+      </c>
+      <c r="K2114" t="n">
+        <v>42906</v>
+      </c>
+    </row>
+    <row r="2115">
+      <c r="A2115" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B2115" t="n">
+        <v>19496.8</v>
+      </c>
+      <c r="C2115" t="n">
+        <v>543.8</v>
+      </c>
+      <c r="D2115" t="n">
+        <v>755.1</v>
+      </c>
+      <c r="E2115" t="n">
+        <v>2645.8</v>
+      </c>
+      <c r="F2115" t="n">
+        <v>15392.8</v>
+      </c>
+      <c r="G2115" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2115" t="n">
+        <v>3488.7</v>
+      </c>
+      <c r="I2115" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2115" t="n">
+        <v>721.6</v>
+      </c>
+      <c r="K2115" t="n">
+        <v>43044.6</v>
+      </c>
+    </row>
+    <row r="2116">
+      <c r="A2116" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B2116" t="n">
+        <v>19428.7</v>
+      </c>
+      <c r="C2116" t="n">
+        <v>632</v>
+      </c>
+      <c r="D2116" t="n">
+        <v>299.1</v>
+      </c>
+      <c r="E2116" t="n">
+        <v>3195.3</v>
+      </c>
+      <c r="F2116" t="n">
+        <v>14902.8</v>
+      </c>
+      <c r="G2116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2116" t="n">
+        <v>3994.8</v>
+      </c>
+      <c r="I2116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2116" t="n">
+        <v>718.1</v>
+      </c>
+      <c r="K2116" t="n">
+        <v>43170.7</v>
+      </c>
+    </row>
+    <row r="2117">
+      <c r="A2117" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B2117" t="n">
+        <v>21980.6</v>
+      </c>
+      <c r="C2117" t="n">
+        <v>567.5</v>
+      </c>
+      <c r="D2117" t="n">
+        <v>227.9</v>
+      </c>
+      <c r="E2117" t="n">
+        <v>3047.8</v>
+      </c>
+      <c r="F2117" t="n">
+        <v>13240</v>
+      </c>
+      <c r="G2117" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2117" t="n">
+        <v>947.4</v>
+      </c>
+      <c r="I2117" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2117" t="n">
+        <v>721.2</v>
+      </c>
+      <c r="K2117" t="n">
+        <v>40732.4</v>
+      </c>
+    </row>
+    <row r="2118">
+      <c r="A2118" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B2118" t="n">
+        <v>18849.7</v>
+      </c>
+      <c r="C2118" t="n">
+        <v>340.3</v>
+      </c>
+      <c r="D2118" t="n">
+        <v>1000.5</v>
+      </c>
+      <c r="E2118" t="n">
+        <v>2200.6</v>
+      </c>
+      <c r="F2118" t="n">
+        <v>10865.1</v>
+      </c>
+      <c r="G2118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2118" t="n">
+        <v>1001.8</v>
+      </c>
+      <c r="I2118" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2118" t="n">
+        <v>711.3</v>
+      </c>
+      <c r="K2118" t="n">
+        <v>34969.3</v>
+      </c>
+    </row>
+    <row r="2119">
+      <c r="A2119" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B2119" t="n">
+        <v>22408.2</v>
+      </c>
+      <c r="C2119" t="n">
+        <v>417.2</v>
+      </c>
+      <c r="D2119" t="n">
+        <v>1342</v>
+      </c>
+      <c r="E2119" t="n">
+        <v>2570.3</v>
+      </c>
+      <c r="F2119" t="n">
+        <v>10089.9</v>
+      </c>
+      <c r="G2119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2119" t="n">
+        <v>825.7</v>
+      </c>
+      <c r="I2119" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J2119" t="n">
+        <v>708.9</v>
+      </c>
+      <c r="K2119" t="n">
+        <v>38372.1</v>
+      </c>
+    </row>
+    <row r="2120">
+      <c r="A2120" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B2120" t="n">
+        <v>26213.6</v>
+      </c>
+      <c r="C2120" t="n">
+        <v>437.2</v>
+      </c>
+      <c r="D2120" t="n">
+        <v>1345.5</v>
+      </c>
+      <c r="E2120" t="n">
+        <v>2526.1</v>
+      </c>
+      <c r="F2120" t="n">
+        <v>8949.1</v>
+      </c>
+      <c r="G2120" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2120" t="n">
+        <v>1157.6</v>
+      </c>
+      <c r="I2120" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2120" t="n">
+        <v>711.6</v>
+      </c>
+      <c r="K2120" t="n">
+        <v>41345.6</v>
+      </c>
+    </row>
+    <row r="2121">
+      <c r="A2121" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B2121" t="n">
+        <v>25344.3</v>
+      </c>
+      <c r="C2121" t="n">
+        <v>555.2</v>
+      </c>
+      <c r="D2121" t="n">
+        <v>1506.1</v>
+      </c>
+      <c r="E2121" t="n">
+        <v>3226.8</v>
+      </c>
+      <c r="F2121" t="n">
+        <v>9802.6</v>
+      </c>
+      <c r="G2121" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2121" t="n">
+        <v>2568.8</v>
+      </c>
+      <c r="I2121" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J2121" t="n">
+        <v>707</v>
+      </c>
+      <c r="K2121" t="n">
+        <v>43716.4</v>
+      </c>
+    </row>
+    <row r="2122">
+      <c r="A2122" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B2122" t="n">
+        <v>25990.3</v>
+      </c>
+      <c r="C2122" t="n">
+        <v>624.7</v>
+      </c>
+      <c r="D2122" t="n">
+        <v>1358.9</v>
+      </c>
+      <c r="E2122" t="n">
+        <v>2163.4</v>
+      </c>
+      <c r="F2122" t="n">
+        <v>10997.4</v>
+      </c>
+      <c r="G2122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2122" t="n">
+        <v>2348.5</v>
+      </c>
+      <c r="I2122" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="J2122" t="n">
+        <v>706.8</v>
+      </c>
+      <c r="K2122" t="n">
+        <v>44209.8</v>
+      </c>
+    </row>
+    <row r="2123">
+      <c r="A2123" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B2123" t="n">
+        <v>25402.7</v>
+      </c>
+      <c r="C2123" t="n">
+        <v>527.4</v>
+      </c>
+      <c r="D2123" t="n">
+        <v>1818.2</v>
+      </c>
+      <c r="E2123" t="n">
+        <v>3295.7</v>
+      </c>
+      <c r="F2123" t="n">
+        <v>9286.799999999999</v>
+      </c>
+      <c r="G2123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2123" t="n">
+        <v>931.5</v>
+      </c>
+      <c r="I2123" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J2123" t="n">
+        <v>717.5</v>
+      </c>
+      <c r="K2123" t="n">
+        <v>41985.2</v>
+      </c>
+    </row>
+    <row r="2124">
+      <c r="A2124" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B2124" t="n">
+        <v>22819.2</v>
+      </c>
+      <c r="C2124" t="n">
+        <v>337.2</v>
+      </c>
+      <c r="D2124" t="n">
+        <v>2244.6</v>
+      </c>
+      <c r="E2124" t="n">
+        <v>2827.8</v>
+      </c>
+      <c r="F2124" t="n">
+        <v>8531.200000000001</v>
+      </c>
+      <c r="G2124" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2124" t="n">
+        <v>666.4</v>
+      </c>
+      <c r="I2124" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J2124" t="n">
+        <v>722.1</v>
+      </c>
+      <c r="K2124" t="n">
+        <v>38153.9</v>
+      </c>
+    </row>
+    <row r="2125">
+      <c r="A2125" s="4" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B2125" t="n">
+        <v>16575.2</v>
+      </c>
+      <c r="C2125" t="n">
+        <v>473.4</v>
+      </c>
+      <c r="D2125" t="n">
+        <v>2192.1</v>
+      </c>
+      <c r="E2125" t="n">
+        <v>3458.6</v>
+      </c>
+      <c r="F2125" t="n">
+        <v>9823.5</v>
+      </c>
+      <c r="G2125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2125" t="n">
+        <v>970.4</v>
+      </c>
+      <c r="I2125" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J2125" t="n">
+        <v>722.9</v>
+      </c>
+      <c r="K2125" t="n">
+        <v>34218.1</v>
+      </c>
+    </row>
+    <row r="2126">
+      <c r="A2126" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B2126" t="n">
+        <v>18485.1</v>
+      </c>
+      <c r="C2126" t="n">
+        <v>699.4</v>
+      </c>
+      <c r="D2126" t="n">
+        <v>1740.5</v>
+      </c>
+      <c r="E2126" t="n">
+        <v>3917.8</v>
+      </c>
+      <c r="F2126" t="n">
+        <v>9363.1</v>
+      </c>
+      <c r="G2126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2126" t="n">
+        <v>4051.5</v>
+      </c>
+      <c r="I2126" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J2126" t="n">
+        <v>728.4</v>
+      </c>
+      <c r="K2126" t="n">
+        <v>38989</v>
+      </c>
+    </row>
+    <row r="2127">
+      <c r="A2127" s="4" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B2127" t="n">
+        <v>14442.4</v>
+      </c>
+      <c r="C2127" t="n">
+        <v>582.2</v>
+      </c>
+      <c r="D2127" t="n">
+        <v>1039.1</v>
+      </c>
+      <c r="E2127" t="n">
+        <v>3711.9</v>
+      </c>
+      <c r="F2127" t="n">
+        <v>8675.5</v>
+      </c>
+      <c r="G2127" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2127" t="n">
+        <v>3295.2</v>
+      </c>
+      <c r="I2127" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="J2127" t="n">
+        <v>603.3</v>
+      </c>
+      <c r="K2127" t="n">
+        <v>32356.9</v>
       </c>
     </row>
   </sheetData>
@@ -76389,7 +77292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M69"/>
+  <dimension ref="A1:M70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79247,6 +80150,47 @@
         <v>3.877</v>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B70" t="n">
+        <v>21.476</v>
+      </c>
+      <c r="C70" t="n">
+        <v>23.829</v>
+      </c>
+      <c r="D70" t="n">
+        <v>129.782</v>
+      </c>
+      <c r="E70" t="n">
+        <v>359.55</v>
+      </c>
+      <c r="F70" t="n">
+        <v>1.453</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0.199</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
+        <v>9.444000000000001</v>
+      </c>
+      <c r="J70" t="n">
+        <v>395.095</v>
+      </c>
+      <c r="K70" t="n">
+        <v>152.146</v>
+      </c>
+      <c r="L70" t="n">
+        <v>134.719</v>
+      </c>
+      <c r="M70" t="n">
+        <v>5.62</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/guatemala_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/guatemala_power_generation_daily.xlsx
@@ -2778,25 +2778,25 @@
         <v>46296</v>
       </c>
       <c r="B71" t="n">
-        <v>523.1177</v>
+        <v>526.6013</v>
       </c>
       <c r="C71" t="n">
-        <v>13.0283</v>
+        <v>13.1471</v>
       </c>
       <c r="D71" t="n">
-        <v>22.7735</v>
+        <v>23.009</v>
       </c>
       <c r="E71" t="n">
-        <v>78.053</v>
+        <v>78.0528</v>
       </c>
       <c r="F71" t="n">
-        <v>353.1659</v>
+        <v>354.9919</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>102.3068</v>
+        <v>103.5073</v>
       </c>
     </row>
   </sheetData>
@@ -77251,34 +77251,34 @@
         <v>46322</v>
       </c>
       <c r="B2127" t="n">
-        <v>14442.4</v>
+        <v>17926</v>
       </c>
       <c r="C2127" t="n">
-        <v>582.2</v>
+        <v>701</v>
       </c>
       <c r="D2127" t="n">
-        <v>1039.1</v>
+        <v>1274.6</v>
       </c>
       <c r="E2127" t="n">
-        <v>3711.9</v>
+        <v>3711.7</v>
       </c>
       <c r="F2127" t="n">
-        <v>8675.5</v>
+        <v>10501.5</v>
       </c>
       <c r="G2127" t="n">
         <v>0</v>
       </c>
       <c r="H2127" t="n">
-        <v>3295.2</v>
+        <v>4367.7</v>
       </c>
       <c r="I2127" t="n">
-        <v>7.3</v>
+        <v>8.9</v>
       </c>
       <c r="J2127" t="n">
-        <v>603.3</v>
+        <v>729.7</v>
       </c>
       <c r="K2127" t="n">
-        <v>32356.9</v>
+        <v>39221.1</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/guatemala_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/guatemala_power_generation_daily.xlsx
@@ -2778,25 +2778,25 @@
         <v>46296</v>
       </c>
       <c r="B71" t="n">
-        <v>526.6013</v>
+        <v>543.8099</v>
       </c>
       <c r="C71" t="n">
-        <v>13.1471</v>
+        <v>13.7773</v>
       </c>
       <c r="D71" t="n">
-        <v>23.009</v>
+        <v>24.4968</v>
       </c>
       <c r="E71" t="n">
-        <v>78.0528</v>
+        <v>81.79490000000001</v>
       </c>
       <c r="F71" t="n">
-        <v>354.9919</v>
+        <v>365.8294</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>103.5073</v>
+        <v>107.5548</v>
       </c>
     </row>
   </sheetData>
@@ -2811,7 +2811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2127"/>
+  <dimension ref="A1:K2128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77263,13 +77263,13 @@
         <v>3711.7</v>
       </c>
       <c r="F2127" t="n">
-        <v>10501.5</v>
+        <v>10503.6</v>
       </c>
       <c r="G2127" t="n">
         <v>0</v>
       </c>
       <c r="H2127" t="n">
-        <v>4367.7</v>
+        <v>4367.1</v>
       </c>
       <c r="I2127" t="n">
         <v>8.9</v>
@@ -77278,7 +77278,42 @@
         <v>729.7</v>
       </c>
       <c r="K2127" t="n">
-        <v>39221.1</v>
+        <v>39222.6</v>
+      </c>
+    </row>
+    <row r="2128">
+      <c r="A2128" s="4" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B2128" t="n">
+        <v>17208.6</v>
+      </c>
+      <c r="C2128" t="n">
+        <v>630.2</v>
+      </c>
+      <c r="D2128" t="n">
+        <v>1487.8</v>
+      </c>
+      <c r="E2128" t="n">
+        <v>3742.1</v>
+      </c>
+      <c r="F2128" t="n">
+        <v>10835.4</v>
+      </c>
+      <c r="G2128" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2128" t="n">
+        <v>3321.9</v>
+      </c>
+      <c r="I2128" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J2128" t="n">
+        <v>719.3</v>
+      </c>
+      <c r="K2128" t="n">
+        <v>37952.2</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/guatemala_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/guatemala_power_generation_daily.xlsx
@@ -2778,25 +2778,25 @@
         <v>46296</v>
       </c>
       <c r="B71" t="n">
-        <v>543.8099</v>
+        <v>561.7533000000001</v>
       </c>
       <c r="C71" t="n">
-        <v>13.7773</v>
+        <v>14.3944</v>
       </c>
       <c r="D71" t="n">
-        <v>24.4968</v>
+        <v>25.6796</v>
       </c>
       <c r="E71" t="n">
-        <v>81.79490000000001</v>
+        <v>85.16990000000001</v>
       </c>
       <c r="F71" t="n">
-        <v>365.8294</v>
+        <v>378.3604</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>107.5548</v>
+        <v>111.9789</v>
       </c>
     </row>
   </sheetData>
@@ -2811,7 +2811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2128"/>
+  <dimension ref="A1:K2129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77263,7 +77263,7 @@
         <v>3711.7</v>
       </c>
       <c r="F2127" t="n">
-        <v>10503.6</v>
+        <v>10504.1</v>
       </c>
       <c r="G2127" t="n">
         <v>0</v>
@@ -77278,7 +77278,7 @@
         <v>729.7</v>
       </c>
       <c r="K2127" t="n">
-        <v>39222.6</v>
+        <v>39223</v>
       </c>
     </row>
     <row r="2128">
@@ -77314,6 +77314,41 @@
       </c>
       <c r="K2128" t="n">
         <v>37952.2</v>
+      </c>
+    </row>
+    <row r="2129">
+      <c r="A2129" s="4" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B2129" t="n">
+        <v>17943.4</v>
+      </c>
+      <c r="C2129" t="n">
+        <v>617.1</v>
+      </c>
+      <c r="D2129" t="n">
+        <v>1182.8</v>
+      </c>
+      <c r="E2129" t="n">
+        <v>3375</v>
+      </c>
+      <c r="F2129" t="n">
+        <v>12530.5</v>
+      </c>
+      <c r="G2129" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2129" t="n">
+        <v>3703.5</v>
+      </c>
+      <c r="I2129" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J2129" t="n">
+        <v>715.8</v>
+      </c>
+      <c r="K2129" t="n">
+        <v>40072.8</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/guatemala_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/guatemala_power_generation_daily.xlsx
@@ -2778,25 +2778,25 @@
         <v>46296</v>
       </c>
       <c r="B71" t="n">
-        <v>561.7533000000001</v>
+        <v>580.552</v>
       </c>
       <c r="C71" t="n">
-        <v>14.3944</v>
+        <v>15.0919</v>
       </c>
       <c r="D71" t="n">
-        <v>25.6796</v>
+        <v>26.8061</v>
       </c>
       <c r="E71" t="n">
-        <v>85.16990000000001</v>
+        <v>88.57300000000001</v>
       </c>
       <c r="F71" t="n">
-        <v>378.3604</v>
+        <v>390.5495</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>111.9789</v>
+        <v>117.1225</v>
       </c>
     </row>
   </sheetData>
@@ -2811,7 +2811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2129"/>
+  <dimension ref="A1:K2130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77339,7 +77339,7 @@
         <v>0</v>
       </c>
       <c r="H2129" t="n">
-        <v>3703.5</v>
+        <v>3703.1</v>
       </c>
       <c r="I2129" t="n">
         <v>4.8</v>
@@ -77348,7 +77348,42 @@
         <v>715.8</v>
       </c>
       <c r="K2129" t="n">
-        <v>40072.8</v>
+        <v>40072.5</v>
+      </c>
+    </row>
+    <row r="2130">
+      <c r="A2130" s="4" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B2130" t="n">
+        <v>18798.7</v>
+      </c>
+      <c r="C2130" t="n">
+        <v>697.5</v>
+      </c>
+      <c r="D2130" t="n">
+        <v>1126.5</v>
+      </c>
+      <c r="E2130" t="n">
+        <v>3403.1</v>
+      </c>
+      <c r="F2130" t="n">
+        <v>12189.1</v>
+      </c>
+      <c r="G2130" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2130" t="n">
+        <v>4414.9</v>
+      </c>
+      <c r="I2130" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J2130" t="n">
+        <v>724</v>
+      </c>
+      <c r="K2130" t="n">
+        <v>41358.9</v>
       </c>
     </row>
   </sheetData>
